--- a/Specialty Claims 2026-S1/ALL Claims 2026-S1 - Master.xlsx
+++ b/Specialty Claims 2026-S1/ALL Claims 2026-S1 - Master.xlsx
@@ -282,7 +282,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22561" uniqueCount="1760">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22562" uniqueCount="1761">
   <si>
     <t>ALL Claims 2026-S1 - Master</t>
   </si>
@@ -5562,6 +5562,9 @@
   </si>
   <si>
     <t xml:space="preserve">HF559271506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statuses currently in use: Denied, Finalized, PAID, Pending, Received, Rejected, Under Review.</t>
   </si>
 </sst>
 </file>
@@ -14808,7 +14811,7 @@
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>25</v>
+        <v>1760</v>
       </c>
     </row>
   </sheetData>
@@ -20542,11 +20545,11 @@
     <row r="47" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D47,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D47,[6]DME!$D$2:$D$52,0))),"")</f>
-        <v>Pending</v>
+        <v>Under Review</v>
       </c>
       <c r="B47" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$B$2:$B$52,MATCH($D47,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$B$2:$B$52,MATCH($D47,[6]DME!$D$2:$D$52,0))),"")</f>
-        <v>***Still processing - check again on 09/16/2026</v>
+        <v>Still processing - check again on 09/16/2026</v>
       </c>
       <c r="C47" s="6" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$C$2:$C$52,MATCH($D47,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$C$2:$C$52,MATCH($D47,[6]DME!$D$2:$D$52,0))),"")</f>
@@ -20915,11 +20918,11 @@
     <row r="50" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]ORTHO!$A$2:$A$39,MATCH($D50,[6]ORTHO!$D$2:$D$39,0))="","",INDEX([6]ORTHO!$A$2:$A$39,MATCH($D50,[6]ORTHO!$D$2:$D$39,0))),"")</f>
-        <v>Denied</v>
+        <v>Under Review</v>
       </c>
       <c r="B50" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]ORTHO!$B$2:$B$39,MATCH($D50,[6]ORTHO!$D$2:$D$39,0))="","",INDEX([6]ORTHO!$B$2:$B$39,MATCH($D50,[6]ORTHO!$D$2:$D$39,0))),"")</f>
-        <v>***Call ins to get bar code letter if needed and insights on denials</v>
+        <v>Call ins to get bar code letter if needed and insights on denials</v>
       </c>
       <c r="C50" s="6">
         <f>IFERROR(IF(INDEX([6]ORTHO!$C$2:$C$39,MATCH($D50,[6]ORTHO!$D$2:$D$39,0))="","",INDEX([6]ORTHO!$C$2:$C$39,MATCH($D50,[6]ORTHO!$D$2:$D$39,0))),"")</f>
@@ -22300,11 +22303,11 @@
     <row r="61" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]ORTHO!$A$2:$A$39,MATCH($D61,[6]ORTHO!$D$2:$D$39,0))="","",INDEX([6]ORTHO!$A$2:$A$39,MATCH($D61,[6]ORTHO!$D$2:$D$39,0))),"")</f>
-        <v>Denied</v>
+        <v>Under Review</v>
       </c>
       <c r="B61" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]ORTHO!$B$2:$B$39,MATCH($D61,[6]ORTHO!$D$2:$D$39,0))="","",INDEX([6]ORTHO!$B$2:$B$39,MATCH($D61,[6]ORTHO!$D$2:$D$39,0))),"")</f>
-        <v>***Call ins to get bar code letter if needed and insights on denials</v>
+        <v>Call ins to get bar code letter if needed and insights on denials</v>
       </c>
       <c r="C61" s="6">
         <f>IFERROR(IF(INDEX([6]ORTHO!$C$2:$C$39,MATCH($D61,[6]ORTHO!$D$2:$D$39,0))="","",INDEX([6]ORTHO!$C$2:$C$39,MATCH($D61,[6]ORTHO!$D$2:$D$39,0))),"")</f>
@@ -22669,11 +22672,11 @@
     <row r="64" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D64,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D64,[6]DME!$D$2:$D$52,0))),"")</f>
-        <v>Denied</v>
+        <v>Under Review</v>
       </c>
       <c r="B64" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$B$2:$B$52,MATCH($D64,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$B$2:$B$52,MATCH($D64,[6]DME!$D$2:$D$52,0))),"")</f>
-        <v xml:space="preserve">***Waiting for bcbs alabama portal access - Jess sent MR throught fax </v>
+        <v xml:space="preserve">Waiting for bcbs alabama portal access - Jess sent MR throught fax </v>
       </c>
       <c r="C64" s="6">
         <f>IFERROR(IF(INDEX([6]DME!$C$2:$C$52,MATCH($D64,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$C$2:$C$52,MATCH($D64,[6]DME!$D$2:$D$52,0))),"")</f>
@@ -23157,11 +23160,11 @@
     <row r="68" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]BH!$A$2:$A$82,MATCH($D68,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$A$2:$A$82,MATCH($D68,[6]BH!$D$2:$D$82,0))),"")</f>
-        <v>Denied</v>
+        <v>Under Review</v>
       </c>
       <c r="B68" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]BH!$B$2:$B$82,MATCH($D68,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$B$2:$B$82,MATCH($D68,[6]BH!$D$2:$D$82,0))),"")</f>
-        <v xml:space="preserve">***Start chat on UHC portal to check the rendering provider status </v>
+        <v xml:space="preserve">Start chat on UHC portal to check the rendering provider status </v>
       </c>
       <c r="C68" s="6">
         <f>IFERROR(IF(INDEX([6]BH!$C$2:$C$82,MATCH($D68,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$C$2:$C$82,MATCH($D68,[6]BH!$D$2:$D$82,0))),"")</f>
@@ -23401,11 +23404,11 @@
     <row r="70" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D70,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D70,[6]DME!$D$2:$D$52,0))),"")</f>
-        <v>Denied</v>
+        <v>Under Review</v>
       </c>
       <c r="B70" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$B$2:$B$52,MATCH($D70,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$B$2:$B$52,MATCH($D70,[6]DME!$D$2:$D$52,0))),"")</f>
-        <v>***call ins and check provider status on dos - DND rendering provider OON</v>
+        <v>call ins and check provider status on dos - DND rendering provider OON</v>
       </c>
       <c r="C70" s="6">
         <f>IFERROR(IF(INDEX([6]DME!$C$2:$C$52,MATCH($D70,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$C$2:$C$52,MATCH($D70,[6]DME!$D$2:$D$52,0))),"")</f>
@@ -24752,11 +24755,11 @@
     <row r="81" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D81,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D81,[6]DME!$D$2:$D$52,0))),"")</f>
-        <v>Denied</v>
+        <v>Under Review</v>
       </c>
       <c r="B81" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$B$2:$B$52,MATCH($D81,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$B$2:$B$52,MATCH($D81,[6]DME!$D$2:$D$52,0))),"")</f>
-        <v>***DND Acodes Preferred Homecare is responsible for these services. Please submit the claim to Preferred Homecare for consideration.</v>
+        <v>DND Acodes Preferred Homecare is responsible for these services. Please submit the claim to Preferred Homecare for consideration.</v>
       </c>
       <c r="C81" s="6">
         <f>IFERROR(IF(INDEX([6]DME!$C$2:$C$52,MATCH($D81,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$C$2:$C$52,MATCH($D81,[6]DME!$D$2:$D$52,0))),"")</f>
@@ -25500,11 +25503,11 @@
     <row r="87" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D87,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D87,[6]DME!$D$2:$D$52,0))),"")</f>
-        <v>Denied</v>
+        <v>Under Review</v>
       </c>
       <c r="B87" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$B$2:$B$52,MATCH($D87,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$B$2:$B$52,MATCH($D87,[6]DME!$D$2:$D$52,0))),"")</f>
-        <v>*** DND Acodes Preferred Homecare is responsible for these services. Please submit the claim to Preferred Homecare for consideration. -Remark N216 We do not offer coverage for this type of service or the patient is not enrolled in this portion of our benefit package</v>
+        <v>DND Acodes Preferred Homecare is responsible for these services. Please submit the claim to Preferred Homecare for consideration. -Remark N216 We do not offer coverage for this type of service or the patient is not enrolled in this portion of our benefit package</v>
       </c>
       <c r="C87" s="6">
         <f>IFERROR(IF(INDEX([6]DME!$C$2:$C$52,MATCH($D87,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$C$2:$C$52,MATCH($D87,[6]DME!$D$2:$D$52,0))),"")</f>
@@ -26367,11 +26370,11 @@
     <row r="94" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]BH!$A$2:$A$33,MATCH($D94,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$A$2:$A$33,MATCH($D94,[5]BH!$D$2:$D$33,0))),"")</f>
-        <v>Denied</v>
+        <v>Under Review</v>
       </c>
       <c r="B94" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]BH!$B$2:$B$33,MATCH($D94,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$B$2:$B$33,MATCH($D94,[5]BH!$D$2:$D$33,0))),"")</f>
-        <v>***I need to call PT - Aetna termed date March 31, 2026</v>
+        <v>I need to call PT - Aetna termed date March 31, 2026</v>
       </c>
       <c r="C94" s="6">
         <f>IFERROR(IF(INDEX([5]BH!$C$2:$C$33,MATCH($D94,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$C$2:$C$33,MATCH($D94,[5]BH!$D$2:$D$33,0))),"")</f>
@@ -29706,11 +29709,11 @@
     <row r="121" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]DME!$A$2:$A$35,MATCH($D121,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$A$2:$A$35,MATCH($D121,[5]DME!$D$2:$D$35,0))),"")</f>
-        <v>Denied</v>
+        <v>Under Review</v>
       </c>
       <c r="B121" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]DME!$B$2:$B$35,MATCH($D121,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$B$2:$B$35,MATCH($D121,[5]DME!$D$2:$D$35,0))),"")</f>
-        <v>***MUE issue - CALL INS</v>
+        <v>MUE issue - CALL INS</v>
       </c>
       <c r="C121" s="6">
         <f>IFERROR(IF(INDEX([5]DME!$C$2:$C$35,MATCH($D121,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$C$2:$C$35,MATCH($D121,[5]DME!$D$2:$D$35,0))),"")</f>
@@ -36756,11 +36759,11 @@
     <row r="177" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A177" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]BH!$A$2:$A$32,MATCH($D177,[2]BH!$D$2:$D$32,0))="","",INDEX([2]BH!$A$2:$A$32,MATCH($D177,[2]BH!$D$2:$D$32,0))),"")</f>
-        <v>Pending</v>
+        <v>Under Review</v>
       </c>
       <c r="B177" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]BH!$B$2:$B$32,MATCH($D177,[2]BH!$D$2:$D$32,0))="","",INDEX([2]BH!$B$2:$B$32,MATCH($D177,[2]BH!$D$2:$D$32,0))),"")</f>
-        <v>***Waiting for payment to be posted, so I can cross over to secondary - Primary paid - Edited rendering and referral provider, and resubmitted - Invalid rendering provider NPIInvalid rendering provider NPI - Rejected</v>
+        <v>Waiting for payment to be posted, so I can cross over to secondary - Primary paid - Edited rendering and referral provider, and resubmitted - Invalid rendering provider NPIInvalid rendering provider NPI - Rejected</v>
       </c>
       <c r="C177" s="6">
         <f>IFERROR(IF(INDEX([2]BH!$C$2:$C$32,MATCH($D177,[2]BH!$D$2:$D$32,0))="","",INDEX([2]BH!$C$2:$C$32,MATCH($D177,[2]BH!$D$2:$D$32,0))),"")</f>
@@ -38613,11 +38616,11 @@
     <row r="192" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A192" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$A$2:$A$34,MATCH($D192,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$A$2:$A$34,MATCH($D192,[4]DME!$D$2:$D$34,0))),"")</f>
-        <v/>
+        <v>Under Review</v>
       </c>
       <c r="B192" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$B$2:$B$34,MATCH($D192,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$B$2:$B$34,MATCH($D192,[4]DME!$D$2:$D$34,0))),"")</f>
-        <v/>
+        <v>Shift to PT if I find same and similar on portal  - ABN signed - Another L0650 was dispensed back on 04/25/2022 - Supplier SONOSPINE ARIZONA LLC - DND L0650 M3 Equipment is the same or similar to equipment already being used</v>
       </c>
       <c r="C192" s="6">
         <f>IFERROR(IF(INDEX([4]DME!$C$2:$C$34,MATCH($D192,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$C$2:$C$34,MATCH($D192,[4]DME!$D$2:$D$34,0))),"")</f>
@@ -53790,11 +53793,11 @@
     <row r="315" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A315" s="5" t="str">
         <f>IFERROR(IF(INDEX([3]DME!$A$2:$A$12,MATCH($D315,[3]DME!$D$2:$D$12,0))="","",INDEX([3]DME!$A$2:$A$12,MATCH($D315,[3]DME!$D$2:$D$12,0))),"")</f>
-        <v>Denied</v>
+        <v>Under Review</v>
       </c>
       <c r="B315" s="5" t="str">
         <f>IFERROR(IF(INDEX([3]DME!$B$2:$B$12,MATCH($D315,[3]DME!$D$2:$D$12,0))="","",INDEX([3]DME!$B$2:$B$12,MATCH($D315,[3]DME!$D$2:$D$12,0))),"")</f>
-        <v xml:space="preserve">***Auth issue - Denied payment again - Bri resubmitted - Provider TAX ID/NPI Combination is not on file with BCBS AZ. </v>
+        <v xml:space="preserve">Auth issue - Denied payment again - Bri resubmitted - Provider TAX ID/NPI Combination is not on file with BCBS AZ. </v>
       </c>
       <c r="C315" s="6">
         <f>IFERROR(IF(INDEX([3]DME!$C$2:$C$12,MATCH($D315,[3]DME!$D$2:$D$12,0))="","",INDEX([3]DME!$C$2:$C$12,MATCH($D315,[3]DME!$D$2:$D$12,0))),"")</f>
@@ -57248,11 +57251,11 @@
     <row r="343" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A343" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]US!$A$2:$A$15,MATCH($D343,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$A$2:$A$15,MATCH($D343,[2]US!$D$2:$D$15,0))),"")</f>
-        <v>Denied</v>
+        <v>Under Review</v>
       </c>
       <c r="B343" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]US!$B$2:$B$15,MATCH($D343,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$B$2:$B$15,MATCH($D343,[2]US!$D$2:$D$15,0))),"")</f>
-        <v xml:space="preserve">***I need to ask Juan for MR </v>
+        <v xml:space="preserve">I need to ask Juan for MR </v>
       </c>
       <c r="C343" s="6">
         <f>IFERROR(IF(INDEX([2]US!$C$2:$C$15,MATCH($D343,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$C$2:$C$15,MATCH($D343,[2]US!$D$2:$D$15,0))),"")</f>
@@ -57863,11 +57866,11 @@
     <row r="348" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A348" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]BH!$A$2:$A$32,MATCH($D348,[2]BH!$D$2:$D$32,0))="","",INDEX([2]BH!$A$2:$A$32,MATCH($D348,[2]BH!$D$2:$D$32,0))),"")</f>
-        <v>Denied</v>
+        <v>Under Review</v>
       </c>
       <c r="B348" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]BH!$B$2:$B$32,MATCH($D348,[2]BH!$D$2:$D$32,0))="","",INDEX([2]BH!$B$2:$B$32,MATCH($D348,[2]BH!$D$2:$D$32,0))),"")</f>
-        <v>***Sent email to AZ Blue for insights - active coverage on DOS - DND Expenses incurred after coverage terminated</v>
+        <v>Sent email to AZ Blue for insights - active coverage on DOS - DND Expenses incurred after coverage terminated</v>
       </c>
       <c r="C348" s="6">
         <f>IFERROR(IF(INDEX([2]BH!$C$2:$C$32,MATCH($D348,[2]BH!$D$2:$D$32,0))="","",INDEX([2]BH!$C$2:$C$32,MATCH($D348,[2]BH!$D$2:$D$32,0))),"")</f>
@@ -59591,11 +59594,11 @@
     <row r="362" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A362" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]GAE!$A$2:$A$8,MATCH($D362,[4]GAE!$D$2:$D$8,0))="","",INDEX([4]GAE!$A$2:$A$8,MATCH($D362,[4]GAE!$D$2:$D$8,0))),"")</f>
-        <v>Denied</v>
+        <v>Under Review</v>
       </c>
       <c r="B362" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]GAE!$B$2:$B$8,MATCH($D362,[4]GAE!$D$2:$D$8,0))="","",INDEX([4]GAE!$B$2:$B$8,MATCH($D362,[4]GAE!$D$2:$D$8,0))),"")</f>
-        <v xml:space="preserve">***DND 75710 This procedure or procedure/modifier combination is not compatible with another procedure or procedure/modifier combination provided on the same day according to the National Correct Coding Initiative or workers compensation state regulations/ fee schedule requirements - Adjusted balance for 36246 not included in the auth requested - 36248 add on requires payment for other cpt code - 99153 cant be billed on pos 24 </v>
+        <v xml:space="preserve">DND 75710 This procedure or procedure/modifier combination is not compatible with another procedure or procedure/modifier combination provided on the same day according to the National Correct Coding Initiative or workers compensation state regulations/ fee schedule requirements - Adjusted balance for 36246 not included in the auth requested - 36248 add on requires payment for other cpt code - 99153 cant be billed on pos 24 </v>
       </c>
       <c r="C362" s="6">
         <f>IFERROR(IF(INDEX([4]GAE!$C$2:$C$8,MATCH($D362,[4]GAE!$D$2:$D$8,0))="","",INDEX([4]GAE!$C$2:$C$8,MATCH($D362,[4]GAE!$D$2:$D$8,0))),"")</f>
@@ -59845,11 +59848,11 @@
     <row r="364" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A364" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]ORTHO!$A$2:$A$24,MATCH($D364,[5]ORTHO!$D$2:$D$24,0))="","",INDEX([5]ORTHO!$A$2:$A$24,MATCH($D364,[5]ORTHO!$D$2:$D$24,0))),"")</f>
-        <v>Denied</v>
+        <v>Under Review</v>
       </c>
       <c r="B364" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]ORTHO!$B$2:$B$24,MATCH($D364,[5]ORTHO!$D$2:$D$24,0))="","",INDEX([5]ORTHO!$B$2:$B$24,MATCH($D364,[5]ORTHO!$D$2:$D$24,0))),"")</f>
-        <v xml:space="preserve">***Call ins - Bundled - but we have an auth for this one </v>
+        <v xml:space="preserve">Call ins - Bundled - but we have an auth for this one </v>
       </c>
       <c r="C364" s="6">
         <f>IFERROR(IF(INDEX([5]ORTHO!$C$2:$C$24,MATCH($D364,[5]ORTHO!$D$2:$D$24,0))="","",INDEX([5]ORTHO!$C$2:$C$24,MATCH($D364,[5]ORTHO!$D$2:$D$24,0))),"")</f>
@@ -61428,11 +61431,11 @@
     <row r="377" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A377" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]GAE!$A$2:$A$8,MATCH($D377,[4]GAE!$D$2:$D$8,0))="","",INDEX([4]GAE!$A$2:$A$8,MATCH($D377,[4]GAE!$D$2:$D$8,0))),"")</f>
-        <v>Denied</v>
+        <v>Under Review</v>
       </c>
       <c r="B377" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]GAE!$B$2:$B$8,MATCH($D377,[4]GAE!$D$2:$D$8,0))="","",INDEX([4]GAE!$B$2:$B$8,MATCH($D377,[4]GAE!$D$2:$D$8,0))),"")</f>
-        <v xml:space="preserve">***DND 36248 due to exceeded MUE - DND 36245, 36246, and 75710 due to invalid dx </v>
+        <v xml:space="preserve">DND 36248 due to exceeded MUE - DND 36245, 36246, and 75710 due to invalid dx </v>
       </c>
       <c r="C377" s="6">
         <f>IFERROR(IF(INDEX([4]GAE!$C$2:$C$8,MATCH($D377,[4]GAE!$D$2:$D$8,0))="","",INDEX([4]GAE!$C$2:$C$8,MATCH($D377,[4]GAE!$D$2:$D$8,0))),"")</f>
@@ -63404,11 +63407,11 @@
     <row r="393" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A393" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$A$2:$A$34,MATCH($D393,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$A$2:$A$34,MATCH($D393,[4]DME!$D$2:$D$34,0))),"")</f>
-        <v>Denied</v>
+        <v>Under Review</v>
       </c>
       <c r="B393" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$B$2:$B$34,MATCH($D393,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$B$2:$B$34,MATCH($D393,[4]DME!$D$2:$D$34,0))),"")</f>
-        <v>***chat with ins to confirm covarage - ABN signed - charges per ins contract - PR non covered</v>
+        <v>chat with ins to confirm covarage - ABN signed - charges per ins contract - PR non covered</v>
       </c>
       <c r="C393" s="6">
         <f>IFERROR(IF(INDEX([4]DME!$C$2:$C$34,MATCH($D393,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$C$2:$C$34,MATCH($D393,[4]DME!$D$2:$D$34,0))),"")</f>
@@ -63650,11 +63653,11 @@
     <row r="395" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A395" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]US!$A$2:$A$23,MATCH($D395,[4]US!$D$2:$D$23,0))="","",INDEX([4]US!$A$2:$A$23,MATCH($D395,[4]US!$D$2:$D$23,0))),"")</f>
-        <v>Denied</v>
+        <v>Under Review</v>
       </c>
       <c r="B395" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]US!$B$2:$B$23,MATCH($D395,[4]US!$D$2:$D$23,0))="","",INDEX([4]US!$B$2:$B$23,MATCH($D395,[4]US!$D$2:$D$23,0))),"")</f>
-        <v>***START A CHAT AND ASK FOR A PIQ REVIEW OR STATUS</v>
+        <v>START A CHAT AND ASK FOR A PIQ REVIEW OR STATUS</v>
       </c>
       <c r="C395" s="6">
         <f>IFERROR(IF(INDEX([4]US!$C$2:$C$23,MATCH($D395,[4]US!$D$2:$D$23,0))="","",INDEX([4]US!$C$2:$C$23,MATCH($D395,[4]US!$D$2:$D$23,0))),"")</f>
@@ -64884,11 +64887,11 @@
     <row r="405" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A405" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]US!$A$2:$A$23,MATCH($D405,[4]US!$D$2:$D$23,0))="","",INDEX([4]US!$A$2:$A$23,MATCH($D405,[4]US!$D$2:$D$23,0))),"")</f>
-        <v>Pending</v>
+        <v>Under Review</v>
       </c>
       <c r="B405" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]US!$B$2:$B$23,MATCH($D405,[4]US!$D$2:$D$23,0))="","",INDEX([4]US!$B$2:$B$23,MATCH($D405,[4]US!$D$2:$D$23,0))),"")</f>
-        <v>***secondary - check cob on noridian, if nothing there, check with April - 1A95CU0TY97</v>
+        <v>secondary - check cob on noridian, if nothing there, check with April - 1A95CU0TY97</v>
       </c>
       <c r="C405" s="6">
         <f>IFERROR(IF(INDEX([4]US!$C$2:$C$23,MATCH($D405,[4]US!$D$2:$D$23,0))="","",INDEX([4]US!$C$2:$C$23,MATCH($D405,[4]US!$D$2:$D$23,0))),"")</f>
@@ -65513,11 +65516,11 @@
     <row r="410" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A410" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]US!$A$2:$A$23,MATCH($D410,[4]US!$D$2:$D$23,0))="","",INDEX([4]US!$A$2:$A$23,MATCH($D410,[4]US!$D$2:$D$23,0))),"")</f>
-        <v>Denied</v>
+        <v>Under Review</v>
       </c>
       <c r="B410" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]US!$B$2:$B$23,MATCH($D410,[4]US!$D$2:$D$23,0))="","",INDEX([4]US!$B$2:$B$23,MATCH($D410,[4]US!$D$2:$D$23,0))),"")</f>
-        <v>***Send pending msm to Bri</v>
+        <v>Send pending msm to Bri</v>
       </c>
       <c r="C410" s="6">
         <f>IFERROR(IF(INDEX([4]US!$C$2:$C$23,MATCH($D410,[4]US!$D$2:$D$23,0))="","",INDEX([4]US!$C$2:$C$23,MATCH($D410,[4]US!$D$2:$D$23,0))),"")</f>
@@ -65752,11 +65755,11 @@
     <row r="412" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A412" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]DME!$A$2:$A$35,MATCH($D412,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$A$2:$A$35,MATCH($D412,[5]DME!$D$2:$D$35,0))),"")</f>
-        <v>Pending</v>
+        <v>Under Review</v>
       </c>
       <c r="B412" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]DME!$B$2:$B$35,MATCH($D412,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$B$2:$B$35,MATCH($D412,[5]DME!$D$2:$D$35,0))),"")</f>
-        <v>***Still processing - ins received claim on 07/20/2026</v>
+        <v>Still processing - ins received claim on 07/20/2026</v>
       </c>
       <c r="C412" s="6" t="str">
         <f>IFERROR(IF(INDEX([5]DME!$C$2:$C$35,MATCH($D412,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$C$2:$C$35,MATCH($D412,[5]DME!$D$2:$D$35,0))),"")</f>
@@ -66621,11 +66624,11 @@
     <row r="419" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A419" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]ORTHO!$A$2:$A$24,MATCH($D419,[5]ORTHO!$D$2:$D$24,0))="","",INDEX([5]ORTHO!$A$2:$A$24,MATCH($D419,[5]ORTHO!$D$2:$D$24,0))),"")</f>
-        <v>Denied</v>
+        <v>Under Review</v>
       </c>
       <c r="B419" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]ORTHO!$B$2:$B$24,MATCH($D419,[5]ORTHO!$D$2:$D$24,0))="","",INDEX([5]ORTHO!$B$2:$B$24,MATCH($D419,[5]ORTHO!$D$2:$D$24,0))),"")</f>
-        <v xml:space="preserve">***Expecting ins reply - DND as medical necessity - Jess sent MR </v>
+        <v xml:space="preserve">Expecting ins reply - DND as medical necessity - Jess sent MR </v>
       </c>
       <c r="C419" s="6">
         <f>IFERROR(IF(INDEX([5]ORTHO!$C$2:$C$24,MATCH($D419,[5]ORTHO!$D$2:$D$24,0))="","",INDEX([5]ORTHO!$C$2:$C$24,MATCH($D419,[5]ORTHO!$D$2:$D$24,0))),"")</f>
@@ -67619,11 +67622,11 @@
     <row r="427" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A427" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]DME!$A$2:$A$35,MATCH($D427,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$A$2:$A$35,MATCH($D427,[5]DME!$D$2:$D$35,0))),"")</f>
-        <v>Denied</v>
+        <v>Under Review</v>
       </c>
       <c r="B427" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]DME!$B$2:$B$35,MATCH($D427,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$B$2:$B$35,MATCH($D427,[5]DME!$D$2:$D$35,0))),"")</f>
-        <v>***Call PT for COB update needed by ins - Rep said the patient will need to update their Coordination of Benefits (COB) information with their insurance carrier. Once the COB has been updated, the claim can be reprocessed for review and adjudication. On yearly basis patient needs to update the COB.</v>
+        <v>Call PT for COB update needed by ins - Rep said the patient will need to update their Coordination of Benefits (COB) information with their insurance carrier. Once the COB has been updated, the claim can be reprocessed for review and adjudication. On yearly basis patient needs to update the COB.</v>
       </c>
       <c r="C427" s="6">
         <f>IFERROR(IF(INDEX([5]DME!$C$2:$C$35,MATCH($D427,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$C$2:$C$35,MATCH($D427,[5]DME!$D$2:$D$35,0))),"")</f>
@@ -69400,11 +69403,11 @@
     <row r="442" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A442" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]GAE!$A$2:$A$4,MATCH($D442,[2]GAE!$D$2:$D$4,0))="","",INDEX([2]GAE!$A$2:$A$4,MATCH($D442,[2]GAE!$D$2:$D$4,0))),"")</f>
-        <v>Denied</v>
+        <v>Under Review</v>
       </c>
       <c r="B442" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]GAE!$B$2:$B$4,MATCH($D442,[2]GAE!$D$2:$D$4,0))="","",INDEX([2]GAE!$B$2:$B$4,MATCH($D442,[2]GAE!$D$2:$D$4,0))),"")</f>
-        <v>***Checking tax code on UMR records - I'm expecting a response by email</v>
+        <v>Checking tax code on UMR records - I'm expecting a response by email</v>
       </c>
       <c r="C442" s="6">
         <f>IFERROR(IF(INDEX([2]GAE!$C$2:$C$4,MATCH($D442,[2]GAE!$D$2:$D$4,0))="","",INDEX([2]GAE!$C$2:$C$4,MATCH($D442,[2]GAE!$D$2:$D$4,0))),"")</f>
@@ -69966,11 +69969,11 @@
     <row r="447" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A447" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]ORTHO!$A$2:$A$21,MATCH($D447,[4]ORTHO!$D$2:$D$21,0))="","",INDEX([4]ORTHO!$A$2:$A$21,MATCH($D447,[4]ORTHO!$D$2:$D$21,0))),"")</f>
-        <v/>
+        <v>Under Review</v>
       </c>
       <c r="B447" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]ORTHO!$B$2:$B$21,MATCH($D447,[4]ORTHO!$D$2:$D$21,0))="","",INDEX([4]ORTHO!$B$2:$B$21,MATCH($D447,[4]ORTHO!$D$2:$D$21,0))),"")</f>
-        <v xml:space="preserve">***trying to get access to EOB with imperial </v>
+        <v xml:space="preserve">trying to get access to EOB with imperial </v>
       </c>
       <c r="C447" s="6" t="str">
         <f>IFERROR(IF(INDEX([4]ORTHO!$C$2:$C$21,MATCH($D447,[4]ORTHO!$D$2:$D$21,0))="","",INDEX([4]ORTHO!$C$2:$C$21,MATCH($D447,[4]ORTHO!$D$2:$D$21,0))),"")</f>
@@ -70075,11 +70078,11 @@
     <row r="448" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A448" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]BH!$A$2:$A$12,MATCH($D448,[4]BH!$D$2:$D$12,0))="","",INDEX([4]BH!$A$2:$A$12,MATCH($D448,[4]BH!$D$2:$D$12,0))),"")</f>
-        <v/>
+        <v>Under Review</v>
       </c>
       <c r="B448" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]BH!$B$2:$B$12,MATCH($D448,[4]BH!$D$2:$D$12,0))="","",INDEX([4]BH!$B$2:$B$12,MATCH($D448,[4]BH!$D$2:$D$12,0))),"")</f>
-        <v>***Waiting for account to get activated again</v>
+        <v>Waiting for account to get activated again</v>
       </c>
       <c r="C448" s="6" t="str">
         <f>IFERROR(IF(INDEX([4]BH!$C$2:$C$12,MATCH($D448,[4]BH!$D$2:$D$12,0))="","",INDEX([4]BH!$C$2:$C$12,MATCH($D448,[4]BH!$D$2:$D$12,0))),"")</f>
@@ -70176,11 +70179,11 @@
     <row r="449" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A449" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]ORTHO!$A$2:$A$21,MATCH($D449,[4]ORTHO!$D$2:$D$21,0))="","",INDEX([4]ORTHO!$A$2:$A$21,MATCH($D449,[4]ORTHO!$D$2:$D$21,0))),"")</f>
-        <v/>
+        <v>Under Review</v>
       </c>
       <c r="B449" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]ORTHO!$B$2:$B$21,MATCH($D449,[4]ORTHO!$D$2:$D$21,0))="","",INDEX([4]ORTHO!$B$2:$B$21,MATCH($D449,[4]ORTHO!$D$2:$D$21,0))),"")</f>
-        <v>***no access</v>
+        <v>no access</v>
       </c>
       <c r="C449" s="6" t="str">
         <f>IFERROR(IF(INDEX([4]ORTHO!$C$2:$C$21,MATCH($D449,[4]ORTHO!$D$2:$D$21,0))="","",INDEX([4]ORTHO!$C$2:$C$21,MATCH($D449,[4]ORTHO!$D$2:$D$21,0))),"")</f>
@@ -70396,11 +70399,11 @@
     <row r="451" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A451" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$A$2:$A$34,MATCH($D451,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$A$2:$A$34,MATCH($D451,[4]DME!$D$2:$D$34,0))),"")</f>
-        <v/>
+        <v>Under Review</v>
       </c>
       <c r="B451" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$B$2:$B$34,MATCH($D451,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$B$2:$B$34,MATCH($D451,[4]DME!$D$2:$D$34,0))),"")</f>
-        <v>***Waiting for account to get activated again</v>
+        <v>Waiting for account to get activated again</v>
       </c>
       <c r="C451" s="6" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$C$2:$C$34,MATCH($D451,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$C$2:$C$34,MATCH($D451,[4]DME!$D$2:$D$34,0))),"")</f>
@@ -70503,11 +70506,11 @@
     <row r="452" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A452" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$A$2:$A$34,MATCH($D452,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$A$2:$A$34,MATCH($D452,[4]DME!$D$2:$D$34,0))),"")</f>
-        <v/>
+        <v>Under Review</v>
       </c>
       <c r="B452" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$B$2:$B$34,MATCH($D452,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$B$2:$B$34,MATCH($D452,[4]DME!$D$2:$D$34,0))),"")</f>
-        <v>***Waiting for account to get activated again</v>
+        <v>Waiting for account to get activated again</v>
       </c>
       <c r="C452" s="6" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$C$2:$C$34,MATCH($D452,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$C$2:$C$34,MATCH($D452,[4]DME!$D$2:$D$34,0))),"")</f>
@@ -70606,11 +70609,11 @@
     <row r="453" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A453" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]US!$A$2:$A$23,MATCH($D453,[4]US!$D$2:$D$23,0))="","",INDEX([4]US!$A$2:$A$23,MATCH($D453,[4]US!$D$2:$D$23,0))),"")</f>
-        <v>Denied</v>
+        <v>Under Review</v>
       </c>
       <c r="B453" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]US!$B$2:$B$23,MATCH($D453,[4]US!$D$2:$D$23,0))="","",INDEX([4]US!$B$2:$B$23,MATCH($D453,[4]US!$D$2:$D$23,0))),"")</f>
-        <v xml:space="preserve">***I need to ask Juan for MR </v>
+        <v xml:space="preserve">Waiting for Bri's reply - Juan sent MR to me </v>
       </c>
       <c r="C453" s="6">
         <f>IFERROR(IF(INDEX([4]US!$C$2:$C$23,MATCH($D453,[4]US!$D$2:$D$23,0))="","",INDEX([4]US!$C$2:$C$23,MATCH($D453,[4]US!$D$2:$D$23,0))),"")</f>
@@ -70720,11 +70723,11 @@
     <row r="454" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A454" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]BH!$A$2:$A$12,MATCH($D454,[4]BH!$D$2:$D$12,0))="","",INDEX([4]BH!$A$2:$A$12,MATCH($D454,[4]BH!$D$2:$D$12,0))),"")</f>
-        <v/>
+        <v>Under Review</v>
       </c>
       <c r="B454" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]BH!$B$2:$B$12,MATCH($D454,[4]BH!$D$2:$D$12,0))="","",INDEX([4]BH!$B$2:$B$12,MATCH($D454,[4]BH!$D$2:$D$12,0))),"")</f>
-        <v>***Waiting for account to get activated again</v>
+        <v>Waiting for account to get activated again</v>
       </c>
       <c r="C454" s="6" t="str">
         <f>IFERROR(IF(INDEX([4]BH!$C$2:$C$12,MATCH($D454,[4]BH!$D$2:$D$12,0))="","",INDEX([4]BH!$C$2:$C$12,MATCH($D454,[4]BH!$D$2:$D$12,0))),"")</f>
@@ -71358,11 +71361,11 @@
     <row r="460" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A460" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]BH!$A$2:$A$33,MATCH($D460,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$A$2:$A$33,MATCH($D460,[5]BH!$D$2:$D$33,0))),"")</f>
-        <v>Received</v>
+        <v>Under Review</v>
       </c>
       <c r="B460" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]BH!$B$2:$B$33,MATCH($D460,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$B$2:$B$33,MATCH($D460,[5]BH!$D$2:$D$33,0))),"")</f>
-        <v>***Waiting for account to get activated again</v>
+        <v>Waiting for account to get activated again</v>
       </c>
       <c r="C460" s="6" t="str">
         <f>IFERROR(IF(INDEX([5]BH!$C$2:$C$33,MATCH($D460,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$C$2:$C$33,MATCH($D460,[5]BH!$D$2:$D$33,0))),"")</f>
@@ -71459,11 +71462,11 @@
     <row r="461" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A461" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]GAE!$A$2:$A$7,MATCH($D461,[5]GAE!$D$2:$D$7,0))="","",INDEX([5]GAE!$A$2:$A$7,MATCH($D461,[5]GAE!$D$2:$D$7,0))),"")</f>
-        <v>Received</v>
+        <v>Under Review</v>
       </c>
       <c r="B461" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]GAE!$B$2:$B$7,MATCH($D461,[5]GAE!$D$2:$D$7,0))="","",INDEX([5]GAE!$B$2:$B$7,MATCH($D461,[5]GAE!$D$2:$D$7,0))),"")</f>
-        <v>***Waiting for account to get activated again</v>
+        <v>Waiting for account to get activated again</v>
       </c>
       <c r="C461" s="6" t="str">
         <f>IFERROR(IF(INDEX([5]GAE!$C$2:$C$7,MATCH($D461,[5]GAE!$D$2:$D$7,0))="","",INDEX([5]GAE!$C$2:$C$7,MATCH($D461,[5]GAE!$D$2:$D$7,0))),"")</f>
@@ -71982,11 +71985,11 @@
     <row r="466" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A466" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]BH!$A$2:$A$33,MATCH($D466,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$A$2:$A$33,MATCH($D466,[5]BH!$D$2:$D$33,0))),"")</f>
-        <v>Received</v>
+        <v>Under Review</v>
       </c>
       <c r="B466" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]BH!$B$2:$B$33,MATCH($D466,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$B$2:$B$33,MATCH($D466,[5]BH!$D$2:$D$33,0))),"")</f>
-        <v>***Waiting for account to get activated again</v>
+        <v>Waiting for account to get activated again</v>
       </c>
       <c r="C466" s="6" t="str">
         <f>IFERROR(IF(INDEX([5]BH!$C$2:$C$33,MATCH($D466,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$C$2:$C$33,MATCH($D466,[5]BH!$D$2:$D$33,0))),"")</f>
@@ -72409,11 +72412,11 @@
     <row r="470" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A470" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D470,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D470,[6]DME!$D$2:$D$52,0))),"")</f>
-        <v/>
+        <v>Under Review</v>
       </c>
       <c r="B470" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$B$2:$B$52,MATCH($D470,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$B$2:$B$52,MATCH($D470,[6]DME!$D$2:$D$52,0))),"")</f>
-        <v>***Waiting for account to get activated again</v>
+        <v>Waiting for account to get activated again</v>
       </c>
       <c r="C470" s="6" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$C$2:$C$52,MATCH($D470,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$C$2:$C$52,MATCH($D470,[6]DME!$D$2:$D$52,0))),"")</f>
@@ -72720,11 +72723,11 @@
     <row r="473" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A473" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]BH!$A$2:$A$82,MATCH($D473,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$A$2:$A$82,MATCH($D473,[6]BH!$D$2:$D$82,0))),"")</f>
-        <v/>
+        <v>Under Review</v>
       </c>
       <c r="B473" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]BH!$B$2:$B$82,MATCH($D473,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$B$2:$B$82,MATCH($D473,[6]BH!$D$2:$D$82,0))),"")</f>
-        <v>***Waiting for account to get activated again</v>
+        <v>Waiting for account to get activated again</v>
       </c>
       <c r="C473" s="6" t="str">
         <f>IFERROR(IF(INDEX([6]BH!$C$2:$C$82,MATCH($D473,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$C$2:$C$82,MATCH($D473,[6]BH!$D$2:$D$82,0))),"")</f>
@@ -73346,11 +73349,11 @@
     <row r="479" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A479" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]ORTHO!$A$2:$A$39,MATCH($D479,[6]ORTHO!$D$2:$D$39,0))="","",INDEX([6]ORTHO!$A$2:$A$39,MATCH($D479,[6]ORTHO!$D$2:$D$39,0))),"")</f>
-        <v/>
+        <v>Under Review</v>
       </c>
       <c r="B479" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]ORTHO!$B$2:$B$39,MATCH($D479,[6]ORTHO!$D$2:$D$39,0))="","",INDEX([6]ORTHO!$B$2:$B$39,MATCH($D479,[6]ORTHO!$D$2:$D$39,0))),"")</f>
-        <v>***Waiting for account to get activated again</v>
+        <v>Waiting for account to get activated again</v>
       </c>
       <c r="C479" s="6" t="str">
         <f>IFERROR(IF(INDEX([6]ORTHO!$C$2:$C$39,MATCH($D479,[6]ORTHO!$D$2:$D$39,0))="","",INDEX([6]ORTHO!$C$2:$C$39,MATCH($D479,[6]ORTHO!$D$2:$D$39,0))),"")</f>
@@ -73453,11 +73456,11 @@
     <row r="480" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A480" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D480,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D480,[6]DME!$D$2:$D$52,0))),"")</f>
-        <v/>
+        <v>Under Review</v>
       </c>
       <c r="B480" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$B$2:$B$52,MATCH($D480,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$B$2:$B$52,MATCH($D480,[6]DME!$D$2:$D$52,0))),"")</f>
-        <v>***Waiting for account to get activated again</v>
+        <v>Waiting for account to get activated again</v>
       </c>
       <c r="C480" s="6" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$C$2:$C$52,MATCH($D480,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$C$2:$C$52,MATCH($D480,[6]DME!$D$2:$D$52,0))),"")</f>

--- a/Specialty Claims 2026-S1/ALL Claims 2026-S1 - Master.xlsx
+++ b/Specialty Claims 2026-S1/ALL Claims 2026-S1 - Master.xlsx
@@ -282,7 +282,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22562" uniqueCount="1761">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22564" uniqueCount="1762">
   <si>
     <t>ALL Claims 2026-S1 - Master</t>
   </si>
@@ -5565,6 +5565,9 @@
   </si>
   <si>
     <t xml:space="preserve">Statuses currently in use: Denied, Finalized, PAID, Pending, Received, Rejected, Under Review.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Statuses currently in use: Denied, Finalized, Not found, PAID, Pending, Received, Rejected, Under Review.</t>
   </si>
 </sst>
 </file>
@@ -14811,7 +14814,7 @@
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
     </row>
   </sheetData>
@@ -44923,7 +44926,7 @@
     <row r="243" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A243" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]ORTHO!$A$2:$A$24,MATCH($D243,[5]ORTHO!$D$2:$D$24,0))="","",INDEX([5]ORTHO!$A$2:$A$24,MATCH($D243,[5]ORTHO!$D$2:$D$24,0))),"")</f>
-        <v>Pendiing</v>
+        <v>Pending</v>
       </c>
       <c r="B243" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]ORTHO!$B$2:$B$24,MATCH($D243,[5]ORTHO!$D$2:$D$24,0))="","",INDEX([5]ORTHO!$B$2:$B$24,MATCH($D243,[5]ORTHO!$D$2:$D$24,0))),"")</f>
@@ -57622,7 +57625,7 @@
     <row r="346" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A346" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]US!$A$2:$A$15,MATCH($D346,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$A$2:$A$15,MATCH($D346,[2]US!$D$2:$D$15,0))),"")</f>
-        <v>No found</v>
+        <v>Not found</v>
       </c>
       <c r="B346" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]US!$B$2:$B$15,MATCH($D346,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$B$2:$B$15,MATCH($D346,[2]US!$D$2:$D$15,0))),"")</f>

--- a/Specialty Claims 2026-S1/ALL Claims 2026-S1 - Master.xlsx
+++ b/Specialty Claims 2026-S1/ALL Claims 2026-S1 - Master.xlsx
@@ -282,7 +282,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22564" uniqueCount="1762">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22671" uniqueCount="1762">
   <si>
     <t>ALL Claims 2026-S1 - Master</t>
   </si>
@@ -16012,8 +16012,8 @@
         <v>-33</v>
       </c>
       <c r="N10" s="11">
-        <f ca="1">IF($C10="","",$C10+60-TODAY())</f>
-        <v>-38</v>
+        <f ca="1">IF($C10="","",$C10+540-TODAY())</f>
+        <v>442</v>
       </c>
       <c r="O10" s="9">
         <v>46250</v>
@@ -16031,7 +16031,7 @@
         <v>105</v>
       </c>
       <c r="T10" s="8" t="s">
-        <v>151</v>
+        <v>1741</v>
       </c>
       <c r="U10" s="8" t="s">
         <v>75</v>
@@ -19345,8 +19345,8 @@
         <v>-19</v>
       </c>
       <c r="M37" s="11">
-        <f ca="1">IF($C37="","",$C37+365-TODAY())</f>
-        <v>285</v>
+        <f ca="1">IF($F37="","",$F37+90-TODAY())</f>
+        <v>-19</v>
       </c>
       <c r="N37" s="11">
         <f ca="1">IF($C37="","",$C37+365-TODAY())</f>
@@ -19362,10 +19362,10 @@
         <v>298</v>
       </c>
       <c r="R37" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S37" s="8" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="T37" s="8" t="s">
         <v>90</v>
@@ -20961,8 +20961,8 @@
         <v>-12</v>
       </c>
       <c r="M50" s="11">
-        <f ca="1">IF($C50="","",$C50+365-TODAY())</f>
-        <v>279</v>
+        <f ca="1">IF($F50="","",$F50+90-TODAY())</f>
+        <v>-12</v>
       </c>
       <c r="N50" s="11">
         <f ca="1">IF($C50="","",$C50+365-TODAY())</f>
@@ -20978,10 +20978,10 @@
         <v>298</v>
       </c>
       <c r="R50" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S50" s="8" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="T50" s="8" t="s">
         <v>90</v>
@@ -21092,8 +21092,8 @@
         <v>-12</v>
       </c>
       <c r="N51" s="11">
-        <f ca="1">IF($C51="","",$C51+60-TODAY())</f>
-        <v>13</v>
+        <f ca="1">IF($C51="","",$C51+540-TODAY())</f>
+        <v>493</v>
       </c>
       <c r="O51" s="9">
         <v>46271</v>
@@ -21111,7 +21111,7 @@
         <v>105</v>
       </c>
       <c r="T51" s="8" t="s">
-        <v>151</v>
+        <v>1741</v>
       </c>
       <c r="U51" s="8" t="s">
         <v>75</v>
@@ -22225,8 +22225,8 @@
         <v>-10</v>
       </c>
       <c r="M60" s="11">
-        <f ca="1">IF($C60="","",$C60+365-TODAY())</f>
-        <v>286</v>
+        <f ca="1">IF($F60="","",$F60+90-TODAY())</f>
+        <v>-10</v>
       </c>
       <c r="N60" s="11">
         <f ca="1">IF($C60="","",$C60+365-TODAY())</f>
@@ -22242,10 +22242,10 @@
         <v>298</v>
       </c>
       <c r="R60" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S60" s="8" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="T60" s="8" t="s">
         <v>90</v>
@@ -22346,8 +22346,8 @@
         <v>-9</v>
       </c>
       <c r="M61" s="11">
-        <f ca="1">IF($C61="","",$C61+365-TODAY())</f>
-        <v>279</v>
+        <f ca="1">IF($F61="","",$F61+90-TODAY())</f>
+        <v>-9</v>
       </c>
       <c r="N61" s="11">
         <f ca="1">IF($C61="","",$C61+365-TODAY())</f>
@@ -22363,10 +22363,10 @@
         <v>298</v>
       </c>
       <c r="R61" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S61" s="8" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="T61" s="8" t="s">
         <v>90</v>
@@ -22469,8 +22469,8 @@
         <v>-9</v>
       </c>
       <c r="M62" s="11">
-        <f ca="1">IF($C62="","",$C62+365-TODAY())</f>
-        <v>278</v>
+        <f ca="1">IF($F62="","",$F62+90-TODAY())</f>
+        <v>-9</v>
       </c>
       <c r="N62" s="11">
         <f ca="1">IF($C62="","",$C62+365-TODAY())</f>
@@ -22486,10 +22486,10 @@
         <v>298</v>
       </c>
       <c r="R62" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S62" s="8" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="T62" s="8" t="s">
         <v>90</v>
@@ -22715,8 +22715,8 @@
         <v>-8</v>
       </c>
       <c r="M64" s="11">
-        <f ca="1">IF($C64="","",$C64+365-TODAY())</f>
-        <v>286</v>
+        <f ca="1">IF($F64="","",$F64+90-TODAY())</f>
+        <v>-8</v>
       </c>
       <c r="N64" s="11">
         <f ca="1">IF($C64="","",$C64+365-TODAY())</f>
@@ -22732,10 +22732,10 @@
         <v>298</v>
       </c>
       <c r="R64" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S64" s="8" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="T64" s="8" t="s">
         <v>90</v>
@@ -24060,8 +24060,8 @@
         <v>-2</v>
       </c>
       <c r="M75" s="11">
-        <f ca="1">IF($C75="","",$C75+365-TODAY())</f>
-        <v>285</v>
+        <f ca="1">IF($F75="","",$F75+90-TODAY())</f>
+        <v>-2</v>
       </c>
       <c r="N75" s="11">
         <f ca="1">IF($C75="","",$C75+365-TODAY())</f>
@@ -24077,10 +24077,10 @@
         <v>298</v>
       </c>
       <c r="R75" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S75" s="8" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="T75" s="8" t="s">
         <v>90</v>
@@ -24427,8 +24427,8 @@
         <v>2</v>
       </c>
       <c r="M78" s="11">
-        <f ca="1">IF($C78="","",$C78+365-TODAY())</f>
-        <v>320</v>
+        <f ca="1">IF($F78="","",$F78+90-TODAY())</f>
+        <v>2</v>
       </c>
       <c r="N78" s="11">
         <f ca="1">IF($C78="","",$C78+365-TODAY())</f>
@@ -24444,10 +24444,10 @@
         <v>298</v>
       </c>
       <c r="R78" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S78" s="8" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="T78" s="8" t="s">
         <v>90</v>
@@ -24921,8 +24921,8 @@
         <v>2</v>
       </c>
       <c r="M82" s="11">
-        <f ca="1">IF($C82="","",$C82+365-TODAY())</f>
-        <v>292</v>
+        <f ca="1">IF($F82="","",$F82+90-TODAY())</f>
+        <v>2</v>
       </c>
       <c r="N82" s="11">
         <f ca="1">IF($C82="","",$C82+365-TODAY())</f>
@@ -24938,10 +24938,10 @@
         <v>298</v>
       </c>
       <c r="R82" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S82" s="8" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="T82" s="8" t="s">
         <v>90</v>
@@ -25177,8 +25177,8 @@
         <v>2</v>
       </c>
       <c r="N84" s="11">
-        <f ca="1">IF($C84="","",$C84+60-TODAY())</f>
-        <v>17</v>
+        <f ca="1">IF($C84="","",$C84+540-TODAY())</f>
+        <v>497</v>
       </c>
       <c r="O84" s="9">
         <v>46285</v>
@@ -25196,7 +25196,7 @@
         <v>105</v>
       </c>
       <c r="T84" s="8" t="s">
-        <v>151</v>
+        <v>1741</v>
       </c>
       <c r="U84" s="8" t="s">
         <v>75</v>
@@ -26290,8 +26290,8 @@
         <v>5</v>
       </c>
       <c r="M93" s="11">
-        <f ca="1">IF($C93="","",$C93+365-TODAY())</f>
-        <v>325</v>
+        <f ca="1">IF($F93="","",$F93+90-TODAY())</f>
+        <v>5</v>
       </c>
       <c r="N93" s="11">
         <f ca="1">IF($C93="","",$C93+365-TODAY())</f>
@@ -26307,10 +26307,10 @@
         <v>298</v>
       </c>
       <c r="R93" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S93" s="8" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="T93" s="8" t="s">
         <v>90</v>
@@ -26907,8 +26907,8 @@
         <v>9</v>
       </c>
       <c r="M98" s="11">
-        <f ca="1">IF($C98="","",$C98+365-TODAY())</f>
-        <v>292</v>
+        <f ca="1">IF($F98="","",$F98+90-TODAY())</f>
+        <v>9</v>
       </c>
       <c r="N98" s="11">
         <f ca="1">IF($C98="","",$C98+365-TODAY())</f>
@@ -26924,10 +26924,10 @@
         <v>298</v>
       </c>
       <c r="R98" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S98" s="8" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="T98" s="8" t="s">
         <v>90</v>
@@ -27032,8 +27032,8 @@
         <v>9</v>
       </c>
       <c r="N99" s="11">
-        <f ca="1">IF($C99="","",$C99+60-TODAY())</f>
-        <v>39</v>
+        <f ca="1">IF($C99="","",$C99+540-TODAY())</f>
+        <v>519</v>
       </c>
       <c r="O99" s="9">
         <v>46292</v>
@@ -27051,7 +27051,7 @@
         <v>105</v>
       </c>
       <c r="T99" s="8" t="s">
-        <v>151</v>
+        <v>1741</v>
       </c>
       <c r="U99" s="8" t="s">
         <v>75</v>
@@ -49158,8 +49158,8 @@
         <v>-166</v>
       </c>
       <c r="N277" s="11">
-        <f ca="1">IF($C277="","",$C277+60-TODAY())</f>
-        <v>-102</v>
+        <f ca="1">IF($C277="","",$C277+540-TODAY())</f>
+        <v>378</v>
       </c>
       <c r="O277" s="9">
         <v>46117</v>
@@ -49177,7 +49177,7 @@
         <v>105</v>
       </c>
       <c r="T277" s="8" t="s">
-        <v>151</v>
+        <v>1741</v>
       </c>
       <c r="U277" s="8" t="s">
         <v>75</v>
@@ -49287,8 +49287,8 @@
         <v>-166</v>
       </c>
       <c r="N278" s="11">
-        <f ca="1">IF($C278="","",$C278+60-TODAY())</f>
-        <v>-81</v>
+        <f ca="1">IF($C278="","",$C278+540-TODAY())</f>
+        <v>399</v>
       </c>
       <c r="O278" s="9">
         <v>46117</v>
@@ -49306,7 +49306,7 @@
         <v>105</v>
       </c>
       <c r="T278" s="8" t="s">
-        <v>151</v>
+        <v>1741</v>
       </c>
       <c r="U278" s="8" t="s">
         <v>75</v>
@@ -49533,8 +49533,8 @@
         <v>-164</v>
       </c>
       <c r="M280" s="11">
-        <f ca="1">IF($C280="","",$C280+365-TODAY())</f>
-        <v>145</v>
+        <f ca="1">IF($F280="","",$F280+90-TODAY())</f>
+        <v>-164</v>
       </c>
       <c r="N280" s="11">
         <f ca="1">IF($C280="","",$C280+365-TODAY())</f>
@@ -49550,10 +49550,10 @@
         <v>298</v>
       </c>
       <c r="R280" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S280" s="8" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="T280" s="8" t="s">
         <v>90</v>
@@ -49658,8 +49658,8 @@
         <v>-163</v>
       </c>
       <c r="N281" s="11">
-        <f ca="1">IF($C281="","",$C281+60-TODAY())</f>
-        <v>-24</v>
+        <f ca="1">IF($C281="","",$C281+540-TODAY())</f>
+        <v>456</v>
       </c>
       <c r="O281" s="9">
         <v>46120</v>
@@ -49677,7 +49677,7 @@
         <v>105</v>
       </c>
       <c r="T281" s="8" t="s">
-        <v>151</v>
+        <v>1741</v>
       </c>
       <c r="U281" s="8" t="s">
         <v>75</v>
@@ -50750,9 +50750,9 @@
         <f ca="1">IF($O290="","",$O290-TODAY())</f>
         <v>-157</v>
       </c>
-      <c r="M290" s="11" t="str">
-        <f ca="1">IF($C290="","",$C290+365-TODAY())</f>
-        <v/>
+      <c r="M290" s="11">
+        <f ca="1">IF($F290="","",$F290+90-TODAY())</f>
+        <v>-157</v>
       </c>
       <c r="N290" s="11" t="str">
         <f ca="1">IF($C290="","",$C290+365-TODAY())</f>
@@ -50768,10 +50768,10 @@
         <v>298</v>
       </c>
       <c r="R290" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S290" s="8" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="T290" s="8" t="s">
         <v>90</v>
@@ -51358,8 +51358,8 @@
         <v>-150</v>
       </c>
       <c r="M295" s="11">
-        <f ca="1">IF($C295="","",$C295+365-TODAY())</f>
-        <v>146</v>
+        <f ca="1">IF($F295="","",$F295+90-TODAY())</f>
+        <v>-150</v>
       </c>
       <c r="N295" s="11">
         <f ca="1">IF($C295="","",$C295+365-TODAY())</f>
@@ -51375,10 +51375,10 @@
         <v>298</v>
       </c>
       <c r="R295" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S295" s="8" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="T295" s="8" t="s">
         <v>90</v>
@@ -51604,8 +51604,8 @@
         <v>-149</v>
       </c>
       <c r="M297" s="11">
-        <f ca="1">IF($C297="","",$C297+365-TODAY())</f>
-        <v>176</v>
+        <f ca="1">IF($F297="","",$F297+90-TODAY())</f>
+        <v>-149</v>
       </c>
       <c r="N297" s="11">
         <f ca="1">IF($C297="","",$C297+365-TODAY())</f>
@@ -51621,10 +51621,10 @@
         <v>298</v>
       </c>
       <c r="R297" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S297" s="8" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="T297" s="8" t="s">
         <v>90</v>
@@ -51727,8 +51727,8 @@
         <v>-148</v>
       </c>
       <c r="M298" s="11">
-        <f ca="1">IF($C298="","",$C298+365-TODAY())</f>
-        <v>245</v>
+        <f ca="1">IF($F298="","",$F298+90-TODAY())</f>
+        <v>-148</v>
       </c>
       <c r="N298" s="11">
         <f ca="1">IF($C298="","",$C298+365-TODAY())</f>
@@ -51744,10 +51744,10 @@
         <v>298</v>
       </c>
       <c r="R298" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S298" s="8" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="T298" s="8" t="s">
         <v>90</v>
@@ -51852,8 +51852,8 @@
         <v>-148</v>
       </c>
       <c r="M299" s="11">
-        <f ca="1">IF($C299="","",$C299+365-TODAY())</f>
-        <v>134</v>
+        <f ca="1">IF($F299="","",$F299+90-TODAY())</f>
+        <v>-148</v>
       </c>
       <c r="N299" s="11">
         <f ca="1">IF($C299="","",$C299+365-TODAY())</f>
@@ -51869,10 +51869,10 @@
         <v>298</v>
       </c>
       <c r="R299" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S299" s="8" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="T299" s="8" t="s">
         <v>90</v>
@@ -52106,8 +52106,8 @@
         <v>-145</v>
       </c>
       <c r="N301" s="11">
-        <f ca="1">IF($C301="","",$C301+60-TODAY())</f>
-        <v>-112</v>
+        <f ca="1">IF($C301="","",$C301+540-TODAY())</f>
+        <v>368</v>
       </c>
       <c r="O301" s="9">
         <v>46138</v>
@@ -52125,7 +52125,7 @@
         <v>105</v>
       </c>
       <c r="T301" s="8" t="s">
-        <v>151</v>
+        <v>1741</v>
       </c>
       <c r="U301" s="8" t="s">
         <v>75</v>
@@ -52231,8 +52231,8 @@
         <v>-144</v>
       </c>
       <c r="M302" s="11">
-        <f ca="1">IF($C302="","",$C302+365-TODAY())</f>
-        <v>210</v>
+        <f ca="1">IF($F302="","",$F302+90-TODAY())</f>
+        <v>-144</v>
       </c>
       <c r="N302" s="11">
         <f ca="1">IF($C302="","",$C302+365-TODAY())</f>
@@ -52248,10 +52248,10 @@
         <v>298</v>
       </c>
       <c r="R302" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S302" s="8" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="T302" s="8" t="s">
         <v>90</v>
@@ -52475,8 +52475,8 @@
         <v>-142</v>
       </c>
       <c r="M304" s="11">
-        <f ca="1">IF($C304="","",$C304+365-TODAY())</f>
-        <v>148</v>
+        <f ca="1">IF($F304="","",$F304+90-TODAY())</f>
+        <v>-142</v>
       </c>
       <c r="N304" s="11">
         <f ca="1">IF($C304="","",$C304+365-TODAY())</f>
@@ -52492,10 +52492,10 @@
         <v>298</v>
       </c>
       <c r="R304" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S304" s="8" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="T304" s="8" t="s">
         <v>90</v>
@@ -52721,8 +52721,8 @@
         <v>-137</v>
       </c>
       <c r="M306" s="11">
-        <f ca="1">IF($C306="","",$C306+365-TODAY())</f>
-        <v>180</v>
+        <f ca="1">IF($F306="","",$F306+90-TODAY())</f>
+        <v>-137</v>
       </c>
       <c r="N306" s="11">
         <f ca="1">IF($C306="","",$C306+365-TODAY())</f>
@@ -52738,10 +52738,10 @@
         <v>298</v>
       </c>
       <c r="R306" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S306" s="8" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="T306" s="8" t="s">
         <v>90</v>
@@ -52975,8 +52975,8 @@
         <v>-134</v>
       </c>
       <c r="N308" s="11">
-        <f ca="1">IF($C308="","",$C308+60-TODAY())</f>
-        <v>-76</v>
+        <f ca="1">IF($C308="","",$C308+540-TODAY())</f>
+        <v>404</v>
       </c>
       <c r="O308" s="9">
         <v>46149</v>
@@ -52994,7 +52994,7 @@
         <v>105</v>
       </c>
       <c r="T308" s="8" t="s">
-        <v>151</v>
+        <v>1741</v>
       </c>
       <c r="U308" s="8" t="s">
         <v>75</v>
@@ -53092,8 +53092,8 @@
         <v>-131</v>
       </c>
       <c r="M309" s="11">
-        <f ca="1">IF($C309="","",$C309+365-TODAY())</f>
-        <v>230</v>
+        <f ca="1">IF($F309="","",$F309+90-TODAY())</f>
+        <v>-131</v>
       </c>
       <c r="N309" s="11">
         <f ca="1">IF($C309="","",$C309+365-TODAY())</f>
@@ -53109,10 +53109,10 @@
         <v>298</v>
       </c>
       <c r="R309" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S309" s="8" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="T309" s="8" t="s">
         <v>90</v>
@@ -53213,8 +53213,8 @@
         <v>-128</v>
       </c>
       <c r="M310" s="11">
-        <f ca="1">IF($C310="","",$C310+365-TODAY())</f>
-        <v>201</v>
+        <f ca="1">IF($F310="","",$F310+90-TODAY())</f>
+        <v>-128</v>
       </c>
       <c r="N310" s="11">
         <f ca="1">IF($C310="","",$C310+365-TODAY())</f>
@@ -53230,10 +53230,10 @@
         <v>298</v>
       </c>
       <c r="R310" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S310" s="8" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="T310" s="8" t="s">
         <v>90</v>
@@ -53707,8 +53707,8 @@
         <v>-124</v>
       </c>
       <c r="M314" s="11">
-        <f ca="1">IF($C314="","",$C314+365-TODAY())</f>
-        <v>236</v>
+        <f ca="1">IF($F314="","",$F314+90-TODAY())</f>
+        <v>-124</v>
       </c>
       <c r="N314" s="11">
         <f ca="1">IF($C314="","",$C314+365-TODAY())</f>
@@ -53724,10 +53724,10 @@
         <v>298</v>
       </c>
       <c r="R314" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S314" s="8" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="T314" s="8" t="s">
         <v>90</v>
@@ -53836,8 +53836,8 @@
         <v>-124</v>
       </c>
       <c r="M315" s="11">
-        <f ca="1">IF($C315="","",$C315+365-TODAY())</f>
-        <v>309</v>
+        <f ca="1">IF($F315="","",$F315+90-TODAY())</f>
+        <v>-124</v>
       </c>
       <c r="N315" s="11">
         <f ca="1">IF($C315="","",$C315+365-TODAY())</f>
@@ -53853,10 +53853,10 @@
         <v>298</v>
       </c>
       <c r="R315" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S315" s="8" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="T315" s="8" t="s">
         <v>90</v>
@@ -54082,8 +54082,8 @@
         <v>-122</v>
       </c>
       <c r="M317" s="11">
-        <f ca="1">IF($C317="","",$C317+365-TODAY())</f>
-        <v>183</v>
+        <f ca="1">IF($F317="","",$F317+90-TODAY())</f>
+        <v>-122</v>
       </c>
       <c r="N317" s="11">
         <f ca="1">IF($C317="","",$C317+365-TODAY())</f>
@@ -54099,10 +54099,10 @@
         <v>298</v>
       </c>
       <c r="R317" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S317" s="8" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="T317" s="8" t="s">
         <v>90</v>
@@ -54699,8 +54699,8 @@
         <v>-114</v>
       </c>
       <c r="M322" s="11">
-        <f ca="1">IF($C322="","",$C322+365-TODAY())</f>
-        <v>294</v>
+        <f ca="1">IF($F322="","",$F322+90-TODAY())</f>
+        <v>-114</v>
       </c>
       <c r="N322" s="11">
         <f ca="1">IF($C322="","",$C322+365-TODAY())</f>
@@ -54716,10 +54716,10 @@
         <v>298</v>
       </c>
       <c r="R322" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S322" s="8" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="T322" s="8" t="s">
         <v>90</v>
@@ -55332,8 +55332,8 @@
         <v>-108</v>
       </c>
       <c r="M327" s="11">
-        <f ca="1">IF($C327="","",$C327+365-TODAY())</f>
-        <v>216</v>
+        <f ca="1">IF($F327="","",$F327+90-TODAY())</f>
+        <v>-108</v>
       </c>
       <c r="N327" s="11">
         <f ca="1">IF($C327="","",$C327+365-TODAY())</f>
@@ -55349,10 +55349,10 @@
         <v>298</v>
       </c>
       <c r="R327" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S327" s="8" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="T327" s="8" t="s">
         <v>90</v>
@@ -55945,8 +55945,8 @@
         <v>-106</v>
       </c>
       <c r="N332" s="11">
-        <f ca="1">IF($C332="","",$C332+60-TODAY())</f>
-        <v>-126</v>
+        <f ca="1">IF($C332="","",$C332+540-TODAY())</f>
+        <v>354</v>
       </c>
       <c r="O332" s="9">
         <v>46177</v>
@@ -55964,7 +55964,7 @@
         <v>105</v>
       </c>
       <c r="T332" s="8" t="s">
-        <v>151</v>
+        <v>1741</v>
       </c>
       <c r="U332" s="8" t="s">
         <v>75</v>
@@ -56062,8 +56062,8 @@
         <v>-106</v>
       </c>
       <c r="M333" s="11">
-        <f ca="1">IF($C333="","",$C333+365-TODAY())</f>
-        <v>285</v>
+        <f ca="1">IF($F333="","",$F333+90-TODAY())</f>
+        <v>-106</v>
       </c>
       <c r="N333" s="11">
         <f ca="1">IF($C333="","",$C333+365-TODAY())</f>
@@ -56079,10 +56079,10 @@
         <v>298</v>
       </c>
       <c r="R333" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S333" s="8" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="T333" s="8" t="s">
         <v>90</v>
@@ -56433,8 +56433,8 @@
         <v>-100</v>
       </c>
       <c r="N336" s="11">
-        <f ca="1">IF($C336="","",$C336+60-TODAY())</f>
-        <v>-115</v>
+        <f ca="1">IF($C336="","",$C336+540-TODAY())</f>
+        <v>365</v>
       </c>
       <c r="O336" s="9">
         <v>46183</v>
@@ -56452,7 +56452,7 @@
         <v>105</v>
       </c>
       <c r="T336" s="8" t="s">
-        <v>151</v>
+        <v>1741</v>
       </c>
       <c r="U336" s="8" t="s">
         <v>75</v>
@@ -56558,8 +56558,8 @@
         <v>-100</v>
       </c>
       <c r="N337" s="11">
-        <f ca="1">IF($C337="","",$C337+60-TODAY())</f>
-        <v>-3</v>
+        <f ca="1">IF($C337="","",$C337+540-TODAY())</f>
+        <v>477</v>
       </c>
       <c r="O337" s="9">
         <v>46183</v>
@@ -56577,7 +56577,7 @@
         <v>105</v>
       </c>
       <c r="T337" s="8" t="s">
-        <v>151</v>
+        <v>1741</v>
       </c>
       <c r="U337" s="8" t="s">
         <v>75</v>
@@ -56923,8 +56923,8 @@
         <v>-96</v>
       </c>
       <c r="M340" s="11">
-        <f ca="1">IF($C340="","",$C340+365-TODAY())</f>
-        <v>217</v>
+        <f ca="1">IF($F340="","",$F340+90-TODAY())</f>
+        <v>-96</v>
       </c>
       <c r="N340" s="11">
         <f ca="1">IF($C340="","",$C340+365-TODAY())</f>
@@ -56940,10 +56940,10 @@
         <v>298</v>
       </c>
       <c r="R340" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S340" s="8" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="T340" s="8" t="s">
         <v>90</v>
@@ -57170,9 +57170,9 @@
         <f ca="1">IF($O342="","",$O342-TODAY())</f>
         <v>-95</v>
       </c>
-      <c r="M342" s="11" t="str">
-        <f ca="1">IF($C342="","",$C342+365-TODAY())</f>
-        <v/>
+      <c r="M342" s="11">
+        <f ca="1">IF($F342="","",$F342+90-TODAY())</f>
+        <v>-95</v>
       </c>
       <c r="N342" s="11" t="str">
         <f ca="1">IF($C342="","",$C342+365-TODAY())</f>
@@ -57188,10 +57188,10 @@
         <v>298</v>
       </c>
       <c r="R342" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S342" s="8" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="T342" s="8" t="s">
         <v>90</v>
@@ -57298,8 +57298,8 @@
         <v>-94</v>
       </c>
       <c r="N343" s="11">
-        <f ca="1">IF($C343="","",$C343+60-TODAY())</f>
-        <v>-3</v>
+        <f ca="1">IF($C343="","",$C343+540-TODAY())</f>
+        <v>477</v>
       </c>
       <c r="O343" s="9">
         <v>46189</v>
@@ -57317,7 +57317,7 @@
         <v>105</v>
       </c>
       <c r="T343" s="8" t="s">
-        <v>151</v>
+        <v>1741</v>
       </c>
       <c r="U343" s="8" t="s">
         <v>75</v>
@@ -57909,8 +57909,8 @@
         <v>-92</v>
       </c>
       <c r="M348" s="11">
-        <f ca="1">IF($C348="","",$C348+365-TODAY())</f>
-        <v>206</v>
+        <f ca="1">IF($F348="","",$F348+90-TODAY())</f>
+        <v>-92</v>
       </c>
       <c r="N348" s="11">
         <f ca="1">IF($C348="","",$C348+365-TODAY())</f>
@@ -57926,10 +57926,10 @@
         <v>298</v>
       </c>
       <c r="R348" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S348" s="8" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="T348" s="8" t="s">
         <v>90</v>
@@ -58405,8 +58405,8 @@
         <v>-87</v>
       </c>
       <c r="N352" s="11">
-        <f ca="1">IF($C352="","",$C352+60-TODAY())</f>
-        <v>-100</v>
+        <f ca="1">IF($C352="","",$C352+540-TODAY())</f>
+        <v>380</v>
       </c>
       <c r="O352" s="9">
         <v>46196</v>
@@ -58424,7 +58424,7 @@
         <v>105</v>
       </c>
       <c r="T352" s="8" t="s">
-        <v>151</v>
+        <v>1741</v>
       </c>
       <c r="U352" s="8" t="s">
         <v>75</v>
@@ -59145,8 +59145,8 @@
         <v>-80</v>
       </c>
       <c r="M358" s="11">
-        <f ca="1">IF($C358="","",$C358+365-TODAY())</f>
-        <v>244</v>
+        <f ca="1">IF($F358="","",$F358+90-TODAY())</f>
+        <v>-80</v>
       </c>
       <c r="N358" s="11">
         <f ca="1">IF($C358="","",$C358+365-TODAY())</f>
@@ -59162,10 +59162,10 @@
         <v>298</v>
       </c>
       <c r="R358" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S358" s="8" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="T358" s="8" t="s">
         <v>90</v>
@@ -59641,8 +59641,8 @@
         <v>-75</v>
       </c>
       <c r="N362" s="11">
-        <f ca="1">IF($C362="","",$C362+60-TODAY())</f>
-        <v>-58</v>
+        <f ca="1">IF($C362="","",$C362+540-TODAY())</f>
+        <v>422</v>
       </c>
       <c r="O362" s="9">
         <v>46208</v>
@@ -59660,7 +59660,7 @@
         <v>105</v>
       </c>
       <c r="T362" s="8" t="s">
-        <v>151</v>
+        <v>1741</v>
       </c>
       <c r="U362" s="8" t="s">
         <v>75</v>
@@ -60014,8 +60014,8 @@
         <v>-74</v>
       </c>
       <c r="M365" s="11">
-        <f ca="1">IF($C365="","",$C365+365-TODAY())</f>
-        <v>246</v>
+        <f ca="1">IF($F365="","",$F365+90-TODAY())</f>
+        <v>-74</v>
       </c>
       <c r="N365" s="11">
         <f ca="1">IF($C365="","",$C365+365-TODAY())</f>
@@ -60031,10 +60031,10 @@
         <v>298</v>
       </c>
       <c r="R365" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S365" s="8" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="T365" s="8" t="s">
         <v>90</v>
@@ -60978,8 +60978,8 @@
         <v>-68</v>
       </c>
       <c r="M373" s="11">
-        <f ca="1">IF($C373="","",$C373+365-TODAY())</f>
-        <v>223</v>
+        <f ca="1">IF($F373="","",$F373+90-TODAY())</f>
+        <v>-68</v>
       </c>
       <c r="N373" s="11">
         <f ca="1">IF($C373="","",$C373+365-TODAY())</f>
@@ -60995,10 +60995,10 @@
         <v>298</v>
       </c>
       <c r="R373" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S373" s="8" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="T373" s="8" t="s">
         <v>90</v>
@@ -61099,8 +61099,8 @@
         <v>-68</v>
       </c>
       <c r="M374" s="11">
-        <f ca="1">IF($C374="","",$C374+365-TODAY())</f>
-        <v>223</v>
+        <f ca="1">IF($F374="","",$F374+90-TODAY())</f>
+        <v>-68</v>
       </c>
       <c r="N374" s="11">
         <f ca="1">IF($C374="","",$C374+365-TODAY())</f>
@@ -61116,10 +61116,10 @@
         <v>298</v>
       </c>
       <c r="R374" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S374" s="8" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="T374" s="8" t="s">
         <v>90</v>
@@ -62704,8 +62704,8 @@
         <v>-61</v>
       </c>
       <c r="M387" s="11">
-        <f ca="1">IF($C387="","",$C387+365-TODAY())</f>
-        <v>239</v>
+        <f ca="1">IF($F387="","",$F387+90-TODAY())</f>
+        <v>-61</v>
       </c>
       <c r="N387" s="11">
         <f ca="1">IF($C387="","",$C387+365-TODAY())</f>
@@ -62721,10 +62721,10 @@
         <v>298</v>
       </c>
       <c r="R387" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S387" s="8" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="T387" s="8" t="s">
         <v>90</v>
@@ -62950,8 +62950,8 @@
         <v>-61</v>
       </c>
       <c r="M389" s="11">
-        <f ca="1">IF($C389="","",$C389+365-TODAY())</f>
-        <v>244</v>
+        <f ca="1">IF($F389="","",$F389+90-TODAY())</f>
+        <v>-61</v>
       </c>
       <c r="N389" s="11">
         <f ca="1">IF($C389="","",$C389+365-TODAY())</f>
@@ -62967,10 +62967,10 @@
         <v>298</v>
       </c>
       <c r="R389" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S389" s="8" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="T389" s="8" t="s">
         <v>90</v>
@@ -63331,8 +63331,8 @@
         <v>-58</v>
       </c>
       <c r="N392" s="11">
-        <f ca="1">IF($C392="","",$C392+60-TODAY())</f>
-        <v>-66</v>
+        <f ca="1">IF($C392="","",$C392+540-TODAY())</f>
+        <v>414</v>
       </c>
       <c r="O392" s="9">
         <v>46225</v>
@@ -63350,7 +63350,7 @@
         <v>105</v>
       </c>
       <c r="T392" s="8" t="s">
-        <v>151</v>
+        <v>1741</v>
       </c>
       <c r="U392" s="8" t="s">
         <v>75</v>
@@ -65303,8 +65303,8 @@
         <v>-51</v>
       </c>
       <c r="M408" s="11">
-        <f ca="1">IF($C408="","",$C408+365-TODAY())</f>
-        <v>244</v>
+        <f ca="1">IF($F408="","",$F408+90-TODAY())</f>
+        <v>-51</v>
       </c>
       <c r="N408" s="11">
         <f ca="1">IF($C408="","",$C408+365-TODAY())</f>
@@ -65320,10 +65320,10 @@
         <v>298</v>
       </c>
       <c r="R408" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S408" s="8" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="T408" s="8" t="s">
         <v>90</v>
@@ -66542,8 +66542,8 @@
         <v>-47</v>
       </c>
       <c r="M418" s="11">
-        <f ca="1">IF($C418="","",$C418+365-TODAY())</f>
-        <v>266</v>
+        <f ca="1">IF($F418="","",$F418+90-TODAY())</f>
+        <v>-47</v>
       </c>
       <c r="N418" s="11">
         <f ca="1">IF($C418="","",$C418+365-TODAY())</f>
@@ -66559,10 +66559,10 @@
         <v>298</v>
       </c>
       <c r="R418" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S418" s="8" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="T418" s="8" t="s">
         <v>90</v>
@@ -66667,8 +66667,8 @@
         <v>-45</v>
       </c>
       <c r="M419" s="11">
-        <f ca="1">IF($C419="","",$C419+365-TODAY())</f>
-        <v>279</v>
+        <f ca="1">IF($F419="","",$F419+90-TODAY())</f>
+        <v>-45</v>
       </c>
       <c r="N419" s="11">
         <f ca="1">IF($C419="","",$C419+365-TODAY())</f>
@@ -66684,10 +66684,10 @@
         <v>298</v>
       </c>
       <c r="R419" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S419" s="8" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="T419" s="8" t="s">
         <v>90</v>
@@ -67538,8 +67538,8 @@
         <v>-40</v>
       </c>
       <c r="N426" s="11">
-        <f ca="1">IF($C426="","",$C426+60-TODAY())</f>
-        <v>-27</v>
+        <f ca="1">IF($C426="","",$C426+540-TODAY())</f>
+        <v>453</v>
       </c>
       <c r="O426" s="9">
         <v>46243</v>
@@ -67557,7 +67557,7 @@
         <v>105</v>
       </c>
       <c r="T426" s="8" t="s">
-        <v>151</v>
+        <v>1741</v>
       </c>
       <c r="U426" s="8" t="s">
         <v>75</v>
@@ -67665,8 +67665,8 @@
         <v>-40</v>
       </c>
       <c r="M427" s="11">
-        <f ca="1">IF($C427="","",$C427+365-TODAY())</f>
-        <v>285</v>
+        <f ca="1">IF($F427="","",$F427+90-TODAY())</f>
+        <v>-40</v>
       </c>
       <c r="N427" s="11">
         <f ca="1">IF($C427="","",$C427+365-TODAY())</f>
@@ -67682,10 +67682,10 @@
         <v>298</v>
       </c>
       <c r="R427" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S427" s="8" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="T427" s="8" t="s">
         <v>90</v>
@@ -67792,8 +67792,8 @@
         <v>-39</v>
       </c>
       <c r="M428" s="11">
-        <f ca="1">IF($C428="","",$C428+365-TODAY())</f>
-        <v>298</v>
+        <f ca="1">IF($F428="","",$F428+90-TODAY())</f>
+        <v>-39</v>
       </c>
       <c r="N428" s="11">
         <f ca="1">IF($C428="","",$C428+365-TODAY())</f>
@@ -67809,10 +67809,10 @@
         <v>298</v>
       </c>
       <c r="R428" s="8" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="S428" s="8" t="s">
-        <v>75</v>
+        <v>105</v>
       </c>
       <c r="T428" s="8" t="s">
         <v>90</v>
@@ -68994,25 +68994,29 @@
         <f>IFERROR(IF(INDEX([3]ORTHO!$K$2:$K$11,MATCH($D438,[3]ORTHO!$D$2:$D$11,0))="","",INDEX([3]ORTHO!$K$2:$K$11,MATCH($D438,[3]ORTHO!$D$2:$D$11,0))),"")</f>
         <v>46195</v>
       </c>
-      <c r="L438" s="11" t="str">
+      <c r="L438" s="11">
         <f ca="1">IF($O438="","",$O438-TODAY())</f>
-        <v/>
+        <v>-135</v>
       </c>
       <c r="M438" s="11">
-        <f ca="1">IF($C438="","",$C438+180-TODAY())</f>
-        <v>39</v>
+        <f ca="1">IF($C438="","",$C438+365-TODAY())</f>
+        <v>224</v>
       </c>
       <c r="N438" s="11">
         <f ca="1">IF($C438="","",$C438+365-TODAY())</f>
         <v>224</v>
       </c>
-      <c r="O438" s="9"/>
-      <c r="P438" s="8"/>
+      <c r="O438" s="9">
+        <v>46148</v>
+      </c>
+      <c r="P438" s="8" t="s">
+        <v>88</v>
+      </c>
       <c r="Q438" s="8" t="s">
         <v>1607</v>
       </c>
       <c r="R438" s="8" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="S438" s="8" t="s">
         <v>75</v>
@@ -69678,25 +69682,29 @@
         <f>IFERROR(IF(INDEX([2]US!$K$2:$K$15,MATCH($D444,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$K$2:$K$15,MATCH($D444,[2]US!$D$2:$D$15,0))),"")</f>
         <v/>
       </c>
-      <c r="L444" s="11" t="str">
+      <c r="L444" s="11">
         <f ca="1">IF($O444="","",$O444-TODAY())</f>
-        <v/>
+        <v>-95</v>
       </c>
       <c r="M444" s="11" t="str">
-        <f ca="1">IF($C444="","",$C444+180-TODAY())</f>
+        <f ca="1">IF($C444="","",$C444+365-TODAY())</f>
         <v/>
       </c>
       <c r="N444" s="11" t="str">
         <f ca="1">IF($C444="","",$C444+365-TODAY())</f>
         <v/>
       </c>
-      <c r="O444" s="9"/>
-      <c r="P444" s="8"/>
+      <c r="O444" s="9">
+        <v>46188</v>
+      </c>
+      <c r="P444" s="8" t="s">
+        <v>88</v>
+      </c>
       <c r="Q444" s="8" t="s">
         <v>1607</v>
       </c>
       <c r="R444" s="8" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="S444" s="8" t="s">
         <v>75</v>
@@ -71278,25 +71286,29 @@
         <f>IFERROR(IF(INDEX([5]US!$K$2:$K$19,MATCH($D459,[5]US!$D$2:$D$19,0))="","",INDEX([5]US!$K$2:$K$19,MATCH($D459,[5]US!$D$2:$D$19,0))),"")</f>
         <v>46259</v>
       </c>
-      <c r="L459" s="11" t="str">
+      <c r="L459" s="11">
         <f ca="1">IF($O459="","",$O459-TODAY())</f>
-        <v/>
+        <v>-44</v>
       </c>
       <c r="M459" s="11">
-        <f ca="1">IF($C459="","",$C459+180-TODAY())</f>
-        <v>133</v>
+        <f ca="1">IF($C459="","",$C459+365-TODAY())</f>
+        <v>318</v>
       </c>
       <c r="N459" s="11">
         <f ca="1">IF($C459="","",$C459+365-TODAY())</f>
         <v>318</v>
       </c>
-      <c r="O459" s="9"/>
-      <c r="P459" s="8"/>
+      <c r="O459" s="9">
+        <v>46239</v>
+      </c>
+      <c r="P459" s="8" t="s">
+        <v>88</v>
+      </c>
       <c r="Q459" s="8" t="s">
         <v>1607</v>
       </c>
       <c r="R459" s="8" t="s">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="S459" s="8" t="s">
         <v>75</v>

--- a/Specialty Claims 2026-S1/ALL Claims 2026-S1 - Master.xlsx
+++ b/Specialty Claims 2026-S1/ALL Claims 2026-S1 - Master.xlsx
@@ -260,20 +260,6 @@
             <scheme val="minor"/>
           </rPr>
           <t>Whether the carrier counts the appeal window from the date of service or from the processed date.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AP1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000010000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color theme="1"/>
-            <rFont val="Calibri"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-          </rPr>
-          <t>The rows of the original 'Merged' sheet that were combined into this claim, so every claim traces back to the source. Informational only.</t>
         </r>
       </text>
     </comment>
@@ -14824,7 +14810,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AP483"/>
+  <dimension ref="A1:AO483"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -14860,10 +14846,10 @@
     <col min="38" max="38" width="20" customWidth="1"/>
     <col min="39" max="39" width="22" customWidth="1"/>
     <col min="40" max="40" width="24" customWidth="1"/>
-    <col min="41" max="42" width="14" customWidth="1"/>
+    <col min="41" max="41" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:41" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>26</v>
       </c>
@@ -14987,11 +14973,8 @@
       <c r="AO1" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="AP1" s="4" t="s">
-        <v>67</v>
-      </c>
     </row>
-    <row r="2" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]US!$A$2:$A$23,MATCH($D2,[4]US!$D$2:$D$23,0))="","",INDEX([4]US!$A$2:$A$23,MATCH($D2,[4]US!$D$2:$D$23,0))),"")</f>
         <v>Finalized</v>
@@ -15110,11 +15093,8 @@
       <c r="AO2" s="9">
         <v>46141</v>
       </c>
-      <c r="AP2" s="8" t="s">
-        <v>84</v>
-      </c>
     </row>
-    <row r="3" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]BH!$A$2:$A$33,MATCH($D3,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$A$2:$A$33,MATCH($D3,[5]BH!$D$2:$D$33,0))),"")</f>
         <v>Pending</v>
@@ -15229,11 +15209,8 @@
       <c r="AO3" s="9">
         <v>46180</v>
       </c>
-      <c r="AP3" s="8" t="s">
-        <v>96</v>
-      </c>
     </row>
-    <row r="4" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]BH!$A$2:$A$33,MATCH($D4,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$A$2:$A$33,MATCH($D4,[5]BH!$D$2:$D$33,0))),"")</f>
         <v>Pending</v>
@@ -15348,11 +15325,8 @@
       <c r="AO4" s="9">
         <v>46180</v>
       </c>
-      <c r="AP4" s="8" t="s">
-        <v>100</v>
-      </c>
     </row>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]ORTHO!$A$2:$A$24,MATCH($D5,[5]ORTHO!$D$2:$D$24,0))="","",INDEX([5]ORTHO!$A$2:$A$24,MATCH($D5,[5]ORTHO!$D$2:$D$24,0))),"")</f>
         <v>Denied</v>
@@ -15469,11 +15443,8 @@
       <c r="AO5" s="9">
         <v>46160</v>
       </c>
-      <c r="AP5" s="8" t="s">
-        <v>110</v>
-      </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]DME!$A$2:$A$35,MATCH($D6,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$A$2:$A$35,MATCH($D6,[5]DME!$D$2:$D$35,0))),"")</f>
         <v>Rejected</v>
@@ -15596,11 +15567,8 @@
       <c r="AO6" s="9">
         <v>46217</v>
       </c>
-      <c r="AP6" s="8" t="s">
-        <v>125</v>
-      </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]BH!$A$2:$A$33,MATCH($D7,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$A$2:$A$33,MATCH($D7,[5]BH!$D$2:$D$33,0))),"")</f>
         <v>Pending</v>
@@ -15715,11 +15683,8 @@
       <c r="AO7" s="9">
         <v>46180</v>
       </c>
-      <c r="AP7" s="8" t="s">
-        <v>133</v>
-      </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]DME!$A$2:$A$35,MATCH($D8,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$A$2:$A$35,MATCH($D8,[5]DME!$D$2:$D$35,0))),"")</f>
         <v>Denied</v>
@@ -15838,11 +15803,8 @@
       <c r="AO8" s="9">
         <v>46162</v>
       </c>
-      <c r="AP8" s="8" t="s">
-        <v>139</v>
-      </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]ORTHO!$A$2:$A$24,MATCH($D9,[5]ORTHO!$D$2:$D$24,0))="","",INDEX([5]ORTHO!$A$2:$A$24,MATCH($D9,[5]ORTHO!$D$2:$D$24,0))),"")</f>
         <v>Denied</v>
@@ -15961,11 +15923,8 @@
       <c r="AO9" s="9">
         <v>46177</v>
       </c>
-      <c r="AP9" s="8" t="s">
-        <v>146</v>
-      </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]DME!$A$2:$A$35,MATCH($D10,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$A$2:$A$35,MATCH($D10,[5]DME!$D$2:$D$35,0))),"")</f>
         <v>Denied</v>
@@ -16086,11 +16045,8 @@
       <c r="AO10" s="9">
         <v>46183</v>
       </c>
-      <c r="AP10" s="8" t="s">
-        <v>155</v>
-      </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]ORTHO!$A$2:$A$39,MATCH($D11,[6]ORTHO!$D$2:$D$39,0))="","",INDEX([6]ORTHO!$A$2:$A$39,MATCH($D11,[6]ORTHO!$D$2:$D$39,0))),"")</f>
         <v>Finalized</v>
@@ -16205,11 +16161,8 @@
       <c r="AO11" s="9">
         <v>46210</v>
       </c>
-      <c r="AP11" s="8" t="s">
-        <v>160</v>
-      </c>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]ORTHO!$A$2:$A$24,MATCH($D12,[5]ORTHO!$D$2:$D$24,0))="","",INDEX([5]ORTHO!$A$2:$A$24,MATCH($D12,[5]ORTHO!$D$2:$D$24,0))),"")</f>
         <v>Finalized</v>
@@ -16330,11 +16283,8 @@
       <c r="AO12" s="9">
         <v>46160</v>
       </c>
-      <c r="AP12" s="8" t="s">
-        <v>165</v>
-      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]BH!$A$2:$A$33,MATCH($D13,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$A$2:$A$33,MATCH($D13,[5]BH!$D$2:$D$33,0))),"")</f>
         <v>Pending</v>
@@ -16453,11 +16403,8 @@
       <c r="AO13" s="9">
         <v>46182</v>
       </c>
-      <c r="AP13" s="8" t="s">
-        <v>172</v>
-      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]BH!$A$2:$A$33,MATCH($D14,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$A$2:$A$33,MATCH($D14,[5]BH!$D$2:$D$33,0))),"")</f>
         <v>Pending</v>
@@ -16576,11 +16523,8 @@
       <c r="AO14" s="9">
         <v>46182</v>
       </c>
-      <c r="AP14" s="8" t="s">
-        <v>177</v>
-      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]US!$A$2:$A$19,MATCH($D15,[5]US!$D$2:$D$19,0))="","",INDEX([5]US!$A$2:$A$19,MATCH($D15,[5]US!$D$2:$D$19,0))),"")</f>
         <v>Finalized</v>
@@ -16697,11 +16641,8 @@
       <c r="AO15" s="9">
         <v>46171</v>
       </c>
-      <c r="AP15" s="8" t="s">
-        <v>182</v>
-      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]US!$A$2:$A$19,MATCH($D16,[5]US!$D$2:$D$19,0))="","",INDEX([5]US!$A$2:$A$19,MATCH($D16,[5]US!$D$2:$D$19,0))),"")</f>
         <v>Denied</v>
@@ -16816,11 +16757,8 @@
       <c r="AO16" s="9">
         <v>46171</v>
       </c>
-      <c r="AP16" s="8" t="s">
-        <v>186</v>
-      </c>
     </row>
-    <row r="17" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]DME!$A$2:$A$35,MATCH($D17,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$A$2:$A$35,MATCH($D17,[5]DME!$D$2:$D$35,0))),"")</f>
         <v>Finalized</v>
@@ -16941,11 +16879,8 @@
       <c r="AO17" s="9">
         <v>46177</v>
       </c>
-      <c r="AP17" s="8" t="s">
-        <v>194</v>
-      </c>
     </row>
-    <row r="18" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]ORTHO!$A$2:$A$24,MATCH($D18,[5]ORTHO!$D$2:$D$24,0))="","",INDEX([5]ORTHO!$A$2:$A$24,MATCH($D18,[5]ORTHO!$D$2:$D$24,0))),"")</f>
         <v>Denied</v>
@@ -17068,11 +17003,8 @@
       <c r="AO18" s="9">
         <v>46177</v>
       </c>
-      <c r="AP18" s="8" t="s">
-        <v>201</v>
-      </c>
     </row>
-    <row r="19" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]BH!$A$2:$A$33,MATCH($D19,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$A$2:$A$33,MATCH($D19,[5]BH!$D$2:$D$33,0))),"")</f>
         <v>Pending</v>
@@ -17187,11 +17119,8 @@
       <c r="AO19" s="9">
         <v>46182</v>
       </c>
-      <c r="AP19" s="8" t="s">
-        <v>209</v>
-      </c>
     </row>
-    <row r="20" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]BH!$A$2:$A$33,MATCH($D20,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$A$2:$A$33,MATCH($D20,[5]BH!$D$2:$D$33,0))),"")</f>
         <v>Denied</v>
@@ -17310,11 +17239,8 @@
       <c r="AO20" s="9">
         <v>46181</v>
       </c>
-      <c r="AP20" s="8" t="s">
-        <v>214</v>
-      </c>
     </row>
-    <row r="21" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]DME!$A$2:$A$35,MATCH($D21,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$A$2:$A$35,MATCH($D21,[5]DME!$D$2:$D$35,0))),"")</f>
         <v>Finalized</v>
@@ -17435,11 +17361,8 @@
       <c r="AO21" s="9">
         <v>46183</v>
       </c>
-      <c r="AP21" s="8" t="s">
-        <v>219</v>
-      </c>
     </row>
-    <row r="22" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]US!$A$2:$A$19,MATCH($D22,[5]US!$D$2:$D$19,0))="","",INDEX([5]US!$A$2:$A$19,MATCH($D22,[5]US!$D$2:$D$19,0))),"")</f>
         <v>Finalized</v>
@@ -17558,11 +17481,8 @@
       <c r="AO22" s="9">
         <v>46171</v>
       </c>
-      <c r="AP22" s="8" t="s">
-        <v>226</v>
-      </c>
     </row>
-    <row r="23" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]US!$A$2:$A$19,MATCH($D23,[5]US!$D$2:$D$19,0))="","",INDEX([5]US!$A$2:$A$19,MATCH($D23,[5]US!$D$2:$D$19,0))),"")</f>
         <v>Denied</v>
@@ -17683,11 +17603,8 @@
       <c r="AO23" s="9">
         <v>46171</v>
       </c>
-      <c r="AP23" s="8" t="s">
-        <v>230</v>
-      </c>
     </row>
-    <row r="24" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]DME!$A$2:$A$35,MATCH($D24,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$A$2:$A$35,MATCH($D24,[5]DME!$D$2:$D$35,0))),"")</f>
         <v>Finalized</v>
@@ -17810,11 +17727,8 @@
       <c r="AO24" s="9">
         <v>46183</v>
       </c>
-      <c r="AP24" s="8" t="s">
-        <v>235</v>
-      </c>
     </row>
-    <row r="25" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]ORTHO!$A$2:$A$24,MATCH($D25,[5]ORTHO!$D$2:$D$24,0))="","",INDEX([5]ORTHO!$A$2:$A$24,MATCH($D25,[5]ORTHO!$D$2:$D$24,0))),"")</f>
         <v>Finalized</v>
@@ -17931,11 +17845,8 @@
       <c r="AO25" s="9">
         <v>46170</v>
       </c>
-      <c r="AP25" s="8" t="s">
-        <v>240</v>
-      </c>
     </row>
-    <row r="26" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]US!$A$2:$A$19,MATCH($D26,[5]US!$D$2:$D$19,0))="","",INDEX([5]US!$A$2:$A$19,MATCH($D26,[5]US!$D$2:$D$19,0))),"")</f>
         <v>Denied</v>
@@ -18058,11 +17969,8 @@
       <c r="AO26" s="9">
         <v>46171</v>
       </c>
-      <c r="AP26" s="8" t="s">
-        <v>248</v>
-      </c>
     </row>
-    <row r="27" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]ORTHO!$A$2:$A$24,MATCH($D27,[5]ORTHO!$D$2:$D$24,0))="","",INDEX([5]ORTHO!$A$2:$A$24,MATCH($D27,[5]ORTHO!$D$2:$D$24,0))),"")</f>
         <v>Denied</v>
@@ -18185,11 +18093,8 @@
       <c r="AO27" s="9">
         <v>46177</v>
       </c>
-      <c r="AP27" s="8" t="s">
-        <v>254</v>
-      </c>
     </row>
-    <row r="28" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D28,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D28,[6]DME!$D$2:$D$52,0))),"")</f>
         <v>Denied</v>
@@ -18310,11 +18215,8 @@
       <c r="AO28" s="9">
         <v>46205</v>
       </c>
-      <c r="AP28" s="8" t="s">
-        <v>259</v>
-      </c>
     </row>
-    <row r="29" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]US!$A$2:$A$23,MATCH($D29,[4]US!$D$2:$D$23,0))="","",INDEX([4]US!$A$2:$A$23,MATCH($D29,[4]US!$D$2:$D$23,0))),"")</f>
         <v>Pending</v>
@@ -18435,11 +18337,8 @@
       <c r="AO29" s="9">
         <v>46147</v>
       </c>
-      <c r="AP29" s="8" t="s">
-        <v>266</v>
-      </c>
     </row>
-    <row r="30" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$A$2:$A$34,MATCH($D30,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$A$2:$A$34,MATCH($D30,[4]DME!$D$2:$D$34,0))),"")</f>
         <v>Finalized</v>
@@ -18562,11 +18461,8 @@
       <c r="AO30" s="9">
         <v>46153</v>
       </c>
-      <c r="AP30" s="8" t="s">
-        <v>272</v>
-      </c>
     </row>
-    <row r="31" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]US!$A$2:$A$23,MATCH($D31,[4]US!$D$2:$D$23,0))="","",INDEX([4]US!$A$2:$A$23,MATCH($D31,[4]US!$D$2:$D$23,0))),"")</f>
         <v>Pending</v>
@@ -18685,11 +18581,8 @@
       <c r="AO31" s="9">
         <v>46147</v>
       </c>
-      <c r="AP31" s="8" t="s">
-        <v>275</v>
-      </c>
     </row>
-    <row r="32" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]BH!$A$2:$A$33,MATCH($D32,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$A$2:$A$33,MATCH($D32,[5]BH!$D$2:$D$33,0))),"")</f>
         <v>Denied</v>
@@ -18806,11 +18699,8 @@
       <c r="AO32" s="9">
         <v>46182</v>
       </c>
-      <c r="AP32" s="8" t="s">
-        <v>277</v>
-      </c>
     </row>
-    <row r="33" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]US!$A$2:$A$23,MATCH($D33,[4]US!$D$2:$D$23,0))="","",INDEX([4]US!$A$2:$A$23,MATCH($D33,[4]US!$D$2:$D$23,0))),"")</f>
         <v>Pending</v>
@@ -18927,11 +18817,8 @@
       <c r="AO33" s="9">
         <v>46148</v>
       </c>
-      <c r="AP33" s="8" t="s">
-        <v>281</v>
-      </c>
     </row>
-    <row r="34" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]ORTHO!$A$2:$A$24,MATCH($D34,[5]ORTHO!$D$2:$D$24,0))="","",INDEX([5]ORTHO!$A$2:$A$24,MATCH($D34,[5]ORTHO!$D$2:$D$24,0))),"")</f>
         <v>Denied</v>
@@ -19050,11 +18937,8 @@
       <c r="AO34" s="9">
         <v>46181</v>
       </c>
-      <c r="AP34" s="8" t="s">
-        <v>285</v>
-      </c>
     </row>
-    <row r="35" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D35,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D35,[6]DME!$D$2:$D$52,0))),"")</f>
         <v>Denied</v>
@@ -19173,11 +19057,8 @@
       <c r="AO35" s="9">
         <v>46185</v>
       </c>
-      <c r="AP35" s="8" t="s">
-        <v>288</v>
-      </c>
     </row>
-    <row r="36" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]ORTHO!$A$2:$A$39,MATCH($D36,[6]ORTHO!$D$2:$D$39,0))="","",INDEX([6]ORTHO!$A$2:$A$39,MATCH($D36,[6]ORTHO!$D$2:$D$39,0))),"")</f>
         <v>Denied</v>
@@ -19298,11 +19179,8 @@
       <c r="AO36" s="9">
         <v>46190</v>
       </c>
-      <c r="AP36" s="8" t="s">
-        <v>294</v>
-      </c>
     </row>
-    <row r="37" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]GAE!$A$2:$A$23,MATCH($D37,[6]GAE!$D$2:$D$23,0))="","",INDEX([6]GAE!$A$2:$A$23,MATCH($D37,[6]GAE!$D$2:$D$23,0))),"")</f>
         <v>PAID</v>
@@ -19427,11 +19305,8 @@
       <c r="AO37" s="9">
         <v>46193</v>
       </c>
-      <c r="AP37" s="8" t="s">
-        <v>306</v>
-      </c>
     </row>
-    <row r="38" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D38,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D38,[6]DME!$D$2:$D$52,0))),"")</f>
         <v>Finalized</v>
@@ -19552,11 +19427,8 @@
       <c r="AO38" s="9">
         <v>46185</v>
       </c>
-      <c r="AP38" s="8" t="s">
-        <v>309</v>
-      </c>
     </row>
-    <row r="39" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]GAE!$A$2:$A$23,MATCH($D39,[6]GAE!$D$2:$D$23,0))="","",INDEX([6]GAE!$A$2:$A$23,MATCH($D39,[6]GAE!$D$2:$D$23,0))),"")</f>
         <v>Denied</v>
@@ -19681,11 +19553,8 @@
       <c r="AO39" s="9">
         <v>46216</v>
       </c>
-      <c r="AP39" s="8" t="s">
-        <v>316</v>
-      </c>
     </row>
-    <row r="40" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D40,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D40,[6]DME!$D$2:$D$52,0))),"")</f>
         <v>Finalized</v>
@@ -19806,11 +19675,8 @@
       <c r="AO40" s="9">
         <v>46185</v>
       </c>
-      <c r="AP40" s="8" t="s">
-        <v>322</v>
-      </c>
     </row>
-    <row r="41" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]DME!$A$2:$A$35,MATCH($D41,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$A$2:$A$35,MATCH($D41,[5]DME!$D$2:$D$35,0))),"")</f>
         <v>Finalized</v>
@@ -19922,11 +19788,8 @@
       <c r="AO41" s="9">
         <v>46162</v>
       </c>
-      <c r="AP41" s="8" t="s">
-        <v>327</v>
-      </c>
     </row>
-    <row r="42" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]GAE!$A$2:$A$7,MATCH($D42,[5]GAE!$D$2:$D$7,0))="","",INDEX([5]GAE!$A$2:$A$7,MATCH($D42,[5]GAE!$D$2:$D$7,0))),"")</f>
         <v>Finalized</v>
@@ -20049,11 +19912,8 @@
       <c r="AO42" s="9">
         <v>46182</v>
       </c>
-      <c r="AP42" s="8" t="s">
-        <v>331</v>
-      </c>
     </row>
-    <row r="43" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]US!$A$2:$A$22,MATCH($D43,[6]US!$D$2:$D$22,0))="","",INDEX([6]US!$A$2:$A$22,MATCH($D43,[6]US!$D$2:$D$22,0))),"")</f>
         <v>Denied</v>
@@ -20172,11 +20032,8 @@
       <c r="AO43" s="9">
         <v>46195</v>
       </c>
-      <c r="AP43" s="8" t="s">
-        <v>337</v>
-      </c>
     </row>
-    <row r="44" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]US!$A$2:$A$19,MATCH($D44,[5]US!$D$2:$D$19,0))="","",INDEX([5]US!$A$2:$A$19,MATCH($D44,[5]US!$D$2:$D$19,0))),"")</f>
         <v>Finalized</v>
@@ -20293,11 +20150,8 @@
       <c r="AO44" s="9">
         <v>46164</v>
       </c>
-      <c r="AP44" s="8" t="s">
-        <v>341</v>
-      </c>
     </row>
-    <row r="45" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]ORTHO!$A$2:$A$39,MATCH($D45,[6]ORTHO!$D$2:$D$39,0))="","",INDEX([6]ORTHO!$A$2:$A$39,MATCH($D45,[6]ORTHO!$D$2:$D$39,0))),"")</f>
         <v>Denied</v>
@@ -20420,11 +20274,8 @@
       <c r="AO45" s="9">
         <v>46190</v>
       </c>
-      <c r="AP45" s="8" t="s">
-        <v>345</v>
-      </c>
     </row>
-    <row r="46" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]US!$A$2:$A$22,MATCH($D46,[6]US!$D$2:$D$22,0))="","",INDEX([6]US!$A$2:$A$22,MATCH($D46,[6]US!$D$2:$D$22,0))),"")</f>
         <v>Pending</v>
@@ -20541,11 +20392,8 @@
       <c r="AO46" s="9">
         <v>46195</v>
       </c>
-      <c r="AP46" s="8" t="s">
-        <v>347</v>
-      </c>
     </row>
-    <row r="47" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A47" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D47,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D47,[6]DME!$D$2:$D$52,0))),"")</f>
         <v>Under Review</v>
@@ -20664,11 +20512,8 @@
       <c r="AO47" s="9">
         <v>46211</v>
       </c>
-      <c r="AP47" s="8" t="s">
-        <v>356</v>
-      </c>
     </row>
-    <row r="48" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]US!$A$2:$A$19,MATCH($D48,[5]US!$D$2:$D$19,0))="","",INDEX([5]US!$A$2:$A$19,MATCH($D48,[5]US!$D$2:$D$19,0))),"")</f>
         <v>Denied</v>
@@ -20787,11 +20632,8 @@
       <c r="AO48" s="9">
         <v>46164</v>
       </c>
-      <c r="AP48" s="8" t="s">
-        <v>358</v>
-      </c>
     </row>
-    <row r="49" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]ORTHO!$A$2:$A$39,MATCH($D49,[6]ORTHO!$D$2:$D$39,0))="","",INDEX([6]ORTHO!$A$2:$A$39,MATCH($D49,[6]ORTHO!$D$2:$D$39,0))),"")</f>
         <v>Pending</v>
@@ -20914,11 +20756,8 @@
       <c r="AO49" s="9">
         <v>46190</v>
       </c>
-      <c r="AP49" s="8" t="s">
-        <v>366</v>
-      </c>
     </row>
-    <row r="50" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]ORTHO!$A$2:$A$39,MATCH($D50,[6]ORTHO!$D$2:$D$39,0))="","",INDEX([6]ORTHO!$A$2:$A$39,MATCH($D50,[6]ORTHO!$D$2:$D$39,0))),"")</f>
         <v>Under Review</v>
@@ -21041,11 +20880,8 @@
       <c r="AO50" s="9">
         <v>46190</v>
       </c>
-      <c r="AP50" s="8" t="s">
-        <v>369</v>
-      </c>
     </row>
-    <row r="51" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]ORTHO!$A$2:$A$39,MATCH($D51,[6]ORTHO!$D$2:$D$39,0))="","",INDEX([6]ORTHO!$A$2:$A$39,MATCH($D51,[6]ORTHO!$D$2:$D$39,0))),"")</f>
         <v>Denied</v>
@@ -21170,11 +21006,8 @@
       <c r="AO51" s="9">
         <v>46190</v>
       </c>
-      <c r="AP51" s="8" t="s">
-        <v>373</v>
-      </c>
     </row>
-    <row r="52" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]GAE!$A$2:$A$23,MATCH($D52,[6]GAE!$D$2:$D$23,0))="","",INDEX([6]GAE!$A$2:$A$23,MATCH($D52,[6]GAE!$D$2:$D$23,0))),"")</f>
         <v>Denied</v>
@@ -21299,11 +21132,8 @@
       <c r="AO52" s="9">
         <v>46216</v>
       </c>
-      <c r="AP52" s="8" t="s">
-        <v>378</v>
-      </c>
     </row>
-    <row r="53" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]GAE!$A$2:$A$23,MATCH($D53,[6]GAE!$D$2:$D$23,0))="","",INDEX([6]GAE!$A$2:$A$23,MATCH($D53,[6]GAE!$D$2:$D$23,0))),"")</f>
         <v>Denied</v>
@@ -21430,11 +21260,8 @@
       <c r="AO53" s="9">
         <v>46216</v>
       </c>
-      <c r="AP53" s="8" t="s">
-        <v>382</v>
-      </c>
     </row>
-    <row r="54" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]GAE!$A$2:$A$23,MATCH($D54,[6]GAE!$D$2:$D$23,0))="","",INDEX([6]GAE!$A$2:$A$23,MATCH($D54,[6]GAE!$D$2:$D$23,0))),"")</f>
         <v>PAID</v>
@@ -21559,11 +21386,8 @@
       <c r="AO54" s="9">
         <v>46216</v>
       </c>
-      <c r="AP54" s="8" t="s">
-        <v>387</v>
-      </c>
     </row>
-    <row r="55" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]BH!$A$2:$A$82,MATCH($D55,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$A$2:$A$82,MATCH($D55,[6]BH!$D$2:$D$82,0))),"")</f>
         <v>Denied</v>
@@ -21678,11 +21502,8 @@
       <c r="AO55" s="9">
         <v>46217</v>
       </c>
-      <c r="AP55" s="8" t="s">
-        <v>389</v>
-      </c>
     </row>
-    <row r="56" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D56,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D56,[6]DME!$D$2:$D$52,0))),"")</f>
         <v>Denied</v>
@@ -21803,11 +21624,8 @@
       <c r="AO56" s="9">
         <v>46191</v>
       </c>
-      <c r="AP56" s="8" t="s">
-        <v>394</v>
-      </c>
     </row>
-    <row r="57" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]US!$A$2:$A$22,MATCH($D57,[6]US!$D$2:$D$22,0))="","",INDEX([6]US!$A$2:$A$22,MATCH($D57,[6]US!$D$2:$D$22,0))),"")</f>
         <v>Denied</v>
@@ -21928,11 +21746,8 @@
       <c r="AO57" s="9">
         <v>46195</v>
       </c>
-      <c r="AP57" s="8" t="s">
-        <v>399</v>
-      </c>
     </row>
-    <row r="58" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A58" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]ORTHO!$A$2:$A$24,MATCH($D58,[5]ORTHO!$D$2:$D$24,0))="","",INDEX([5]ORTHO!$A$2:$A$24,MATCH($D58,[5]ORTHO!$D$2:$D$24,0))),"")</f>
         <v>Finalized</v>
@@ -22057,11 +21872,8 @@
       <c r="AO58" s="9">
         <v>46156</v>
       </c>
-      <c r="AP58" s="8" t="s">
-        <v>404</v>
-      </c>
     </row>
-    <row r="59" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]BH!$A$2:$A$82,MATCH($D59,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$A$2:$A$82,MATCH($D59,[6]BH!$D$2:$D$82,0))),"")</f>
         <v>Denied</v>
@@ -22178,11 +21990,8 @@
       <c r="AO59" s="9">
         <v>46217</v>
       </c>
-      <c r="AP59" s="8" t="s">
-        <v>413</v>
-      </c>
     </row>
-    <row r="60" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]US!$A$2:$A$22,MATCH($D60,[6]US!$D$2:$D$22,0))="","",INDEX([6]US!$A$2:$A$22,MATCH($D60,[6]US!$D$2:$D$22,0))),"")</f>
         <v>Denied</v>
@@ -22299,11 +22108,8 @@
       <c r="AO60" s="9">
         <v>46195</v>
       </c>
-      <c r="AP60" s="8" t="s">
-        <v>416</v>
-      </c>
     </row>
-    <row r="61" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]ORTHO!$A$2:$A$39,MATCH($D61,[6]ORTHO!$D$2:$D$39,0))="","",INDEX([6]ORTHO!$A$2:$A$39,MATCH($D61,[6]ORTHO!$D$2:$D$39,0))),"")</f>
         <v>Under Review</v>
@@ -22422,11 +22228,8 @@
       <c r="AO61" s="9">
         <v>46188</v>
       </c>
-      <c r="AP61" s="8" t="s">
-        <v>418</v>
-      </c>
     </row>
-    <row r="62" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]ORTHO!$A$2:$A$39,MATCH($D62,[6]ORTHO!$D$2:$D$39,0))="","",INDEX([6]ORTHO!$A$2:$A$39,MATCH($D62,[6]ORTHO!$D$2:$D$39,0))),"")</f>
         <v>Denied</v>
@@ -22547,11 +22350,8 @@
       <c r="AO62" s="9">
         <v>46190</v>
       </c>
-      <c r="AP62" s="8" t="s">
-        <v>431</v>
-      </c>
     </row>
-    <row r="63" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]ORTHO!$A$2:$A$39,MATCH($D63,[6]ORTHO!$D$2:$D$39,0))="","",INDEX([6]ORTHO!$A$2:$A$39,MATCH($D63,[6]ORTHO!$D$2:$D$39,0))),"")</f>
         <v>Denied</v>
@@ -22668,11 +22468,8 @@
       <c r="AO63" s="9">
         <v>46189</v>
       </c>
-      <c r="AP63" s="8" t="s">
-        <v>434</v>
-      </c>
     </row>
-    <row r="64" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D64,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D64,[6]DME!$D$2:$D$52,0))),"")</f>
         <v>Under Review</v>
@@ -22791,11 +22588,8 @@
       <c r="AO64" s="9">
         <v>46190</v>
       </c>
-      <c r="AP64" s="8" t="s">
-        <v>437</v>
-      </c>
     </row>
-    <row r="65" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]ORTHO!$A$2:$A$24,MATCH($D65,[5]ORTHO!$D$2:$D$24,0))="","",INDEX([5]ORTHO!$A$2:$A$24,MATCH($D65,[5]ORTHO!$D$2:$D$24,0))),"")</f>
         <v/>
@@ -22914,11 +22708,8 @@
       <c r="AO65" s="9">
         <v>46161</v>
       </c>
-      <c r="AP65" s="8" t="s">
-        <v>441</v>
-      </c>
     </row>
-    <row r="66" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]ORTHO!$A$2:$A$24,MATCH($D66,[5]ORTHO!$D$2:$D$24,0))="","",INDEX([5]ORTHO!$A$2:$A$24,MATCH($D66,[5]ORTHO!$D$2:$D$24,0))),"")</f>
         <v>Finalized</v>
@@ -23035,11 +22826,8 @@
       <c r="AO66" s="9">
         <v>46161</v>
       </c>
-      <c r="AP66" s="8" t="s">
-        <v>443</v>
-      </c>
     </row>
-    <row r="67" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]BH!$A$2:$A$32,MATCH($D67,[2]BH!$D$2:$D$32,0))="","",INDEX([2]BH!$A$2:$A$32,MATCH($D67,[2]BH!$D$2:$D$32,0))),"")</f>
         <v>Finalized</v>
@@ -23156,11 +22944,8 @@
       <c r="AO67" s="9">
         <v>46119</v>
       </c>
-      <c r="AP67" s="8" t="s">
-        <v>449</v>
-      </c>
     </row>
-    <row r="68" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]BH!$A$2:$A$82,MATCH($D68,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$A$2:$A$82,MATCH($D68,[6]BH!$D$2:$D$82,0))),"")</f>
         <v>Under Review</v>
@@ -23277,11 +23062,8 @@
       <c r="AO68" s="9">
         <v>46233</v>
       </c>
-      <c r="AP68" s="8" t="s">
-        <v>463</v>
-      </c>
     </row>
-    <row r="69" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D69,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D69,[6]DME!$D$2:$D$52,0))),"")</f>
         <v>Finalized</v>
@@ -23400,11 +23182,8 @@
       <c r="AO69" s="9">
         <v>46191</v>
       </c>
-      <c r="AP69" s="8" t="s">
-        <v>464</v>
-      </c>
     </row>
-    <row r="70" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D70,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D70,[6]DME!$D$2:$D$52,0))),"")</f>
         <v>Under Review</v>
@@ -23525,11 +23304,8 @@
       <c r="AO70" s="9">
         <v>46191</v>
       </c>
-      <c r="AP70" s="8" t="s">
-        <v>472</v>
-      </c>
     </row>
-    <row r="71" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]US!$A$2:$A$22,MATCH($D71,[6]US!$D$2:$D$22,0))="","",INDEX([6]US!$A$2:$A$22,MATCH($D71,[6]US!$D$2:$D$22,0))),"")</f>
         <v>Denied</v>
@@ -23648,11 +23424,8 @@
       <c r="AO71" s="9">
         <v>46195</v>
       </c>
-      <c r="AP71" s="8" t="s">
-        <v>474</v>
-      </c>
     </row>
-    <row r="72" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]BH!$A$2:$A$32,MATCH($D72,[2]BH!$D$2:$D$32,0))="","",INDEX([2]BH!$A$2:$A$32,MATCH($D72,[2]BH!$D$2:$D$32,0))),"")</f>
         <v>Denied</v>
@@ -23769,11 +23542,8 @@
       <c r="AO72" s="9">
         <v>46119</v>
       </c>
-      <c r="AP72" s="8" t="s">
-        <v>478</v>
-      </c>
     </row>
-    <row r="73" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A73" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]DME!$A$2:$A$35,MATCH($D73,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$A$2:$A$35,MATCH($D73,[5]DME!$D$2:$D$35,0))),"")</f>
         <v>Not found</v>
@@ -23894,11 +23664,8 @@
       <c r="AO73" s="9">
         <v>46162</v>
       </c>
-      <c r="AP73" s="8" t="s">
-        <v>481</v>
-      </c>
     </row>
-    <row r="74" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]BH!$A$2:$A$82,MATCH($D74,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$A$2:$A$82,MATCH($D74,[6]BH!$D$2:$D$82,0))),"")</f>
         <v>Pending</v>
@@ -24013,11 +23780,8 @@
       <c r="AO74" s="9">
         <v>46217</v>
       </c>
-      <c r="AP74" s="8" t="s">
-        <v>484</v>
-      </c>
     </row>
-    <row r="75" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D75,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D75,[6]DME!$D$2:$D$52,0))),"")</f>
         <v>Denied</v>
@@ -24134,11 +23898,8 @@
       <c r="AO75" s="9">
         <v>46196</v>
       </c>
-      <c r="AP75" s="8" t="s">
-        <v>485</v>
-      </c>
     </row>
-    <row r="76" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A76" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D76,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D76,[6]DME!$D$2:$D$52,0))),"")</f>
         <v>Denied</v>
@@ -24255,11 +24016,8 @@
       <c r="AO76" s="9">
         <v>46196</v>
       </c>
-      <c r="AP76" s="8" t="s">
-        <v>488</v>
-      </c>
     </row>
-    <row r="77" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]ORTHO!$A$2:$A$39,MATCH($D77,[6]ORTHO!$D$2:$D$39,0))="","",INDEX([6]ORTHO!$A$2:$A$39,MATCH($D77,[6]ORTHO!$D$2:$D$39,0))),"")</f>
         <v>Pending</v>
@@ -24380,11 +24138,8 @@
       <c r="AO77" s="9">
         <v>46210</v>
       </c>
-      <c r="AP77" s="8" t="s">
-        <v>493</v>
-      </c>
     </row>
-    <row r="78" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]BH!$A$2:$A$82,MATCH($D78,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$A$2:$A$82,MATCH($D78,[6]BH!$D$2:$D$82,0))),"")</f>
         <v>Denied</v>
@@ -24501,11 +24256,8 @@
       <c r="AO78" s="9">
         <v>46234</v>
       </c>
-      <c r="AP78" s="8" t="s">
-        <v>503</v>
-      </c>
     </row>
-    <row r="79" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D79,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D79,[6]DME!$D$2:$D$52,0))),"")</f>
         <v>Denied</v>
@@ -24626,11 +24378,8 @@
       <c r="AO79" s="9">
         <v>46196</v>
       </c>
-      <c r="AP79" s="8" t="s">
-        <v>505</v>
-      </c>
     </row>
-    <row r="80" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D80,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D80,[6]DME!$D$2:$D$52,0))),"")</f>
         <v>Denied</v>
@@ -24751,11 +24500,8 @@
       <c r="AO80" s="9">
         <v>46196</v>
       </c>
-      <c r="AP80" s="8" t="s">
-        <v>510</v>
-      </c>
     </row>
-    <row r="81" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D81,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D81,[6]DME!$D$2:$D$52,0))),"")</f>
         <v>Under Review</v>
@@ -24874,11 +24620,8 @@
       <c r="AO81" s="9">
         <v>46196</v>
       </c>
-      <c r="AP81" s="8" t="s">
-        <v>512</v>
-      </c>
     </row>
-    <row r="82" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D82,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D82,[6]DME!$D$2:$D$52,0))),"")</f>
         <v>Denied</v>
@@ -24997,11 +24740,8 @@
       <c r="AO82" s="9">
         <v>46196</v>
       </c>
-      <c r="AP82" s="8" t="s">
-        <v>516</v>
-      </c>
     </row>
-    <row r="83" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]GAE!$A$2:$A$23,MATCH($D83,[6]GAE!$D$2:$D$23,0))="","",INDEX([6]GAE!$A$2:$A$23,MATCH($D83,[6]GAE!$D$2:$D$23,0))),"")</f>
         <v>Denied</v>
@@ -25126,11 +24866,8 @@
       <c r="AO83" s="9">
         <v>46216</v>
       </c>
-      <c r="AP83" s="8" t="s">
-        <v>521</v>
-      </c>
     </row>
-    <row r="84" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]GAE!$A$2:$A$23,MATCH($D84,[6]GAE!$D$2:$D$23,0))="","",INDEX([6]GAE!$A$2:$A$23,MATCH($D84,[6]GAE!$D$2:$D$23,0))),"")</f>
         <v>Denied</v>
@@ -25253,11 +24990,8 @@
       <c r="AO84" s="9">
         <v>46216</v>
       </c>
-      <c r="AP84" s="8" t="s">
-        <v>525</v>
-      </c>
     </row>
-    <row r="85" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A85" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D85,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D85,[6]DME!$D$2:$D$52,0))),"")</f>
         <v>Denied</v>
@@ -25376,11 +25110,8 @@
       <c r="AO85" s="9">
         <v>46204</v>
       </c>
-      <c r="AP85" s="8" t="s">
-        <v>528</v>
-      </c>
     </row>
-    <row r="86" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]ORTHO!$A$2:$A$39,MATCH($D86,[6]ORTHO!$D$2:$D$39,0))="","",INDEX([6]ORTHO!$A$2:$A$39,MATCH($D86,[6]ORTHO!$D$2:$D$39,0))),"")</f>
         <v>Denied</v>
@@ -25499,11 +25230,8 @@
       <c r="AO86" s="9">
         <v>46203</v>
       </c>
-      <c r="AP86" s="8" t="s">
-        <v>534</v>
-      </c>
     </row>
-    <row r="87" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D87,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D87,[6]DME!$D$2:$D$52,0))),"")</f>
         <v>Under Review</v>
@@ -25624,11 +25352,8 @@
       <c r="AO87" s="9">
         <v>46205</v>
       </c>
-      <c r="AP87" s="8" t="s">
-        <v>536</v>
-      </c>
     </row>
-    <row r="88" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]DME!$A$2:$A$35,MATCH($D88,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$A$2:$A$35,MATCH($D88,[5]DME!$D$2:$D$35,0))),"")</f>
         <v>Denied</v>
@@ -25753,11 +25478,8 @@
       <c r="AO88" s="9">
         <v>46183</v>
       </c>
-      <c r="AP88" s="8" t="s">
-        <v>544</v>
-      </c>
     </row>
-    <row r="89" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]BH!$A$2:$A$82,MATCH($D89,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$A$2:$A$82,MATCH($D89,[6]BH!$D$2:$D$82,0))),"")</f>
         <v>Pending</v>
@@ -25872,11 +25594,8 @@
       <c r="AO89" s="9">
         <v>46217</v>
       </c>
-      <c r="AP89" s="8" t="s">
-        <v>546</v>
-      </c>
     </row>
-    <row r="90" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]ORTHO!$A$2:$A$39,MATCH($D90,[6]ORTHO!$D$2:$D$39,0))="","",INDEX([6]ORTHO!$A$2:$A$39,MATCH($D90,[6]ORTHO!$D$2:$D$39,0))),"")</f>
         <v>Rejected</v>
@@ -25999,11 +25718,8 @@
       <c r="AO90" s="9">
         <v>46203</v>
       </c>
-      <c r="AP90" s="8" t="s">
-        <v>553</v>
-      </c>
     </row>
-    <row r="91" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]ORTHO!$A$2:$A$39,MATCH($D91,[6]ORTHO!$D$2:$D$39,0))="","",INDEX([6]ORTHO!$A$2:$A$39,MATCH($D91,[6]ORTHO!$D$2:$D$39,0))),"")</f>
         <v>Denied</v>
@@ -26124,11 +25840,8 @@
       <c r="AO91" s="9">
         <v>46203</v>
       </c>
-      <c r="AP91" s="8" t="s">
-        <v>556</v>
-      </c>
     </row>
-    <row r="92" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]US!$A$2:$A$22,MATCH($D92,[6]US!$D$2:$D$22,0))="","",INDEX([6]US!$A$2:$A$22,MATCH($D92,[6]US!$D$2:$D$22,0))),"")</f>
         <v>Pending</v>
@@ -26243,11 +25956,8 @@
       <c r="AO92" s="9">
         <v>46204</v>
       </c>
-      <c r="AP92" s="8" t="s">
-        <v>559</v>
-      </c>
     </row>
-    <row r="93" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D93,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D93,[6]DME!$D$2:$D$52,0))),"")</f>
         <v>Denied</v>
@@ -26366,11 +26076,8 @@
       <c r="AO93" s="9">
         <v>46205</v>
       </c>
-      <c r="AP93" s="8" t="s">
-        <v>562</v>
-      </c>
     </row>
-    <row r="94" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A94" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]BH!$A$2:$A$33,MATCH($D94,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$A$2:$A$33,MATCH($D94,[5]BH!$D$2:$D$33,0))),"")</f>
         <v>Under Review</v>
@@ -26487,11 +26194,8 @@
       <c r="AO94" s="9">
         <v>46182</v>
       </c>
-      <c r="AP94" s="8" t="s">
-        <v>566</v>
-      </c>
     </row>
-    <row r="95" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A95" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]BH!$A$2:$A$33,MATCH($D95,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$A$2:$A$33,MATCH($D95,[5]BH!$D$2:$D$33,0))),"")</f>
         <v>Finalized</v>
@@ -26614,11 +26318,8 @@
       <c r="AO95" s="9">
         <v>46234</v>
       </c>
-      <c r="AP95" s="8" t="s">
-        <v>571</v>
-      </c>
     </row>
-    <row r="96" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D96,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D96,[6]DME!$D$2:$D$52,0))),"")</f>
         <v>Denied</v>
@@ -26739,11 +26440,8 @@
       <c r="AO96" s="9">
         <v>46204</v>
       </c>
-      <c r="AP96" s="8" t="s">
-        <v>586</v>
-      </c>
     </row>
-    <row r="97" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D97,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D97,[6]DME!$D$2:$D$52,0))),"")</f>
         <v>Denied</v>
@@ -26860,11 +26558,8 @@
       <c r="AO97" s="9">
         <v>46205</v>
       </c>
-      <c r="AP97" s="8" t="s">
-        <v>587</v>
-      </c>
     </row>
-    <row r="98" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D98,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D98,[6]DME!$D$2:$D$52,0))),"")</f>
         <v>Denied</v>
@@ -26981,11 +26676,8 @@
       <c r="AO98" s="9">
         <v>46205</v>
       </c>
-      <c r="AP98" s="8" t="s">
-        <v>589</v>
-      </c>
     </row>
-    <row r="99" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]GAE!$A$2:$A$23,MATCH($D99,[6]GAE!$D$2:$D$23,0))="","",INDEX([6]GAE!$A$2:$A$23,MATCH($D99,[6]GAE!$D$2:$D$23,0))),"")</f>
         <v>Denied</v>
@@ -27110,11 +26802,8 @@
       <c r="AO99" s="9">
         <v>46216</v>
       </c>
-      <c r="AP99" s="8" t="s">
-        <v>598</v>
-      </c>
     </row>
-    <row r="100" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D100,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D100,[6]DME!$D$2:$D$52,0))),"")</f>
         <v>Rejected</v>
@@ -27231,11 +26920,8 @@
       <c r="AO100" s="9">
         <v>46217</v>
       </c>
-      <c r="AP100" s="8" t="s">
-        <v>599</v>
-      </c>
     </row>
-    <row r="101" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]GAE!$A$2:$A$23,MATCH($D101,[6]GAE!$D$2:$D$23,0))="","",INDEX([6]GAE!$A$2:$A$23,MATCH($D101,[6]GAE!$D$2:$D$23,0))),"")</f>
         <v>Pending</v>
@@ -27352,11 +27038,8 @@
       <c r="AO101" s="9">
         <v>46225</v>
       </c>
-      <c r="AP101" s="8" t="s">
-        <v>605</v>
-      </c>
     </row>
-    <row r="102" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D102,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D102,[6]DME!$D$2:$D$52,0))),"")</f>
         <v>Denied</v>
@@ -27475,11 +27158,8 @@
       <c r="AO102" s="9">
         <v>46205</v>
       </c>
-      <c r="AP102" s="8" t="s">
-        <v>609</v>
-      </c>
     </row>
-    <row r="103" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]ORTHO!$A$2:$A$39,MATCH($D103,[6]ORTHO!$D$2:$D$39,0))="","",INDEX([6]ORTHO!$A$2:$A$39,MATCH($D103,[6]ORTHO!$D$2:$D$39,0))),"")</f>
         <v/>
@@ -27598,11 +27278,8 @@
       <c r="AO103" s="9">
         <v>46213</v>
       </c>
-      <c r="AP103" s="8" t="s">
-        <v>616</v>
-      </c>
     </row>
-    <row r="104" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A104" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]US!$A$2:$A$22,MATCH($D104,[6]US!$D$2:$D$22,0))="","",INDEX([6]US!$A$2:$A$22,MATCH($D104,[6]US!$D$2:$D$22,0))),"")</f>
         <v/>
@@ -27721,11 +27398,8 @@
       <c r="AO104" s="9">
         <v>46204</v>
       </c>
-      <c r="AP104" s="8" t="s">
-        <v>621</v>
-      </c>
     </row>
-    <row r="105" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]ORTHO!$A$2:$A$39,MATCH($D105,[6]ORTHO!$D$2:$D$39,0))="","",INDEX([6]ORTHO!$A$2:$A$39,MATCH($D105,[6]ORTHO!$D$2:$D$39,0))),"")</f>
         <v/>
@@ -27842,11 +27516,8 @@
       <c r="AO105" s="9">
         <v>46211</v>
       </c>
-      <c r="AP105" s="8" t="s">
-        <v>623</v>
-      </c>
     </row>
-    <row r="106" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]BH!$A$2:$A$82,MATCH($D106,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$A$2:$A$82,MATCH($D106,[6]BH!$D$2:$D$82,0))),"")</f>
         <v/>
@@ -27961,11 +27632,8 @@
       <c r="AO106" s="9">
         <v>46217</v>
       </c>
-      <c r="AP106" s="8" t="s">
-        <v>627</v>
-      </c>
     </row>
-    <row r="107" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A107" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]GAE!$A$2:$A$23,MATCH($D107,[6]GAE!$D$2:$D$23,0))="","",INDEX([6]GAE!$A$2:$A$23,MATCH($D107,[6]GAE!$D$2:$D$23,0))),"")</f>
         <v/>
@@ -28090,11 +27758,8 @@
       <c r="AO107" s="9">
         <v>46216</v>
       </c>
-      <c r="AP107" s="8" t="s">
-        <v>638</v>
-      </c>
     </row>
-    <row r="108" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A108" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]ORTHO!$A$2:$A$39,MATCH($D108,[6]ORTHO!$D$2:$D$39,0))="","",INDEX([6]ORTHO!$A$2:$A$39,MATCH($D108,[6]ORTHO!$D$2:$D$39,0))),"")</f>
         <v>Finalized</v>
@@ -28215,11 +27880,8 @@
       <c r="AO108" s="9">
         <v>46184</v>
       </c>
-      <c r="AP108" s="8" t="s">
-        <v>641</v>
-      </c>
     </row>
-    <row r="109" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]ORTHO!$A$2:$A$39,MATCH($D109,[6]ORTHO!$D$2:$D$39,0))="","",INDEX([6]ORTHO!$A$2:$A$39,MATCH($D109,[6]ORTHO!$D$2:$D$39,0))),"")</f>
         <v/>
@@ -28338,11 +28000,8 @@
       <c r="AO109" s="9">
         <v>46203</v>
       </c>
-      <c r="AP109" s="8" t="s">
-        <v>656</v>
-      </c>
     </row>
-    <row r="110" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]GAE!$A$2:$A$23,MATCH($D110,[6]GAE!$D$2:$D$23,0))="","",INDEX([6]GAE!$A$2:$A$23,MATCH($D110,[6]GAE!$D$2:$D$23,0))),"")</f>
         <v/>
@@ -28467,11 +28126,8 @@
       <c r="AO110" s="9">
         <v>46216</v>
       </c>
-      <c r="AP110" s="8" t="s">
-        <v>660</v>
-      </c>
     </row>
-    <row r="111" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]BH!$A$2:$A$82,MATCH($D111,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$A$2:$A$82,MATCH($D111,[6]BH!$D$2:$D$82,0))),"")</f>
         <v/>
@@ -28586,11 +28242,8 @@
       <c r="AO111" s="9">
         <v>46217</v>
       </c>
-      <c r="AP111" s="8" t="s">
-        <v>662</v>
-      </c>
     </row>
-    <row r="112" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A112" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]US!$A$2:$A$22,MATCH($D112,[6]US!$D$2:$D$22,0))="","",INDEX([6]US!$A$2:$A$22,MATCH($D112,[6]US!$D$2:$D$22,0))),"")</f>
         <v/>
@@ -28707,11 +28360,8 @@
       <c r="AO112" s="9">
         <v>46195</v>
       </c>
-      <c r="AP112" s="8" t="s">
-        <v>664</v>
-      </c>
     </row>
-    <row r="113" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A113" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]US!$A$2:$A$22,MATCH($D113,[6]US!$D$2:$D$22,0))="","",INDEX([6]US!$A$2:$A$22,MATCH($D113,[6]US!$D$2:$D$22,0))),"")</f>
         <v/>
@@ -28826,11 +28476,8 @@
       <c r="AO113" s="9">
         <v>46204</v>
       </c>
-      <c r="AP113" s="8" t="s">
-        <v>667</v>
-      </c>
     </row>
-    <row r="114" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A114" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]GAE!$A$2:$A$8,MATCH($D114,[4]GAE!$D$2:$D$8,0))="","",INDEX([4]GAE!$A$2:$A$8,MATCH($D114,[4]GAE!$D$2:$D$8,0))),"")</f>
         <v>Finalized</v>
@@ -28957,11 +28604,8 @@
       <c r="AO114" s="9">
         <v>46152</v>
       </c>
-      <c r="AP114" s="8" t="s">
-        <v>673</v>
-      </c>
     </row>
-    <row r="115" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A115" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D115,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D115,[6]DME!$D$2:$D$52,0))),"")</f>
         <v>Pending</v>
@@ -29082,11 +28726,8 @@
       <c r="AO115" s="9">
         <v>46196</v>
       </c>
-      <c r="AP115" s="8" t="s">
-        <v>678</v>
-      </c>
     </row>
-    <row r="116" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A116" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]ORTHO!$A$2:$A$39,MATCH($D116,[6]ORTHO!$D$2:$D$39,0))="","",INDEX([6]ORTHO!$A$2:$A$39,MATCH($D116,[6]ORTHO!$D$2:$D$39,0))),"")</f>
         <v/>
@@ -29205,11 +28846,8 @@
       <c r="AO116" s="9">
         <v>46205</v>
       </c>
-      <c r="AP116" s="8" t="s">
-        <v>684</v>
-      </c>
     </row>
-    <row r="117" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]ORTHO!$A$2:$A$39,MATCH($D117,[6]ORTHO!$D$2:$D$39,0))="","",INDEX([6]ORTHO!$A$2:$A$39,MATCH($D117,[6]ORTHO!$D$2:$D$39,0))),"")</f>
         <v/>
@@ -29330,11 +28968,8 @@
       <c r="AO117" s="9">
         <v>46203</v>
       </c>
-      <c r="AP117" s="8" t="s">
-        <v>694</v>
-      </c>
     </row>
-    <row r="118" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A118" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]GAE!$A$2:$A$23,MATCH($D118,[6]GAE!$D$2:$D$23,0))="","",INDEX([6]GAE!$A$2:$A$23,MATCH($D118,[6]GAE!$D$2:$D$23,0))),"")</f>
         <v/>
@@ -29459,11 +29094,8 @@
       <c r="AO118" s="9">
         <v>46216</v>
       </c>
-      <c r="AP118" s="8" t="s">
-        <v>699</v>
-      </c>
     </row>
-    <row r="119" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]DME!$A$2:$A$35,MATCH($D119,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$A$2:$A$35,MATCH($D119,[5]DME!$D$2:$D$35,0))),"")</f>
         <v>Denied</v>
@@ -29584,11 +29216,8 @@
       <c r="AO119" s="9">
         <v>46162</v>
       </c>
-      <c r="AP119" s="8" t="s">
-        <v>702</v>
-      </c>
     </row>
-    <row r="120" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A120" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]ORTHO!$A$2:$A$24,MATCH($D120,[5]ORTHO!$D$2:$D$24,0))="","",INDEX([5]ORTHO!$A$2:$A$24,MATCH($D120,[5]ORTHO!$D$2:$D$24,0))),"")</f>
         <v>Finalized</v>
@@ -29705,11 +29334,8 @@
       <c r="AO120" s="9">
         <v>46157</v>
       </c>
-      <c r="AP120" s="8" t="s">
-        <v>710</v>
-      </c>
     </row>
-    <row r="121" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]DME!$A$2:$A$35,MATCH($D121,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$A$2:$A$35,MATCH($D121,[5]DME!$D$2:$D$35,0))),"")</f>
         <v>Under Review</v>
@@ -29830,11 +29456,8 @@
       <c r="AO121" s="9">
         <v>46183</v>
       </c>
-      <c r="AP121" s="8" t="s">
-        <v>711</v>
-      </c>
     </row>
-    <row r="122" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A122" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]DME!$A$2:$A$35,MATCH($D122,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$A$2:$A$35,MATCH($D122,[5]DME!$D$2:$D$35,0))),"")</f>
         <v>Denied</v>
@@ -29957,11 +29580,8 @@
       <c r="AO122" s="9">
         <v>46183</v>
       </c>
-      <c r="AP122" s="8" t="s">
-        <v>714</v>
-      </c>
     </row>
-    <row r="123" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D123,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D123,[6]DME!$D$2:$D$52,0))),"")</f>
         <v/>
@@ -30080,11 +29700,8 @@
       <c r="AO123" s="9">
         <v>46185</v>
       </c>
-      <c r="AP123" s="8" t="s">
-        <v>725</v>
-      </c>
     </row>
-    <row r="124" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A124" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]GAE!$A$2:$A$23,MATCH($D124,[6]GAE!$D$2:$D$23,0))="","",INDEX([6]GAE!$A$2:$A$23,MATCH($D124,[6]GAE!$D$2:$D$23,0))),"")</f>
         <v/>
@@ -30209,11 +29826,8 @@
       <c r="AO124" s="9">
         <v>46216</v>
       </c>
-      <c r="AP124" s="8" t="s">
-        <v>732</v>
-      </c>
     </row>
-    <row r="125" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A125" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D125,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D125,[6]DME!$D$2:$D$52,0))),"")</f>
         <v/>
@@ -30338,11 +29952,8 @@
       <c r="AO125" s="9">
         <v>46205</v>
       </c>
-      <c r="AP125" s="8" t="s">
-        <v>734</v>
-      </c>
     </row>
-    <row r="126" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A126" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]BH!$A$2:$A$17,MATCH($D126,[1]BH!$D$2:$D$17,0))="","",INDEX([1]BH!$A$2:$A$17,MATCH($D126,[1]BH!$D$2:$D$17,0))),"")</f>
         <v>PAID</v>
@@ -30461,11 +30072,8 @@
       <c r="AO126" s="9">
         <v>46057</v>
       </c>
-      <c r="AP126" s="8" t="s">
-        <v>739</v>
-      </c>
     </row>
-    <row r="127" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A127" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]DME!$A$2:$A$8,MATCH($D127,[1]DME!$D$2:$D$8,0))="","",INDEX([1]DME!$A$2:$A$8,MATCH($D127,[1]DME!$D$2:$D$8,0))),"")</f>
         <v>Denied</v>
@@ -30586,11 +30194,8 @@
       <c r="AO127" s="9">
         <v>46036</v>
       </c>
-      <c r="AP127" s="8" t="s">
-        <v>745</v>
-      </c>
     </row>
-    <row r="128" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A128" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]DME!$A$2:$A$8,MATCH($D128,[1]DME!$D$2:$D$8,0))="","",INDEX([1]DME!$A$2:$A$8,MATCH($D128,[1]DME!$D$2:$D$8,0))),"")</f>
         <v/>
@@ -30709,11 +30314,8 @@
       <c r="AO128" s="9">
         <v>46036</v>
       </c>
-      <c r="AP128" s="8" t="s">
-        <v>749</v>
-      </c>
     </row>
-    <row r="129" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A129" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]GAE!$A$2:$A$12,MATCH($D129,[1]GAE!$D$2:$D$12,0))="","",INDEX([1]GAE!$A$2:$A$12,MATCH($D129,[1]GAE!$D$2:$D$12,0))),"")</f>
         <v>Finalized</v>
@@ -30840,11 +30442,8 @@
       <c r="AO129" s="9">
         <v>46062</v>
       </c>
-      <c r="AP129" s="8" t="s">
-        <v>753</v>
-      </c>
     </row>
-    <row r="130" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A130" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]DME!$A$2:$A$8,MATCH($D130,[1]DME!$D$2:$D$8,0))="","",INDEX([1]DME!$A$2:$A$8,MATCH($D130,[1]DME!$D$2:$D$8,0))),"")</f>
         <v/>
@@ -30965,11 +30564,8 @@
       <c r="AO130" s="9">
         <v>46043</v>
       </c>
-      <c r="AP130" s="8" t="s">
-        <v>756</v>
-      </c>
     </row>
-    <row r="131" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A131" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]DME!$A$2:$A$8,MATCH($D131,[1]DME!$D$2:$D$8,0))="","",INDEX([1]DME!$A$2:$A$8,MATCH($D131,[1]DME!$D$2:$D$8,0))),"")</f>
         <v/>
@@ -31090,11 +30686,8 @@
       <c r="AO131" s="9">
         <v>46043</v>
       </c>
-      <c r="AP131" s="8" t="s">
-        <v>759</v>
-      </c>
     </row>
-    <row r="132" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A132" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]GAE!$A$2:$A$12,MATCH($D132,[1]GAE!$D$2:$D$12,0))="","",INDEX([1]GAE!$A$2:$A$12,MATCH($D132,[1]GAE!$D$2:$D$12,0))),"")</f>
         <v>Finalized</v>
@@ -31217,11 +30810,8 @@
       <c r="AO132" s="9">
         <v>46062</v>
       </c>
-      <c r="AP132" s="8" t="s">
-        <v>763</v>
-      </c>
     </row>
-    <row r="133" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A133" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]GAE!$A$2:$A$12,MATCH($D133,[1]GAE!$D$2:$D$12,0))="","",INDEX([1]GAE!$A$2:$A$12,MATCH($D133,[1]GAE!$D$2:$D$12,0))),"")</f>
         <v>Denied</v>
@@ -31350,11 +30940,8 @@
       <c r="AO133" s="9">
         <v>46062</v>
       </c>
-      <c r="AP133" s="8" t="s">
-        <v>767</v>
-      </c>
     </row>
-    <row r="134" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A134" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]GAE!$A$2:$A$12,MATCH($D134,[1]GAE!$D$2:$D$12,0))="","",INDEX([1]GAE!$A$2:$A$12,MATCH($D134,[1]GAE!$D$2:$D$12,0))),"")</f>
         <v>Finalized</v>
@@ -31483,11 +31070,8 @@
       <c r="AO134" s="9">
         <v>46062</v>
       </c>
-      <c r="AP134" s="8" t="s">
-        <v>771</v>
-      </c>
     </row>
-    <row r="135" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A135" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]BH!$A$2:$A$17,MATCH($D135,[1]BH!$D$2:$D$17,0))="","",INDEX([1]BH!$A$2:$A$17,MATCH($D135,[1]BH!$D$2:$D$17,0))),"")</f>
         <v>Pending</v>
@@ -31606,11 +31190,8 @@
       <c r="AO135" s="9">
         <v>46056</v>
       </c>
-      <c r="AP135" s="8" t="s">
-        <v>774</v>
-      </c>
     </row>
-    <row r="136" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A136" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]BH!$A$2:$A$17,MATCH($D136,[1]BH!$D$2:$D$17,0))="","",INDEX([1]BH!$A$2:$A$17,MATCH($D136,[1]BH!$D$2:$D$17,0))),"")</f>
         <v>Denied</v>
@@ -31727,11 +31308,8 @@
       <c r="AO136" s="9">
         <v>46056</v>
       </c>
-      <c r="AP136" s="8" t="s">
-        <v>776</v>
-      </c>
     </row>
-    <row r="137" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A137" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]GAE!$A$2:$A$12,MATCH($D137,[1]GAE!$D$2:$D$12,0))="","",INDEX([1]GAE!$A$2:$A$12,MATCH($D137,[1]GAE!$D$2:$D$12,0))),"")</f>
         <v>Finalized</v>
@@ -31860,11 +31438,8 @@
       <c r="AO137" s="9">
         <v>46062</v>
       </c>
-      <c r="AP137" s="8" t="s">
-        <v>780</v>
-      </c>
     </row>
-    <row r="138" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A138" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]GAE!$A$2:$A$12,MATCH($D138,[1]GAE!$D$2:$D$12,0))="","",INDEX([1]GAE!$A$2:$A$12,MATCH($D138,[1]GAE!$D$2:$D$12,0))),"")</f>
         <v>Denied</v>
@@ -31991,11 +31566,8 @@
       <c r="AO138" s="9">
         <v>46063</v>
       </c>
-      <c r="AP138" s="8" t="s">
-        <v>785</v>
-      </c>
     </row>
-    <row r="139" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A139" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]BH!$A$2:$A$17,MATCH($D139,[1]BH!$D$2:$D$17,0))="","",INDEX([1]BH!$A$2:$A$17,MATCH($D139,[1]BH!$D$2:$D$17,0))),"")</f>
         <v>Pending</v>
@@ -32114,11 +31686,8 @@
       <c r="AO139" s="9">
         <v>46057</v>
       </c>
-      <c r="AP139" s="8" t="s">
-        <v>788</v>
-      </c>
     </row>
-    <row r="140" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A140" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]DME!$A$2:$A$8,MATCH($D140,[1]DME!$D$2:$D$8,0))="","",INDEX([1]DME!$A$2:$A$8,MATCH($D140,[1]DME!$D$2:$D$8,0))),"")</f>
         <v/>
@@ -32241,11 +31810,8 @@
       <c r="AO140" s="9">
         <v>46183</v>
       </c>
-      <c r="AP140" s="8" t="s">
-        <v>790</v>
-      </c>
     </row>
-    <row r="141" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A141" s="5" t="str">
         <f>IFERROR(IF(INDEX([3]GAE!$A$2:$A$6,MATCH($D141,[3]GAE!$D$2:$D$6,0))="","",INDEX([3]GAE!$A$2:$A$6,MATCH($D141,[3]GAE!$D$2:$D$6,0))),"")</f>
         <v>Received</v>
@@ -32374,11 +31940,8 @@
       <c r="AO141" s="9">
         <v>46064</v>
       </c>
-      <c r="AP141" s="8" t="s">
-        <v>793</v>
-      </c>
     </row>
-    <row r="142" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A142" s="5" t="str">
         <f>IFERROR(IF(INDEX([3]GAE!$A$2:$A$6,MATCH($D142,[3]GAE!$D$2:$D$6,0))="","",INDEX([3]GAE!$A$2:$A$6,MATCH($D142,[3]GAE!$D$2:$D$6,0))),"")</f>
         <v>Denied</v>
@@ -32505,11 +32068,8 @@
       <c r="AO142" s="9">
         <v>46064</v>
       </c>
-      <c r="AP142" s="8" t="s">
-        <v>799</v>
-      </c>
     </row>
-    <row r="143" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A143" s="5" t="str">
         <f>IFERROR(IF(INDEX([3]US!$A$2:$A$6,MATCH($D143,[3]US!$D$2:$D$6,0))="","",INDEX([3]US!$A$2:$A$6,MATCH($D143,[3]US!$D$2:$D$6,0))),"")</f>
         <v>PAID</v>
@@ -32634,11 +32194,8 @@
       <c r="AO143" s="9">
         <v>46072</v>
       </c>
-      <c r="AP143" s="8" t="s">
-        <v>803</v>
-      </c>
     </row>
-    <row r="144" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A144" s="5" t="str">
         <f>IFERROR(IF(INDEX([3]GAE!$A$2:$A$6,MATCH($D144,[3]GAE!$D$2:$D$6,0))="","",INDEX([3]GAE!$A$2:$A$6,MATCH($D144,[3]GAE!$D$2:$D$6,0))),"")</f>
         <v>Denied</v>
@@ -32759,11 +32316,8 @@
       <c r="AO144" s="9">
         <v>46065</v>
       </c>
-      <c r="AP144" s="8" t="s">
-        <v>807</v>
-      </c>
     </row>
-    <row r="145" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A145" s="5" t="str">
         <f>IFERROR(IF(INDEX([3]DME!$A$2:$A$12,MATCH($D145,[3]DME!$D$2:$D$12,0))="","",INDEX([3]DME!$A$2:$A$12,MATCH($D145,[3]DME!$D$2:$D$12,0))),"")</f>
         <v>Denied</v>
@@ -32884,11 +32438,8 @@
       <c r="AO145" s="9">
         <v>46099</v>
       </c>
-      <c r="AP145" s="8" t="s">
-        <v>809</v>
-      </c>
     </row>
-    <row r="146" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A146" s="5" t="str">
         <f>IFERROR(IF(INDEX([3]DME!$A$2:$A$12,MATCH($D146,[3]DME!$D$2:$D$12,0))="","",INDEX([3]DME!$A$2:$A$12,MATCH($D146,[3]DME!$D$2:$D$12,0))),"")</f>
         <v>Denied</v>
@@ -33007,11 +32558,8 @@
       <c r="AO146" s="9">
         <v>46105</v>
       </c>
-      <c r="AP146" s="8" t="s">
-        <v>811</v>
-      </c>
     </row>
-    <row r="147" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A147" s="5" t="str">
         <f>IFERROR(IF(INDEX([3]US!$A$2:$A$6,MATCH($D147,[3]US!$D$2:$D$6,0))="","",INDEX([3]US!$A$2:$A$6,MATCH($D147,[3]US!$D$2:$D$6,0))),"")</f>
         <v>PAID</v>
@@ -33130,11 +32678,8 @@
       <c r="AO147" s="9">
         <v>46119</v>
       </c>
-      <c r="AP147" s="8" t="s">
-        <v>815</v>
-      </c>
     </row>
-    <row r="148" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A148" s="5" t="str">
         <f>IFERROR(IF(INDEX([3]DME!$A$2:$A$12,MATCH($D148,[3]DME!$D$2:$D$12,0))="","",INDEX([3]DME!$A$2:$A$12,MATCH($D148,[3]DME!$D$2:$D$12,0))),"")</f>
         <v>Denied</v>
@@ -33259,11 +32804,8 @@
       <c r="AO148" s="9">
         <v>46077</v>
       </c>
-      <c r="AP148" s="8" t="s">
-        <v>817</v>
-      </c>
     </row>
-    <row r="149" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A149" s="5" t="str">
         <f>IFERROR(IF(INDEX([3]DME!$A$2:$A$12,MATCH($D149,[3]DME!$D$2:$D$12,0))="","",INDEX([3]DME!$A$2:$A$12,MATCH($D149,[3]DME!$D$2:$D$12,0))),"")</f>
         <v>Denied</v>
@@ -33390,11 +32932,8 @@
       <c r="AO149" s="9">
         <v>46080</v>
       </c>
-      <c r="AP149" s="8" t="s">
-        <v>824</v>
-      </c>
     </row>
-    <row r="150" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A150" s="5" t="str">
         <f>IFERROR(IF(INDEX([3]GAE!$A$2:$A$6,MATCH($D150,[3]GAE!$D$2:$D$6,0))="","",INDEX([3]GAE!$A$2:$A$6,MATCH($D150,[3]GAE!$D$2:$D$6,0))),"")</f>
         <v>Denied</v>
@@ -33521,11 +33060,8 @@
       <c r="AO150" s="9">
         <v>46090</v>
       </c>
-      <c r="AP150" s="8" t="s">
-        <v>826</v>
-      </c>
     </row>
-    <row r="151" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A151" s="5" t="str">
         <f>IFERROR(IF(INDEX([3]DME!$A$2:$A$12,MATCH($D151,[3]DME!$D$2:$D$12,0))="","",INDEX([3]DME!$A$2:$A$12,MATCH($D151,[3]DME!$D$2:$D$12,0))),"")</f>
         <v>PAID</v>
@@ -33648,11 +33184,8 @@
       <c r="AO151" s="9">
         <v>46099</v>
       </c>
-      <c r="AP151" s="8" t="s">
-        <v>830</v>
-      </c>
     </row>
-    <row r="152" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A152" s="5" t="str">
         <f>IFERROR(IF(INDEX([3]ORTHO!$A$2:$A$11,MATCH($D152,[3]ORTHO!$D$2:$D$11,0))="","",INDEX([3]ORTHO!$A$2:$A$11,MATCH($D152,[3]ORTHO!$D$2:$D$11,0))),"")</f>
         <v>Finalized</v>
@@ -33773,11 +33306,8 @@
       <c r="AO152" s="9">
         <v>46072</v>
       </c>
-      <c r="AP152" s="8" t="s">
-        <v>833</v>
-      </c>
     </row>
-    <row r="153" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A153" s="5" t="str">
         <f>IFERROR(IF(INDEX([3]US!$A$2:$A$6,MATCH($D153,[3]US!$D$2:$D$6,0))="","",INDEX([3]US!$A$2:$A$6,MATCH($D153,[3]US!$D$2:$D$6,0))),"")</f>
         <v>PAID</v>
@@ -33896,11 +33426,8 @@
       <c r="AO153" s="9">
         <v>46076</v>
       </c>
-      <c r="AP153" s="8" t="s">
-        <v>835</v>
-      </c>
     </row>
-    <row r="154" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A154" s="5" t="str">
         <f>IFERROR(IF(INDEX([3]DME!$A$2:$A$12,MATCH($D154,[3]DME!$D$2:$D$12,0))="","",INDEX([3]DME!$A$2:$A$12,MATCH($D154,[3]DME!$D$2:$D$12,0))),"")</f>
         <v>Denied</v>
@@ -34019,11 +33546,8 @@
       <c r="AO154" s="9">
         <v>46093</v>
       </c>
-      <c r="AP154" s="8" t="s">
-        <v>840</v>
-      </c>
     </row>
-    <row r="155" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A155" s="5" t="str">
         <f>IFERROR(IF(INDEX([3]US!$A$2:$A$6,MATCH($D155,[3]US!$D$2:$D$6,0))="","",INDEX([3]US!$A$2:$A$6,MATCH($D155,[3]US!$D$2:$D$6,0))),"")</f>
         <v>PAID</v>
@@ -34142,11 +33666,8 @@
       <c r="AO155" s="9">
         <v>46119</v>
       </c>
-      <c r="AP155" s="8" t="s">
-        <v>841</v>
-      </c>
     </row>
-    <row r="156" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A156" s="5" t="str">
         <f>IFERROR(IF(INDEX([3]ORTHO!$A$2:$A$11,MATCH($D156,[3]ORTHO!$D$2:$D$11,0))="","",INDEX([3]ORTHO!$A$2:$A$11,MATCH($D156,[3]ORTHO!$D$2:$D$11,0))),"")</f>
         <v>Pending</v>
@@ -34265,11 +33786,8 @@
       <c r="AO156" s="9">
         <v>46077</v>
       </c>
-      <c r="AP156" s="8" t="s">
-        <v>843</v>
-      </c>
     </row>
-    <row r="157" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A157" s="5" t="str">
         <f>IFERROR(IF(INDEX([3]DME!$A$2:$A$12,MATCH($D157,[3]DME!$D$2:$D$12,0))="","",INDEX([3]DME!$A$2:$A$12,MATCH($D157,[3]DME!$D$2:$D$12,0))),"")</f>
         <v>Denied</v>
@@ -34390,11 +33908,8 @@
       <c r="AO157" s="9">
         <v>46085</v>
       </c>
-      <c r="AP157" s="8" t="s">
-        <v>848</v>
-      </c>
     </row>
-    <row r="158" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A158" s="5" t="str">
         <f>IFERROR(IF(INDEX([3]ORTHO!$A$2:$A$11,MATCH($D158,[3]ORTHO!$D$2:$D$11,0))="","",INDEX([3]ORTHO!$A$2:$A$11,MATCH($D158,[3]ORTHO!$D$2:$D$11,0))),"")</f>
         <v>Denied</v>
@@ -34521,11 +34036,8 @@
       <c r="AO158" s="9">
         <v>46093</v>
       </c>
-      <c r="AP158" s="8" t="s">
-        <v>853</v>
-      </c>
     </row>
-    <row r="159" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A159" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]BH!$A$2:$A$32,MATCH($D159,[2]BH!$D$2:$D$32,0))="","",INDEX([2]BH!$A$2:$A$32,MATCH($D159,[2]BH!$D$2:$D$32,0))),"")</f>
         <v>Finalized</v>
@@ -34644,11 +34156,8 @@
       <c r="AO159" s="9">
         <v>46119</v>
       </c>
-      <c r="AP159" s="8" t="s">
-        <v>856</v>
-      </c>
     </row>
-    <row r="160" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A160" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]ORTHO!$A$2:$A$16,MATCH($D160,[2]ORTHO!$D$2:$D$16,0))="","",INDEX([2]ORTHO!$A$2:$A$16,MATCH($D160,[2]ORTHO!$D$2:$D$16,0))),"")</f>
         <v>Denied</v>
@@ -34767,11 +34276,8 @@
       <c r="AO160" s="9">
         <v>46105</v>
       </c>
-      <c r="AP160" s="8" t="s">
-        <v>859</v>
-      </c>
     </row>
-    <row r="161" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A161" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]DME!$A$2:$A$11,MATCH($D161,[2]DME!$D$2:$D$11,0))="","",INDEX([2]DME!$A$2:$A$11,MATCH($D161,[2]DME!$D$2:$D$11,0))),"")</f>
         <v/>
@@ -34890,11 +34396,8 @@
       <c r="AO161" s="9">
         <v>46099</v>
       </c>
-      <c r="AP161" s="8" t="s">
-        <v>863</v>
-      </c>
     </row>
-    <row r="162" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A162" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]ORTHO!$A$2:$A$16,MATCH($D162,[2]ORTHO!$D$2:$D$16,0))="","",INDEX([2]ORTHO!$A$2:$A$16,MATCH($D162,[2]ORTHO!$D$2:$D$16,0))),"")</f>
         <v>Denied</v>
@@ -35017,11 +34520,8 @@
       <c r="AO162" s="9">
         <v>46197</v>
       </c>
-      <c r="AP162" s="8" t="s">
-        <v>865</v>
-      </c>
     </row>
-    <row r="163" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A163" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]US!$A$2:$A$15,MATCH($D163,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$A$2:$A$15,MATCH($D163,[2]US!$D$2:$D$15,0))),"")</f>
         <v/>
@@ -35142,11 +34642,8 @@
       <c r="AO163" s="9">
         <v>46106</v>
       </c>
-      <c r="AP163" s="8" t="s">
-        <v>870</v>
-      </c>
     </row>
-    <row r="164" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A164" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]BH!$A$2:$A$32,MATCH($D164,[2]BH!$D$2:$D$32,0))="","",INDEX([2]BH!$A$2:$A$32,MATCH($D164,[2]BH!$D$2:$D$32,0))),"")</f>
         <v>Finalized</v>
@@ -35265,11 +34762,8 @@
       <c r="AO164" s="9">
         <v>46119</v>
       </c>
-      <c r="AP164" s="8" t="s">
-        <v>872</v>
-      </c>
     </row>
-    <row r="165" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A165" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]BH!$A$2:$A$32,MATCH($D165,[2]BH!$D$2:$D$32,0))="","",INDEX([2]BH!$A$2:$A$32,MATCH($D165,[2]BH!$D$2:$D$32,0))),"")</f>
         <v>Rejected</v>
@@ -35384,11 +34878,8 @@
       <c r="AO165" s="9">
         <v>46119</v>
       </c>
-      <c r="AP165" s="8" t="s">
-        <v>874</v>
-      </c>
     </row>
-    <row r="166" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A166" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]BH!$A$2:$A$32,MATCH($D166,[2]BH!$D$2:$D$32,0))="","",INDEX([2]BH!$A$2:$A$32,MATCH($D166,[2]BH!$D$2:$D$32,0))),"")</f>
         <v>Finalized</v>
@@ -35507,11 +34998,8 @@
       <c r="AO166" s="9">
         <v>46119</v>
       </c>
-      <c r="AP166" s="8" t="s">
-        <v>876</v>
-      </c>
     </row>
-    <row r="167" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A167" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]BH!$A$2:$A$32,MATCH($D167,[2]BH!$D$2:$D$32,0))="","",INDEX([2]BH!$A$2:$A$32,MATCH($D167,[2]BH!$D$2:$D$32,0))),"")</f>
         <v>Finalized</v>
@@ -35630,11 +35118,8 @@
       <c r="AO167" s="9">
         <v>46119</v>
       </c>
-      <c r="AP167" s="8" t="s">
-        <v>879</v>
-      </c>
     </row>
-    <row r="168" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A168" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]DME!$A$2:$A$11,MATCH($D168,[2]DME!$D$2:$D$11,0))="","",INDEX([2]DME!$A$2:$A$11,MATCH($D168,[2]DME!$D$2:$D$11,0))),"")</f>
         <v/>
@@ -35755,11 +35240,8 @@
       <c r="AO168" s="9">
         <v>46099</v>
       </c>
-      <c r="AP168" s="8" t="s">
-        <v>882</v>
-      </c>
     </row>
-    <row r="169" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A169" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]DME!$A$2:$A$11,MATCH($D169,[2]DME!$D$2:$D$11,0))="","",INDEX([2]DME!$A$2:$A$11,MATCH($D169,[2]DME!$D$2:$D$11,0))),"")</f>
         <v>Received</v>
@@ -35880,11 +35362,8 @@
       <c r="AO169" s="9">
         <v>46115</v>
       </c>
-      <c r="AP169" s="8" t="s">
-        <v>885</v>
-      </c>
     </row>
-    <row r="170" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A170" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]ORTHO!$A$2:$A$16,MATCH($D170,[2]ORTHO!$D$2:$D$16,0))="","",INDEX([2]ORTHO!$A$2:$A$16,MATCH($D170,[2]ORTHO!$D$2:$D$16,0))),"")</f>
         <v>Pending</v>
@@ -36003,11 +35482,8 @@
       <c r="AO170" s="9">
         <v>46101</v>
       </c>
-      <c r="AP170" s="8" t="s">
-        <v>889</v>
-      </c>
     </row>
-    <row r="171" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A171" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]DME!$A$2:$A$11,MATCH($D171,[2]DME!$D$2:$D$11,0))="","",INDEX([2]DME!$A$2:$A$11,MATCH($D171,[2]DME!$D$2:$D$11,0))),"")</f>
         <v/>
@@ -36130,11 +35606,8 @@
       <c r="AO171" s="9">
         <v>46118</v>
       </c>
-      <c r="AP171" s="8" t="s">
-        <v>892</v>
-      </c>
     </row>
-    <row r="172" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A172" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]ORTHO!$A$2:$A$16,MATCH($D172,[2]ORTHO!$D$2:$D$16,0))="","",INDEX([2]ORTHO!$A$2:$A$16,MATCH($D172,[2]ORTHO!$D$2:$D$16,0))),"")</f>
         <v>Denied</v>
@@ -36259,11 +35732,8 @@
       <c r="AO172" s="9">
         <v>46197</v>
       </c>
-      <c r="AP172" s="8" t="s">
-        <v>898</v>
-      </c>
     </row>
-    <row r="173" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A173" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]DME!$A$2:$A$11,MATCH($D173,[2]DME!$D$2:$D$11,0))="","",INDEX([2]DME!$A$2:$A$11,MATCH($D173,[2]DME!$D$2:$D$11,0))),"")</f>
         <v/>
@@ -36384,11 +35854,8 @@
       <c r="AO173" s="9">
         <v>46133</v>
       </c>
-      <c r="AP173" s="8" t="s">
-        <v>901</v>
-      </c>
     </row>
-    <row r="174" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A174" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]ORTHO!$A$2:$A$16,MATCH($D174,[2]ORTHO!$D$2:$D$16,0))="","",INDEX([2]ORTHO!$A$2:$A$16,MATCH($D174,[2]ORTHO!$D$2:$D$16,0))),"")</f>
         <v>Pending</v>
@@ -36507,11 +35974,8 @@
       <c r="AO174" s="9">
         <v>46107</v>
       </c>
-      <c r="AP174" s="8" t="s">
-        <v>903</v>
-      </c>
     </row>
-    <row r="175" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A175" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]BH!$A$2:$A$32,MATCH($D175,[2]BH!$D$2:$D$32,0))="","",INDEX([2]BH!$A$2:$A$32,MATCH($D175,[2]BH!$D$2:$D$32,0))),"")</f>
         <v>Pending</v>
@@ -36630,11 +36094,8 @@
       <c r="AO175" s="9">
         <v>46119</v>
       </c>
-      <c r="AP175" s="8" t="s">
-        <v>905</v>
-      </c>
     </row>
-    <row r="176" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A176" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]ORTHO!$A$2:$A$16,MATCH($D176,[2]ORTHO!$D$2:$D$16,0))="","",INDEX([2]ORTHO!$A$2:$A$16,MATCH($D176,[2]ORTHO!$D$2:$D$16,0))),"")</f>
         <v>Pending</v>
@@ -36755,11 +36216,8 @@
       <c r="AO176" s="9">
         <v>46112</v>
       </c>
-      <c r="AP176" s="8" t="s">
-        <v>190</v>
-      </c>
     </row>
-    <row r="177" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A177" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]BH!$A$2:$A$32,MATCH($D177,[2]BH!$D$2:$D$32,0))="","",INDEX([2]BH!$A$2:$A$32,MATCH($D177,[2]BH!$D$2:$D$32,0))),"")</f>
         <v>Under Review</v>
@@ -36874,11 +36332,8 @@
       <c r="AO177" s="9">
         <v>46119</v>
       </c>
-      <c r="AP177" s="8" t="s">
-        <v>907</v>
-      </c>
     </row>
-    <row r="178" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A178" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]BH!$A$2:$A$32,MATCH($D178,[2]BH!$D$2:$D$32,0))="","",INDEX([2]BH!$A$2:$A$32,MATCH($D178,[2]BH!$D$2:$D$32,0))),"")</f>
         <v>Denied</v>
@@ -36995,11 +36450,8 @@
       <c r="AO178" s="9">
         <v>46119</v>
       </c>
-      <c r="AP178" s="8" t="s">
-        <v>909</v>
-      </c>
     </row>
-    <row r="179" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A179" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]DME!$A$2:$A$11,MATCH($D179,[2]DME!$D$2:$D$11,0))="","",INDEX([2]DME!$A$2:$A$11,MATCH($D179,[2]DME!$D$2:$D$11,0))),"")</f>
         <v/>
@@ -37120,11 +36572,8 @@
       <c r="AO179" s="9">
         <v>46133</v>
       </c>
-      <c r="AP179" s="8" t="s">
-        <v>911</v>
-      </c>
     </row>
-    <row r="180" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A180" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]DME!$A$2:$A$11,MATCH($D180,[2]DME!$D$2:$D$11,0))="","",INDEX([2]DME!$A$2:$A$11,MATCH($D180,[2]DME!$D$2:$D$11,0))),"")</f>
         <v/>
@@ -37247,11 +36696,8 @@
       <c r="AO180" s="9">
         <v>46118</v>
       </c>
-      <c r="AP180" s="8" t="s">
-        <v>914</v>
-      </c>
     </row>
-    <row r="181" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A181" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]US!$A$2:$A$15,MATCH($D181,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$A$2:$A$15,MATCH($D181,[2]US!$D$2:$D$15,0))),"")</f>
         <v/>
@@ -37372,11 +36818,8 @@
       <c r="AO181" s="9">
         <v>46121</v>
       </c>
-      <c r="AP181" s="8" t="s">
-        <v>918</v>
-      </c>
     </row>
-    <row r="182" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A182" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]BH!$A$2:$A$12,MATCH($D182,[4]BH!$D$2:$D$12,0))="","",INDEX([4]BH!$A$2:$A$12,MATCH($D182,[4]BH!$D$2:$D$12,0))),"")</f>
         <v>Denied</v>
@@ -37493,11 +36936,8 @@
       <c r="AO182" s="9">
         <v>46153</v>
       </c>
-      <c r="AP182" s="8" t="s">
-        <v>920</v>
-      </c>
     </row>
-    <row r="183" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A183" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$A$2:$A$34,MATCH($D183,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$A$2:$A$34,MATCH($D183,[4]DME!$D$2:$D$34,0))),"")</f>
         <v/>
@@ -37620,11 +37060,8 @@
       <c r="AO183" s="9">
         <v>46121</v>
       </c>
-      <c r="AP183" s="8" t="s">
-        <v>924</v>
-      </c>
     </row>
-    <row r="184" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A184" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]ORTHO!$A$2:$A$21,MATCH($D184,[4]ORTHO!$D$2:$D$21,0))="","",INDEX([4]ORTHO!$A$2:$A$21,MATCH($D184,[4]ORTHO!$D$2:$D$21,0))),"")</f>
         <v>Denied</v>
@@ -37743,11 +37180,8 @@
       <c r="AO184" s="9">
         <v>46133</v>
       </c>
-      <c r="AP184" s="8" t="s">
-        <v>926</v>
-      </c>
     </row>
-    <row r="185" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A185" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]ORTHO!$A$2:$A$21,MATCH($D185,[4]ORTHO!$D$2:$D$21,0))="","",INDEX([4]ORTHO!$A$2:$A$21,MATCH($D185,[4]ORTHO!$D$2:$D$21,0))),"")</f>
         <v>Denied</v>
@@ -37866,11 +37300,8 @@
       <c r="AO185" s="9">
         <v>46133</v>
       </c>
-      <c r="AP185" s="8" t="s">
-        <v>928</v>
-      </c>
     </row>
-    <row r="186" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A186" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]US!$A$2:$A$23,MATCH($D186,[4]US!$D$2:$D$23,0))="","",INDEX([4]US!$A$2:$A$23,MATCH($D186,[4]US!$D$2:$D$23,0))),"")</f>
         <v>Denied</v>
@@ -37989,11 +37420,8 @@
       <c r="AO186" s="9">
         <v>46140</v>
       </c>
-      <c r="AP186" s="8" t="s">
-        <v>935</v>
-      </c>
     </row>
-    <row r="187" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A187" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$A$2:$A$34,MATCH($D187,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$A$2:$A$34,MATCH($D187,[4]DME!$D$2:$D$34,0))),"")</f>
         <v/>
@@ -38110,11 +37538,8 @@
       <c r="AO187" s="9">
         <v>46133</v>
       </c>
-      <c r="AP187" s="8" t="s">
-        <v>938</v>
-      </c>
     </row>
-    <row r="188" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A188" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$A$2:$A$34,MATCH($D188,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$A$2:$A$34,MATCH($D188,[4]DME!$D$2:$D$34,0))),"")</f>
         <v/>
@@ -38233,11 +37658,8 @@
       <c r="AO188" s="9">
         <v>46133</v>
       </c>
-      <c r="AP188" s="8" t="s">
-        <v>940</v>
-      </c>
     </row>
-    <row r="189" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A189" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$A$2:$A$34,MATCH($D189,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$A$2:$A$34,MATCH($D189,[4]DME!$D$2:$D$34,0))),"")</f>
         <v/>
@@ -38356,11 +37778,8 @@
       <c r="AO189" s="9">
         <v>46134</v>
       </c>
-      <c r="AP189" s="8" t="s">
-        <v>942</v>
-      </c>
     </row>
-    <row r="190" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A190" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$A$2:$A$34,MATCH($D190,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$A$2:$A$34,MATCH($D190,[4]DME!$D$2:$D$34,0))),"")</f>
         <v/>
@@ -38481,11 +37900,8 @@
       <c r="AO190" s="9">
         <v>46134</v>
       </c>
-      <c r="AP190" s="8" t="s">
-        <v>945</v>
-      </c>
     </row>
-    <row r="191" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A191" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]GAE!$A$2:$A$8,MATCH($D191,[4]GAE!$D$2:$D$8,0))="","",INDEX([4]GAE!$A$2:$A$8,MATCH($D191,[4]GAE!$D$2:$D$8,0))),"")</f>
         <v>Denied</v>
@@ -38612,11 +38028,8 @@
       <c r="AO191" s="9">
         <v>46152</v>
       </c>
-      <c r="AP191" s="8" t="s">
-        <v>948</v>
-      </c>
     </row>
-    <row r="192" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A192" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$A$2:$A$34,MATCH($D192,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$A$2:$A$34,MATCH($D192,[4]DME!$D$2:$D$34,0))),"")</f>
         <v>Under Review</v>
@@ -38735,11 +38148,8 @@
       <c r="AO192" s="9">
         <v>46143</v>
       </c>
-      <c r="AP192" s="8" t="s">
-        <v>950</v>
-      </c>
     </row>
-    <row r="193" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A193" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]ORTHO!$A$2:$A$21,MATCH($D193,[4]ORTHO!$D$2:$D$21,0))="","",INDEX([4]ORTHO!$A$2:$A$21,MATCH($D193,[4]ORTHO!$D$2:$D$21,0))),"")</f>
         <v>Denied</v>
@@ -38856,11 +38266,8 @@
       <c r="AO193" s="9">
         <v>46133</v>
       </c>
-      <c r="AP193" s="8" t="s">
-        <v>953</v>
-      </c>
     </row>
-    <row r="194" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A194" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]ORTHO!$A$2:$A$21,MATCH($D194,[4]ORTHO!$D$2:$D$21,0))="","",INDEX([4]ORTHO!$A$2:$A$21,MATCH($D194,[4]ORTHO!$D$2:$D$21,0))),"")</f>
         <v>Pending</v>
@@ -38979,11 +38386,8 @@
       <c r="AO194" s="9">
         <v>46134</v>
       </c>
-      <c r="AP194" s="8" t="s">
-        <v>956</v>
-      </c>
     </row>
-    <row r="195" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A195" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$A$2:$A$34,MATCH($D195,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$A$2:$A$34,MATCH($D195,[4]DME!$D$2:$D$34,0))),"")</f>
         <v/>
@@ -39102,11 +38506,8 @@
       <c r="AO195" s="9">
         <v>46134</v>
       </c>
-      <c r="AP195" s="8" t="s">
-        <v>957</v>
-      </c>
     </row>
-    <row r="196" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A196" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$A$2:$A$34,MATCH($D196,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$A$2:$A$34,MATCH($D196,[4]DME!$D$2:$D$34,0))),"")</f>
         <v/>
@@ -39225,11 +38626,8 @@
       <c r="AO196" s="9">
         <v>46198</v>
       </c>
-      <c r="AP196" s="8" t="s">
-        <v>959</v>
-      </c>
     </row>
-    <row r="197" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A197" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]BH!$A$2:$A$12,MATCH($D197,[4]BH!$D$2:$D$12,0))="","",INDEX([4]BH!$A$2:$A$12,MATCH($D197,[4]BH!$D$2:$D$12,0))),"")</f>
         <v>Pending</v>
@@ -39348,11 +38746,8 @@
       <c r="AO197" s="9">
         <v>46153</v>
       </c>
-      <c r="AP197" s="8" t="s">
-        <v>962</v>
-      </c>
     </row>
-    <row r="198" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A198" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]US!$A$2:$A$22,MATCH($D198,[6]US!$D$2:$D$22,0))="","",INDEX([6]US!$A$2:$A$22,MATCH($D198,[6]US!$D$2:$D$22,0))),"")</f>
         <v/>
@@ -39473,9 +38868,8 @@
       <c r="AO198" s="9">
         <v>46195</v>
       </c>
-      <c r="AP198" s="8"/>
     </row>
-    <row r="199" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A199" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]US!$A$2:$A$23,MATCH($D199,[4]US!$D$2:$D$23,0))="","",INDEX([4]US!$A$2:$A$23,MATCH($D199,[4]US!$D$2:$D$23,0))),"")</f>
         <v>Pending</v>
@@ -39598,11 +38992,8 @@
       <c r="AO199" s="9">
         <v>46141</v>
       </c>
-      <c r="AP199" s="8" t="s">
-        <v>964</v>
-      </c>
     </row>
-    <row r="200" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A200" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]US!$A$2:$A$23,MATCH($D200,[4]US!$D$2:$D$23,0))="","",INDEX([4]US!$A$2:$A$23,MATCH($D200,[4]US!$D$2:$D$23,0))),"")</f>
         <v>Pending</v>
@@ -39725,11 +39116,8 @@
       <c r="AO200" s="9">
         <v>46141</v>
       </c>
-      <c r="AP200" s="8" t="s">
-        <v>967</v>
-      </c>
     </row>
-    <row r="201" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A201" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]ORTHO!$A$2:$A$21,MATCH($D201,[4]ORTHO!$D$2:$D$21,0))="","",INDEX([4]ORTHO!$A$2:$A$21,MATCH($D201,[4]ORTHO!$D$2:$D$21,0))),"")</f>
         <v>Denied</v>
@@ -39850,11 +39238,8 @@
       <c r="AO201" s="9">
         <v>46140</v>
       </c>
-      <c r="AP201" s="8" t="s">
-        <v>969</v>
-      </c>
     </row>
-    <row r="202" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A202" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]BH!$A$2:$A$82,MATCH($D202,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$A$2:$A$82,MATCH($D202,[6]BH!$D$2:$D$82,0))),"")</f>
         <v/>
@@ -39975,9 +39360,8 @@
       <c r="AO202" s="9">
         <v>46217</v>
       </c>
-      <c r="AP202" s="8"/>
     </row>
-    <row r="203" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A203" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$A$2:$A$34,MATCH($D203,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$A$2:$A$34,MATCH($D203,[4]DME!$D$2:$D$34,0))),"")</f>
         <v/>
@@ -40096,11 +39480,8 @@
       <c r="AO203" s="9">
         <v>46140</v>
       </c>
-      <c r="AP203" s="8" t="s">
-        <v>970</v>
-      </c>
     </row>
-    <row r="204" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A204" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]BH!$A$2:$A$82,MATCH($D204,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$A$2:$A$82,MATCH($D204,[6]BH!$D$2:$D$82,0))),"")</f>
         <v/>
@@ -40219,9 +39600,8 @@
       <c r="AO204" s="9">
         <v>46217</v>
       </c>
-      <c r="AP204" s="8"/>
     </row>
-    <row r="205" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A205" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]US!$A$2:$A$23,MATCH($D205,[4]US!$D$2:$D$23,0))="","",INDEX([4]US!$A$2:$A$23,MATCH($D205,[4]US!$D$2:$D$23,0))),"")</f>
         <v>Denied</v>
@@ -40338,11 +39718,8 @@
       <c r="AO205" s="9">
         <v>46147</v>
       </c>
-      <c r="AP205" s="8" t="s">
-        <v>974</v>
-      </c>
     </row>
-    <row r="206" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A206" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]US!$A$2:$A$23,MATCH($D206,[4]US!$D$2:$D$23,0))="","",INDEX([4]US!$A$2:$A$23,MATCH($D206,[4]US!$D$2:$D$23,0))),"")</f>
         <v>Denied</v>
@@ -40459,11 +39836,8 @@
       <c r="AO206" s="9">
         <v>46147</v>
       </c>
-      <c r="AP206" s="8" t="s">
-        <v>977</v>
-      </c>
     </row>
-    <row r="207" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A207" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]US!$A$2:$A$23,MATCH($D207,[4]US!$D$2:$D$23,0))="","",INDEX([4]US!$A$2:$A$23,MATCH($D207,[4]US!$D$2:$D$23,0))),"")</f>
         <v>Denied</v>
@@ -40580,11 +39954,8 @@
       <c r="AO207" s="9">
         <v>46147</v>
       </c>
-      <c r="AP207" s="8" t="s">
-        <v>980</v>
-      </c>
     </row>
-    <row r="208" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A208" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$A$2:$A$34,MATCH($D208,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$A$2:$A$34,MATCH($D208,[4]DME!$D$2:$D$34,0))),"")</f>
         <v>Finalized</v>
@@ -40707,11 +40078,8 @@
       <c r="AO208" s="9">
         <v>46153</v>
       </c>
-      <c r="AP208" s="8" t="s">
-        <v>987</v>
-      </c>
     </row>
-    <row r="209" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A209" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]ORTHO!$A$2:$A$24,MATCH($D209,[5]ORTHO!$D$2:$D$24,0))="","",INDEX([5]ORTHO!$A$2:$A$24,MATCH($D209,[5]ORTHO!$D$2:$D$24,0))),"")</f>
         <v>Denied</v>
@@ -40830,11 +40198,8 @@
       <c r="AO209" s="9">
         <v>46155</v>
       </c>
-      <c r="AP209" s="8" t="s">
-        <v>988</v>
-      </c>
     </row>
-    <row r="210" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A210" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]BH!$A$2:$A$33,MATCH($D210,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$A$2:$A$33,MATCH($D210,[5]BH!$D$2:$D$33,0))),"")</f>
         <v>Finalized</v>
@@ -40949,11 +40314,8 @@
       <c r="AO210" s="9">
         <v>46182</v>
       </c>
-      <c r="AP210" s="8" t="s">
-        <v>991</v>
-      </c>
     </row>
-    <row r="211" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A211" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]BH!$A$2:$A$33,MATCH($D211,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$A$2:$A$33,MATCH($D211,[5]BH!$D$2:$D$33,0))),"")</f>
         <v>Denied</v>
@@ -41070,11 +40432,8 @@
       <c r="AO211" s="9">
         <v>46182</v>
       </c>
-      <c r="AP211" s="8" t="s">
-        <v>993</v>
-      </c>
     </row>
-    <row r="212" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A212" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D212,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D212,[6]DME!$D$2:$D$52,0))),"")</f>
         <v/>
@@ -41191,9 +40550,8 @@
       <c r="AO212" s="9">
         <v>46274</v>
       </c>
-      <c r="AP212" s="8"/>
     </row>
-    <row r="213" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A213" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]ORTHO!$A$2:$A$24,MATCH($D213,[5]ORTHO!$D$2:$D$24,0))="","",INDEX([5]ORTHO!$A$2:$A$24,MATCH($D213,[5]ORTHO!$D$2:$D$24,0))),"")</f>
         <v/>
@@ -41316,11 +40674,8 @@
       <c r="AO213" s="9">
         <v>46155</v>
       </c>
-      <c r="AP213" s="8" t="s">
-        <v>996</v>
-      </c>
     </row>
-    <row r="214" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A214" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]BH!$A$2:$A$33,MATCH($D214,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$A$2:$A$33,MATCH($D214,[5]BH!$D$2:$D$33,0))),"")</f>
         <v>Pending</v>
@@ -41439,11 +40794,8 @@
       <c r="AO214" s="9">
         <v>46182</v>
       </c>
-      <c r="AP214" s="8" t="s">
-        <v>998</v>
-      </c>
     </row>
-    <row r="215" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A215" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]DME!$A$2:$A$35,MATCH($D215,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$A$2:$A$35,MATCH($D215,[5]DME!$D$2:$D$35,0))),"")</f>
         <v>Denied</v>
@@ -41562,11 +40914,8 @@
       <c r="AO215" s="9">
         <v>46155</v>
       </c>
-      <c r="AP215" s="8" t="s">
-        <v>1000</v>
-      </c>
     </row>
-    <row r="216" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A216" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]DME!$A$2:$A$35,MATCH($D216,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$A$2:$A$35,MATCH($D216,[5]DME!$D$2:$D$35,0))),"")</f>
         <v>PAID</v>
@@ -41687,11 +41036,8 @@
       <c r="AO216" s="9">
         <v>46155</v>
       </c>
-      <c r="AP216" s="8" t="s">
-        <v>1003</v>
-      </c>
     </row>
-    <row r="217" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A217" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]US!$A$2:$A$19,MATCH($D217,[5]US!$D$2:$D$19,0))="","",INDEX([5]US!$A$2:$A$19,MATCH($D217,[5]US!$D$2:$D$19,0))),"")</f>
         <v>Denied</v>
@@ -41812,11 +41158,8 @@
       <c r="AO217" s="9">
         <v>46164</v>
       </c>
-      <c r="AP217" s="8" t="s">
-        <v>1005</v>
-      </c>
     </row>
-    <row r="218" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A218" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]BH!$A$2:$A$33,MATCH($D218,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$A$2:$A$33,MATCH($D218,[5]BH!$D$2:$D$33,0))),"")</f>
         <v>Finalized</v>
@@ -41935,11 +41278,8 @@
       <c r="AO218" s="9">
         <v>46181</v>
       </c>
-      <c r="AP218" s="8" t="s">
-        <v>1006</v>
-      </c>
     </row>
-    <row r="219" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A219" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]BH!$A$2:$A$33,MATCH($D219,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$A$2:$A$33,MATCH($D219,[5]BH!$D$2:$D$33,0))),"")</f>
         <v>PAID</v>
@@ -42056,11 +41396,8 @@
       <c r="AO219" s="9">
         <v>46182</v>
       </c>
-      <c r="AP219" s="8" t="s">
-        <v>1008</v>
-      </c>
     </row>
-    <row r="220" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A220" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]BH!$A$2:$A$33,MATCH($D220,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$A$2:$A$33,MATCH($D220,[5]BH!$D$2:$D$33,0))),"")</f>
         <v>Finalized</v>
@@ -42179,11 +41516,8 @@
       <c r="AO220" s="9">
         <v>46182</v>
       </c>
-      <c r="AP220" s="8" t="s">
-        <v>1009</v>
-      </c>
     </row>
-    <row r="221" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A221" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]DME!$A$2:$A$35,MATCH($D221,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$A$2:$A$35,MATCH($D221,[5]DME!$D$2:$D$35,0))),"")</f>
         <v>PAID</v>
@@ -42306,11 +41640,8 @@
       <c r="AO221" s="9">
         <v>46155</v>
       </c>
-      <c r="AP221" s="8" t="s">
-        <v>1011</v>
-      </c>
     </row>
-    <row r="222" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A222" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]DME!$A$2:$A$35,MATCH($D222,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$A$2:$A$35,MATCH($D222,[5]DME!$D$2:$D$35,0))),"")</f>
         <v>Denied</v>
@@ -42433,11 +41764,8 @@
       <c r="AO222" s="9">
         <v>46183</v>
       </c>
-      <c r="AP222" s="8" t="s">
-        <v>1012</v>
-      </c>
     </row>
-    <row r="223" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A223" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]ORTHO!$A$2:$A$24,MATCH($D223,[5]ORTHO!$D$2:$D$24,0))="","",INDEX([5]ORTHO!$A$2:$A$24,MATCH($D223,[5]ORTHO!$D$2:$D$24,0))),"")</f>
         <v>Denied</v>
@@ -42554,11 +41882,8 @@
       <c r="AO223" s="9">
         <v>46156</v>
       </c>
-      <c r="AP223" s="8" t="s">
-        <v>1014</v>
-      </c>
     </row>
-    <row r="224" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A224" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]GAE!$A$2:$A$7,MATCH($D224,[5]GAE!$D$2:$D$7,0))="","",INDEX([5]GAE!$A$2:$A$7,MATCH($D224,[5]GAE!$D$2:$D$7,0))),"")</f>
         <v>Denied</v>
@@ -42685,11 +42010,8 @@
       <c r="AO224" s="9">
         <v>46182</v>
       </c>
-      <c r="AP224" s="8" t="s">
-        <v>1018</v>
-      </c>
     </row>
-    <row r="225" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A225" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]US!$A$2:$A$19,MATCH($D225,[5]US!$D$2:$D$19,0))="","",INDEX([5]US!$A$2:$A$19,MATCH($D225,[5]US!$D$2:$D$19,0))),"")</f>
         <v>Denied</v>
@@ -42806,11 +42128,8 @@
       <c r="AO225" s="9">
         <v>46164</v>
       </c>
-      <c r="AP225" s="8" t="s">
-        <v>1020</v>
-      </c>
     </row>
-    <row r="226" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A226" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]BH!$A$2:$A$33,MATCH($D226,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$A$2:$A$33,MATCH($D226,[5]BH!$D$2:$D$33,0))),"")</f>
         <v>Pending</v>
@@ -42929,11 +42248,8 @@
       <c r="AO226" s="9">
         <v>46182</v>
       </c>
-      <c r="AP226" s="8" t="s">
-        <v>1022</v>
-      </c>
     </row>
-    <row r="227" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A227" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]ORTHO!$A$2:$A$24,MATCH($D227,[5]ORTHO!$D$2:$D$24,0))="","",INDEX([5]ORTHO!$A$2:$A$24,MATCH($D227,[5]ORTHO!$D$2:$D$24,0))),"")</f>
         <v>Denied</v>
@@ -43052,11 +42368,8 @@
       <c r="AO227" s="9">
         <v>46160</v>
       </c>
-      <c r="AP227" s="8" t="s">
-        <v>1025</v>
-      </c>
     </row>
-    <row r="228" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A228" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]BH!$A$2:$A$82,MATCH($D228,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$A$2:$A$82,MATCH($D228,[6]BH!$D$2:$D$82,0))),"")</f>
         <v/>
@@ -43171,9 +42484,8 @@
       <c r="AO228" s="9">
         <v>46274</v>
       </c>
-      <c r="AP228" s="8"/>
     </row>
-    <row r="229" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A229" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]US!$A$2:$A$19,MATCH($D229,[5]US!$D$2:$D$19,0))="","",INDEX([5]US!$A$2:$A$19,MATCH($D229,[5]US!$D$2:$D$19,0))),"")</f>
         <v>Finalized</v>
@@ -43292,11 +42604,8 @@
       <c r="AO229" s="9">
         <v>46164</v>
       </c>
-      <c r="AP229" s="8" t="s">
-        <v>1027</v>
-      </c>
     </row>
-    <row r="230" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A230" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]DME!$A$2:$A$35,MATCH($D230,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$A$2:$A$35,MATCH($D230,[5]DME!$D$2:$D$35,0))),"")</f>
         <v>Pending</v>
@@ -43419,11 +42728,8 @@
       <c r="AO230" s="9">
         <v>46162</v>
       </c>
-      <c r="AP230" s="8" t="s">
-        <v>1028</v>
-      </c>
     </row>
-    <row r="231" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A231" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]DME!$A$2:$A$35,MATCH($D231,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$A$2:$A$35,MATCH($D231,[5]DME!$D$2:$D$35,0))),"")</f>
         <v>Finalized</v>
@@ -43544,11 +42850,8 @@
       <c r="AO231" s="9">
         <v>46210</v>
       </c>
-      <c r="AP231" s="8" t="s">
-        <v>1034</v>
-      </c>
     </row>
-    <row r="232" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A232" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]ORTHO!$A$2:$A$24,MATCH($D232,[5]ORTHO!$D$2:$D$24,0))="","",INDEX([5]ORTHO!$A$2:$A$24,MATCH($D232,[5]ORTHO!$D$2:$D$24,0))),"")</f>
         <v>Denied</v>
@@ -43669,11 +42972,8 @@
       <c r="AO232" s="9">
         <v>46160</v>
       </c>
-      <c r="AP232" s="8" t="s">
-        <v>1036</v>
-      </c>
     </row>
-    <row r="233" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A233" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]BH!$A$2:$A$33,MATCH($D233,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$A$2:$A$33,MATCH($D233,[5]BH!$D$2:$D$33,0))),"")</f>
         <v>Pending</v>
@@ -43792,11 +43092,8 @@
       <c r="AO233" s="9">
         <v>46182</v>
       </c>
-      <c r="AP233" s="8" t="s">
-        <v>1038</v>
-      </c>
     </row>
-    <row r="234" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A234" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]DME!$A$2:$A$35,MATCH($D234,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$A$2:$A$35,MATCH($D234,[5]DME!$D$2:$D$35,0))),"")</f>
         <v>Finalized</v>
@@ -43915,11 +43212,8 @@
       <c r="AO234" s="9">
         <v>46162</v>
       </c>
-      <c r="AP234" s="8" t="s">
-        <v>1042</v>
-      </c>
     </row>
-    <row r="235" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A235" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]GAE!$A$2:$A$7,MATCH($D235,[5]GAE!$D$2:$D$7,0))="","",INDEX([5]GAE!$A$2:$A$7,MATCH($D235,[5]GAE!$D$2:$D$7,0))),"")</f>
         <v>PAID</v>
@@ -44048,11 +43342,8 @@
       <c r="AO235" s="9">
         <v>46182</v>
       </c>
-      <c r="AP235" s="8" t="s">
-        <v>1045</v>
-      </c>
     </row>
-    <row r="236" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A236" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]DME!$A$2:$A$35,MATCH($D236,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$A$2:$A$35,MATCH($D236,[5]DME!$D$2:$D$35,0))),"")</f>
         <v>Finalized</v>
@@ -44173,11 +43464,8 @@
       <c r="AO236" s="9">
         <v>46183</v>
       </c>
-      <c r="AP236" s="8" t="s">
-        <v>1048</v>
-      </c>
     </row>
-    <row r="237" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A237" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]US!$A$2:$A$19,MATCH($D237,[5]US!$D$2:$D$19,0))="","",INDEX([5]US!$A$2:$A$19,MATCH($D237,[5]US!$D$2:$D$19,0))),"")</f>
         <v>Denied</v>
@@ -44298,11 +43586,8 @@
       <c r="AO237" s="9">
         <v>46171</v>
       </c>
-      <c r="AP237" s="8" t="s">
-        <v>1051</v>
-      </c>
     </row>
-    <row r="238" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A238" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]US!$A$2:$A$19,MATCH($D238,[5]US!$D$2:$D$19,0))="","",INDEX([5]US!$A$2:$A$19,MATCH($D238,[5]US!$D$2:$D$19,0))),"")</f>
         <v>Denied</v>
@@ -44419,11 +43704,8 @@
       <c r="AO238" s="9">
         <v>46171</v>
       </c>
-      <c r="AP238" s="8" t="s">
-        <v>1054</v>
-      </c>
     </row>
-    <row r="239" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A239" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]DME!$A$2:$A$35,MATCH($D239,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$A$2:$A$35,MATCH($D239,[5]DME!$D$2:$D$35,0))),"")</f>
         <v>PAID</v>
@@ -44544,11 +43826,8 @@
       <c r="AO239" s="9">
         <v>46183</v>
       </c>
-      <c r="AP239" s="8" t="s">
-        <v>1055</v>
-      </c>
     </row>
-    <row r="240" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A240" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]DME!$A$2:$A$35,MATCH($D240,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$A$2:$A$35,MATCH($D240,[5]DME!$D$2:$D$35,0))),"")</f>
         <v>PAID</v>
@@ -44667,11 +43946,8 @@
       <c r="AO240" s="9">
         <v>46183</v>
       </c>
-      <c r="AP240" s="8" t="s">
-        <v>1057</v>
-      </c>
     </row>
-    <row r="241" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A241" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]BH!$A$2:$A$33,MATCH($D241,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$A$2:$A$33,MATCH($D241,[5]BH!$D$2:$D$33,0))),"")</f>
         <v>Pending</v>
@@ -44790,11 +44066,8 @@
       <c r="AO241" s="9">
         <v>46182</v>
       </c>
-      <c r="AP241" s="8" t="s">
-        <v>1059</v>
-      </c>
     </row>
-    <row r="242" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A242" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]DME!$A$2:$A$35,MATCH($D242,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$A$2:$A$35,MATCH($D242,[5]DME!$D$2:$D$35,0))),"")</f>
         <v>Denied</v>
@@ -44919,11 +44192,8 @@
       <c r="AO242" s="9">
         <v>46199</v>
       </c>
-      <c r="AP242" s="8" t="s">
-        <v>1065</v>
-      </c>
     </row>
-    <row r="243" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A243" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]ORTHO!$A$2:$A$24,MATCH($D243,[5]ORTHO!$D$2:$D$24,0))="","",INDEX([5]ORTHO!$A$2:$A$24,MATCH($D243,[5]ORTHO!$D$2:$D$24,0))),"")</f>
         <v>Pending</v>
@@ -45044,11 +44314,8 @@
       <c r="AO243" s="9">
         <v>46175</v>
       </c>
-      <c r="AP243" s="8" t="s">
-        <v>1066</v>
-      </c>
     </row>
-    <row r="244" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A244" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]BH!$A$2:$A$82,MATCH($D244,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$A$2:$A$82,MATCH($D244,[6]BH!$D$2:$D$82,0))),"")</f>
         <v/>
@@ -45163,9 +44430,8 @@
       <c r="AO244" s="9">
         <v>46273</v>
       </c>
-      <c r="AP244" s="8"/>
     </row>
-    <row r="245" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A245" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D245,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D245,[6]DME!$D$2:$D$52,0))),"")</f>
         <v/>
@@ -45288,9 +44554,8 @@
       <c r="AO245" s="9">
         <v>46196</v>
       </c>
-      <c r="AP245" s="8"/>
     </row>
-    <row r="246" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A246" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]DME!$A$2:$A$35,MATCH($D246,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$A$2:$A$35,MATCH($D246,[5]DME!$D$2:$D$35,0))),"")</f>
         <v>Finalized</v>
@@ -45413,11 +44678,8 @@
       <c r="AO246" s="9">
         <v>46183</v>
       </c>
-      <c r="AP246" s="8" t="s">
-        <v>1068</v>
-      </c>
     </row>
-    <row r="247" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A247" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]GAE!$A$2:$A$23,MATCH($D247,[6]GAE!$D$2:$D$23,0))="","",INDEX([6]GAE!$A$2:$A$23,MATCH($D247,[6]GAE!$D$2:$D$23,0))),"")</f>
         <v/>
@@ -45544,11 +44806,8 @@
       <c r="AO247" s="9">
         <v>46193</v>
       </c>
-      <c r="AP247" s="8" t="s">
-        <v>1071</v>
-      </c>
     </row>
-    <row r="248" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A248" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]BH!$A$2:$A$82,MATCH($D248,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$A$2:$A$82,MATCH($D248,[6]BH!$D$2:$D$82,0))),"")</f>
         <v/>
@@ -45665,11 +44924,8 @@
       <c r="AO248" s="9">
         <v>46217</v>
       </c>
-      <c r="AP248" s="8" t="s">
-        <v>1074</v>
-      </c>
     </row>
-    <row r="249" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A249" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]US!$A$2:$A$22,MATCH($D249,[6]US!$D$2:$D$22,0))="","",INDEX([6]US!$A$2:$A$22,MATCH($D249,[6]US!$D$2:$D$22,0))),"")</f>
         <v/>
@@ -45788,11 +45044,8 @@
       <c r="AO249" s="9">
         <v>46195</v>
       </c>
-      <c r="AP249" s="8" t="s">
-        <v>1081</v>
-      </c>
     </row>
-    <row r="250" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A250" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]BH!$A$2:$A$82,MATCH($D250,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$A$2:$A$82,MATCH($D250,[6]BH!$D$2:$D$82,0))),"")</f>
         <v/>
@@ -45907,9 +45160,8 @@
       <c r="AO250" s="9">
         <v>46274</v>
       </c>
-      <c r="AP250" s="8"/>
     </row>
-    <row r="251" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A251" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]ORTHO!$A$2:$A$39,MATCH($D251,[6]ORTHO!$D$2:$D$39,0))="","",INDEX([6]ORTHO!$A$2:$A$39,MATCH($D251,[6]ORTHO!$D$2:$D$39,0))),"")</f>
         <v/>
@@ -46028,11 +45280,8 @@
       <c r="AO251" s="9">
         <v>46181</v>
       </c>
-      <c r="AP251" s="8" t="s">
-        <v>1085</v>
-      </c>
     </row>
-    <row r="252" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A252" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D252,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D252,[6]DME!$D$2:$D$52,0))),"")</f>
         <v/>
@@ -46153,11 +45402,8 @@
       <c r="AO252" s="9">
         <v>46185</v>
       </c>
-      <c r="AP252" s="8" t="s">
-        <v>1094</v>
-      </c>
     </row>
-    <row r="253" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A253" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D253,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D253,[6]DME!$D$2:$D$52,0))),"")</f>
         <v/>
@@ -46278,11 +45524,8 @@
       <c r="AO253" s="9">
         <v>46191</v>
       </c>
-      <c r="AP253" s="8" t="s">
-        <v>1098</v>
-      </c>
     </row>
-    <row r="254" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A254" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D254,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D254,[6]DME!$D$2:$D$52,0))),"")</f>
         <v>Finalized</v>
@@ -46403,11 +45646,8 @@
       <c r="AO254" s="9">
         <v>46185</v>
       </c>
-      <c r="AP254" s="8" t="s">
-        <v>1108</v>
-      </c>
     </row>
-    <row r="255" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A255" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D255,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D255,[6]DME!$D$2:$D$52,0))),"")</f>
         <v/>
@@ -46524,11 +45764,8 @@
       <c r="AO255" s="9">
         <v>46211</v>
       </c>
-      <c r="AP255" s="8" t="s">
-        <v>1111</v>
-      </c>
     </row>
-    <row r="256" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A256" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]BH!$A$2:$A$82,MATCH($D256,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$A$2:$A$82,MATCH($D256,[6]BH!$D$2:$D$82,0))),"")</f>
         <v/>
@@ -46645,11 +45882,8 @@
       <c r="AO256" s="9">
         <v>46217</v>
       </c>
-      <c r="AP256" s="8" t="s">
-        <v>1113</v>
-      </c>
     </row>
-    <row r="257" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A257" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]BH!$A$2:$A$82,MATCH($D257,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$A$2:$A$82,MATCH($D257,[6]BH!$D$2:$D$82,0))),"")</f>
         <v/>
@@ -46766,9 +46000,8 @@
       <c r="AO257" s="9">
         <v>46246</v>
       </c>
-      <c r="AP257" s="8"/>
     </row>
-    <row r="258" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A258" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D258,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D258,[6]DME!$D$2:$D$52,0))),"")</f>
         <v/>
@@ -46885,11 +46118,8 @@
       <c r="AO258" s="9">
         <v>46191</v>
       </c>
-      <c r="AP258" s="8" t="s">
-        <v>1116</v>
-      </c>
     </row>
-    <row r="259" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A259" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]BH!$A$2:$A$82,MATCH($D259,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$A$2:$A$82,MATCH($D259,[6]BH!$D$2:$D$82,0))),"")</f>
         <v/>
@@ -47006,11 +46236,8 @@
       <c r="AO259" s="9">
         <v>46217</v>
       </c>
-      <c r="AP259" s="8" t="s">
-        <v>1121</v>
-      </c>
     </row>
-    <row r="260" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A260" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]ORTHO!$A$2:$A$39,MATCH($D260,[6]ORTHO!$D$2:$D$39,0))="","",INDEX([6]ORTHO!$A$2:$A$39,MATCH($D260,[6]ORTHO!$D$2:$D$39,0))),"")</f>
         <v/>
@@ -47129,11 +46356,8 @@
       <c r="AO260" s="9">
         <v>46190</v>
       </c>
-      <c r="AP260" s="8" t="s">
-        <v>1137</v>
-      </c>
     </row>
-    <row r="261" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A261" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]US!$A$2:$A$22,MATCH($D261,[6]US!$D$2:$D$22,0))="","",INDEX([6]US!$A$2:$A$22,MATCH($D261,[6]US!$D$2:$D$22,0))),"")</f>
         <v/>
@@ -47252,11 +46476,8 @@
       <c r="AO261" s="9">
         <v>46195</v>
       </c>
-      <c r="AP261" s="8" t="s">
-        <v>1147</v>
-      </c>
     </row>
-    <row r="262" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A262" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]US!$A$2:$A$22,MATCH($D262,[6]US!$D$2:$D$22,0))="","",INDEX([6]US!$A$2:$A$22,MATCH($D262,[6]US!$D$2:$D$22,0))),"")</f>
         <v/>
@@ -47377,11 +46598,8 @@
       <c r="AO262" s="9">
         <v>46204</v>
       </c>
-      <c r="AP262" s="8" t="s">
-        <v>1156</v>
-      </c>
     </row>
-    <row r="263" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A263" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]ORTHO!$A$2:$A$39,MATCH($D263,[6]ORTHO!$D$2:$D$39,0))="","",INDEX([6]ORTHO!$A$2:$A$39,MATCH($D263,[6]ORTHO!$D$2:$D$39,0))),"")</f>
         <v/>
@@ -47500,11 +46718,8 @@
       <c r="AO263" s="9">
         <v>46210</v>
       </c>
-      <c r="AP263" s="8" t="s">
-        <v>1159</v>
-      </c>
     </row>
-    <row r="264" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A264" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]BH!$A$2:$A$82,MATCH($D264,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$A$2:$A$82,MATCH($D264,[6]BH!$D$2:$D$82,0))),"")</f>
         <v/>
@@ -47621,11 +46836,8 @@
       <c r="AO264" s="9">
         <v>46217</v>
       </c>
-      <c r="AP264" s="8" t="s">
-        <v>1160</v>
-      </c>
     </row>
-    <row r="265" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A265" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D265,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D265,[6]DME!$D$2:$D$52,0))),"")</f>
         <v>Finalized</v>
@@ -47750,11 +46962,8 @@
       <c r="AO265" s="9">
         <v>46196</v>
       </c>
-      <c r="AP265" s="8" t="s">
-        <v>1167</v>
-      </c>
     </row>
-    <row r="266" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A266" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D266,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D266,[6]DME!$D$2:$D$52,0))),"")</f>
         <v/>
@@ -47871,11 +47080,8 @@
       <c r="AO266" s="9">
         <v>46196</v>
       </c>
-      <c r="AP266" s="8" t="s">
-        <v>1168</v>
-      </c>
     </row>
-    <row r="267" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A267" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]BH!$A$2:$A$82,MATCH($D267,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$A$2:$A$82,MATCH($D267,[6]BH!$D$2:$D$82,0))),"")</f>
         <v/>
@@ -47994,9 +47200,8 @@
       <c r="AO267" s="9">
         <v>46217</v>
       </c>
-      <c r="AP267" s="8"/>
     </row>
-    <row r="268" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A268" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D268,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D268,[6]DME!$D$2:$D$52,0))),"")</f>
         <v/>
@@ -48117,11 +47322,8 @@
       <c r="AO268" s="9">
         <v>46204</v>
       </c>
-      <c r="AP268" s="8" t="s">
-        <v>1184</v>
-      </c>
     </row>
-    <row r="269" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A269" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]BH!$A$2:$A$82,MATCH($D269,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$A$2:$A$82,MATCH($D269,[6]BH!$D$2:$D$82,0))),"")</f>
         <v/>
@@ -48236,11 +47438,8 @@
       <c r="AO269" s="9">
         <v>46217</v>
       </c>
-      <c r="AP269" s="8" t="s">
-        <v>1189</v>
-      </c>
     </row>
-    <row r="270" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A270" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D270,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D270,[6]DME!$D$2:$D$52,0))),"")</f>
         <v/>
@@ -48359,11 +47558,8 @@
       <c r="AO270" s="9">
         <v>46205</v>
       </c>
-      <c r="AP270" s="8" t="s">
-        <v>1190</v>
-      </c>
     </row>
-    <row r="271" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A271" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]BH!$A$2:$A$82,MATCH($D271,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$A$2:$A$82,MATCH($D271,[6]BH!$D$2:$D$82,0))),"")</f>
         <v/>
@@ -48480,11 +47676,8 @@
       <c r="AO271" s="9">
         <v>46217</v>
       </c>
-      <c r="AP271" s="8" t="s">
-        <v>1195</v>
-      </c>
     </row>
-    <row r="272" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A272" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D272,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D272,[6]DME!$D$2:$D$52,0))),"")</f>
         <v>Finalized</v>
@@ -48605,11 +47798,8 @@
       <c r="AO272" s="9">
         <v>46205</v>
       </c>
-      <c r="AP272" s="8" t="s">
-        <v>1198</v>
-      </c>
     </row>
-    <row r="273" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A273" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D273,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D273,[6]DME!$D$2:$D$52,0))),"")</f>
         <v/>
@@ -48728,11 +47918,8 @@
       <c r="AO273" s="9">
         <v>46204</v>
       </c>
-      <c r="AP273" s="8" t="s">
-        <v>1200</v>
-      </c>
     </row>
-    <row r="274" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A274" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]GAE!$A$2:$A$23,MATCH($D274,[6]GAE!$D$2:$D$23,0))="","",INDEX([6]GAE!$A$2:$A$23,MATCH($D274,[6]GAE!$D$2:$D$23,0))),"")</f>
         <v/>
@@ -48857,11 +48044,8 @@
       <c r="AO274" s="9">
         <v>46216</v>
       </c>
-      <c r="AP274" s="8" t="s">
-        <v>1207</v>
-      </c>
     </row>
-    <row r="275" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A275" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]ORTHO!$A$2:$A$10,MATCH($D275,[1]ORTHO!$D$2:$D$10,0))="","",INDEX([1]ORTHO!$A$2:$A$10,MATCH($D275,[1]ORTHO!$D$2:$D$10,0))),"")</f>
         <v/>
@@ -48978,11 +48162,8 @@
       <c r="AO275" s="9">
         <v>46048</v>
       </c>
-      <c r="AP275" s="8" t="s">
-        <v>1213</v>
-      </c>
     </row>
-    <row r="276" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A276" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]DME!$A$2:$A$8,MATCH($D276,[1]DME!$D$2:$D$8,0))="","",INDEX([1]DME!$A$2:$A$8,MATCH($D276,[1]DME!$D$2:$D$8,0))),"")</f>
         <v>Finalized</v>
@@ -49107,11 +48288,8 @@
       <c r="AO276" s="9">
         <v>46036</v>
       </c>
-      <c r="AP276" s="8" t="s">
-        <v>1216</v>
-      </c>
     </row>
-    <row r="277" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A277" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]GAE!$A$2:$A$12,MATCH($D277,[1]GAE!$D$2:$D$12,0))="","",INDEX([1]GAE!$A$2:$A$12,MATCH($D277,[1]GAE!$D$2:$D$12,0))),"")</f>
         <v/>
@@ -49236,11 +48414,8 @@
       <c r="AO277" s="9">
         <v>46062</v>
       </c>
-      <c r="AP277" s="8" t="s">
-        <v>1219</v>
-      </c>
     </row>
-    <row r="278" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A278" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]GAE!$A$2:$A$12,MATCH($D278,[1]GAE!$D$2:$D$12,0))="","",INDEX([1]GAE!$A$2:$A$12,MATCH($D278,[1]GAE!$D$2:$D$12,0))),"")</f>
         <v/>
@@ -49365,11 +48540,8 @@
       <c r="AO278" s="9">
         <v>46062</v>
       </c>
-      <c r="AP278" s="8" t="s">
-        <v>1222</v>
-      </c>
     </row>
-    <row r="279" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A279" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]BH!$A$2:$A$17,MATCH($D279,[1]BH!$D$2:$D$17,0))="","",INDEX([1]BH!$A$2:$A$17,MATCH($D279,[1]BH!$D$2:$D$17,0))),"")</f>
         <v>Denied</v>
@@ -49486,11 +48658,8 @@
       <c r="AO279" s="9">
         <v>46057</v>
       </c>
-      <c r="AP279" s="8" t="s">
-        <v>1224</v>
-      </c>
     </row>
-    <row r="280" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A280" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]BH!$A$2:$A$17,MATCH($D280,[1]BH!$D$2:$D$17,0))="","",INDEX([1]BH!$A$2:$A$17,MATCH($D280,[1]BH!$D$2:$D$17,0))),"")</f>
         <v>Denied</v>
@@ -49607,11 +48776,8 @@
       <c r="AO280" s="9">
         <v>46057</v>
       </c>
-      <c r="AP280" s="8" t="s">
-        <v>1226</v>
-      </c>
     </row>
-    <row r="281" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A281" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]US!$A$2:$A$8,MATCH($D281,[1]US!$D$2:$D$8,0))="","",INDEX([1]US!$A$2:$A$8,MATCH($D281,[1]US!$D$2:$D$8,0))),"")</f>
         <v>Received</v>
@@ -49728,11 +48894,8 @@
       <c r="AO281" s="9">
         <v>46048</v>
       </c>
-      <c r="AP281" s="8" t="s">
-        <v>1228</v>
-      </c>
     </row>
-    <row r="282" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A282" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]BH!$A$2:$A$82,MATCH($D282,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$A$2:$A$82,MATCH($D282,[6]BH!$D$2:$D$82,0))),"")</f>
         <v/>
@@ -49847,9 +49010,8 @@
       <c r="AO282" s="9">
         <v>46273</v>
       </c>
-      <c r="AP282" s="8"/>
     </row>
-    <row r="283" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A283" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]US!$A$2:$A$8,MATCH($D283,[1]US!$D$2:$D$8,0))="","",INDEX([1]US!$A$2:$A$8,MATCH($D283,[1]US!$D$2:$D$8,0))),"")</f>
         <v/>
@@ -49968,11 +49130,8 @@
       <c r="AO283" s="9">
         <v>46048</v>
       </c>
-      <c r="AP283" s="8" t="s">
-        <v>1231</v>
-      </c>
     </row>
-    <row r="284" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A284" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]BH!$A$2:$A$17,MATCH($D284,[1]BH!$D$2:$D$17,0))="","",INDEX([1]BH!$A$2:$A$17,MATCH($D284,[1]BH!$D$2:$D$17,0))),"")</f>
         <v>Denied</v>
@@ -50089,11 +49248,8 @@
       <c r="AO284" s="9">
         <v>46057</v>
       </c>
-      <c r="AP284" s="8" t="s">
-        <v>1232</v>
-      </c>
     </row>
-    <row r="285" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A285" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]ORTHO!$A$2:$A$10,MATCH($D285,[1]ORTHO!$D$2:$D$10,0))="","",INDEX([1]ORTHO!$A$2:$A$10,MATCH($D285,[1]ORTHO!$D$2:$D$10,0))),"")</f>
         <v>Received</v>
@@ -50210,11 +49366,8 @@
       <c r="AO285" s="9">
         <v>46037</v>
       </c>
-      <c r="AP285" s="8" t="s">
-        <v>1234</v>
-      </c>
     </row>
-    <row r="286" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A286" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]ORTHO!$A$2:$A$10,MATCH($D286,[1]ORTHO!$D$2:$D$10,0))="","",INDEX([1]ORTHO!$A$2:$A$10,MATCH($D286,[1]ORTHO!$D$2:$D$10,0))),"")</f>
         <v>Finalized</v>
@@ -50333,11 +49486,8 @@
       <c r="AO286" s="9">
         <v>46037</v>
       </c>
-      <c r="AP286" s="8" t="s">
-        <v>1236</v>
-      </c>
     </row>
-    <row r="287" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A287" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]ORTHO!$A$2:$A$10,MATCH($D287,[1]ORTHO!$D$2:$D$10,0))="","",INDEX([1]ORTHO!$A$2:$A$10,MATCH($D287,[1]ORTHO!$D$2:$D$10,0))),"")</f>
         <v/>
@@ -50456,11 +49606,8 @@
       <c r="AO287" s="9">
         <v>46037</v>
       </c>
-      <c r="AP287" s="8" t="s">
-        <v>1238</v>
-      </c>
     </row>
-    <row r="288" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A288" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]US!$A$2:$A$8,MATCH($D288,[1]US!$D$2:$D$8,0))="","",INDEX([1]US!$A$2:$A$8,MATCH($D288,[1]US!$D$2:$D$8,0))),"")</f>
         <v>Received</v>
@@ -50577,11 +49724,8 @@
       <c r="AO288" s="9">
         <v>46051</v>
       </c>
-      <c r="AP288" s="8" t="s">
-        <v>1241</v>
-      </c>
     </row>
-    <row r="289" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A289" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]US!$A$2:$A$8,MATCH($D289,[1]US!$D$2:$D$8,0))="","",INDEX([1]US!$A$2:$A$8,MATCH($D289,[1]US!$D$2:$D$8,0))),"")</f>
         <v>Received</v>
@@ -50704,11 +49848,8 @@
       <c r="AO289" s="9">
         <v>46048</v>
       </c>
-      <c r="AP289" s="8" t="s">
-        <v>1245</v>
-      </c>
     </row>
-    <row r="290" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A290" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]ORTHO!$A$2:$A$10,MATCH($D290,[1]ORTHO!$D$2:$D$10,0))="","",INDEX([1]ORTHO!$A$2:$A$10,MATCH($D290,[1]ORTHO!$D$2:$D$10,0))),"")</f>
         <v/>
@@ -50825,11 +49966,8 @@
       <c r="AO290" s="9">
         <v>46042</v>
       </c>
-      <c r="AP290" s="8" t="s">
-        <v>1247</v>
-      </c>
     </row>
-    <row r="291" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A291" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]BH!$A$2:$A$17,MATCH($D291,[1]BH!$D$2:$D$17,0))="","",INDEX([1]BH!$A$2:$A$17,MATCH($D291,[1]BH!$D$2:$D$17,0))),"")</f>
         <v>Denied</v>
@@ -50946,11 +50084,8 @@
       <c r="AO291" s="9">
         <v>46057</v>
       </c>
-      <c r="AP291" s="8" t="s">
-        <v>1249</v>
-      </c>
     </row>
-    <row r="292" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A292" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]US!$A$2:$A$8,MATCH($D292,[1]US!$D$2:$D$8,0))="","",INDEX([1]US!$A$2:$A$8,MATCH($D292,[1]US!$D$2:$D$8,0))),"")</f>
         <v/>
@@ -51069,11 +50204,8 @@
       <c r="AO292" s="9">
         <v>46048</v>
       </c>
-      <c r="AP292" s="8" t="s">
-        <v>1251</v>
-      </c>
     </row>
-    <row r="293" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A293" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]ORTHO!$A$2:$A$39,MATCH($D293,[6]ORTHO!$D$2:$D$39,0))="","",INDEX([6]ORTHO!$A$2:$A$39,MATCH($D293,[6]ORTHO!$D$2:$D$39,0))),"")</f>
         <v/>
@@ -51190,9 +50322,8 @@
       <c r="AO293" s="9">
         <v>46217</v>
       </c>
-      <c r="AP293" s="8"/>
     </row>
-    <row r="294" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A294" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]US!$A$2:$A$8,MATCH($D294,[1]US!$D$2:$D$8,0))="","",INDEX([1]US!$A$2:$A$8,MATCH($D294,[1]US!$D$2:$D$8,0))),"")</f>
         <v>Received</v>
@@ -51311,11 +50442,8 @@
       <c r="AO294" s="9">
         <v>46048</v>
       </c>
-      <c r="AP294" s="8" t="s">
-        <v>1254</v>
-      </c>
     </row>
-    <row r="295" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A295" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]BH!$A$2:$A$17,MATCH($D295,[1]BH!$D$2:$D$17,0))="","",INDEX([1]BH!$A$2:$A$17,MATCH($D295,[1]BH!$D$2:$D$17,0))),"")</f>
         <v>Denied</v>
@@ -51432,11 +50560,8 @@
       <c r="AO295" s="9">
         <v>46057</v>
       </c>
-      <c r="AP295" s="8" t="s">
-        <v>1256</v>
-      </c>
     </row>
-    <row r="296" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A296" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]ORTHO!$A$2:$A$39,MATCH($D296,[6]ORTHO!$D$2:$D$39,0))="","",INDEX([6]ORTHO!$A$2:$A$39,MATCH($D296,[6]ORTHO!$D$2:$D$39,0))),"")</f>
         <v/>
@@ -51559,9 +50684,8 @@
       <c r="AO296" s="9">
         <v>46246</v>
       </c>
-      <c r="AP296" s="8"/>
     </row>
-    <row r="297" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A297" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]BH!$A$2:$A$17,MATCH($D297,[1]BH!$D$2:$D$17,0))="","",INDEX([1]BH!$A$2:$A$17,MATCH($D297,[1]BH!$D$2:$D$17,0))),"")</f>
         <v>Finalized</v>
@@ -51680,11 +50804,8 @@
       <c r="AO297" s="9">
         <v>46056</v>
       </c>
-      <c r="AP297" s="8" t="s">
-        <v>1259</v>
-      </c>
     </row>
-    <row r="298" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A298" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]ORTHO!$A$2:$A$10,MATCH($D298,[1]ORTHO!$D$2:$D$10,0))="","",INDEX([1]ORTHO!$A$2:$A$10,MATCH($D298,[1]ORTHO!$D$2:$D$10,0))),"")</f>
         <v>Denied</v>
@@ -51805,11 +50926,8 @@
       <c r="AO298" s="9">
         <v>46049</v>
       </c>
-      <c r="AP298" s="8" t="s">
-        <v>1261</v>
-      </c>
     </row>
-    <row r="299" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A299" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]ORTHO!$A$2:$A$10,MATCH($D299,[1]ORTHO!$D$2:$D$10,0))="","",INDEX([1]ORTHO!$A$2:$A$10,MATCH($D299,[1]ORTHO!$D$2:$D$10,0))),"")</f>
         <v>Denied</v>
@@ -51926,11 +51044,8 @@
       <c r="AO299" s="9">
         <v>46049</v>
       </c>
-      <c r="AP299" s="8" t="s">
-        <v>1263</v>
-      </c>
     </row>
-    <row r="300" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A300" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]DME!$A$2:$A$8,MATCH($D300,[1]DME!$D$2:$D$8,0))="","",INDEX([1]DME!$A$2:$A$8,MATCH($D300,[1]DME!$D$2:$D$8,0))),"")</f>
         <v>Denied</v>
@@ -52055,11 +51170,8 @@
       <c r="AO300" s="9">
         <v>46063</v>
       </c>
-      <c r="AP300" s="8" t="s">
-        <v>78</v>
-      </c>
     </row>
-    <row r="301" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A301" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]GAE!$A$2:$A$12,MATCH($D301,[1]GAE!$D$2:$D$12,0))="","",INDEX([1]GAE!$A$2:$A$12,MATCH($D301,[1]GAE!$D$2:$D$12,0))),"")</f>
         <v/>
@@ -52184,11 +51296,8 @@
       <c r="AO301" s="9">
         <v>46062</v>
       </c>
-      <c r="AP301" s="8" t="s">
-        <v>1267</v>
-      </c>
     </row>
-    <row r="302" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A302" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]BH!$A$2:$A$17,MATCH($D302,[1]BH!$D$2:$D$17,0))="","",INDEX([1]BH!$A$2:$A$17,MATCH($D302,[1]BH!$D$2:$D$17,0))),"")</f>
         <v>Received</v>
@@ -52305,11 +51414,8 @@
       <c r="AO302" s="9">
         <v>46057</v>
       </c>
-      <c r="AP302" s="8" t="s">
-        <v>1269</v>
-      </c>
     </row>
-    <row r="303" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A303" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]BH!$A$2:$A$17,MATCH($D303,[1]BH!$D$2:$D$17,0))="","",INDEX([1]BH!$A$2:$A$17,MATCH($D303,[1]BH!$D$2:$D$17,0))),"")</f>
         <v>Denied</v>
@@ -52428,11 +51534,8 @@
       <c r="AO303" s="9">
         <v>46056</v>
       </c>
-      <c r="AP303" s="8" t="s">
-        <v>1271</v>
-      </c>
     </row>
-    <row r="304" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A304" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]BH!$A$2:$A$17,MATCH($D304,[1]BH!$D$2:$D$17,0))="","",INDEX([1]BH!$A$2:$A$17,MATCH($D304,[1]BH!$D$2:$D$17,0))),"")</f>
         <v>Pending</v>
@@ -52549,11 +51652,8 @@
       <c r="AO304" s="9">
         <v>46056</v>
       </c>
-      <c r="AP304" s="8" t="s">
-        <v>1274</v>
-      </c>
     </row>
-    <row r="305" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A305" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]US!$A$2:$A$8,MATCH($D305,[1]US!$D$2:$D$8,0))="","",INDEX([1]US!$A$2:$A$8,MATCH($D305,[1]US!$D$2:$D$8,0))),"")</f>
         <v/>
@@ -52674,11 +51774,8 @@
       <c r="AO305" s="9">
         <v>46058</v>
       </c>
-      <c r="AP305" s="8" t="s">
-        <v>1275</v>
-      </c>
     </row>
-    <row r="306" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A306" s="5" t="str">
         <f>IFERROR(IF(INDEX([3]BH!$A$2:$A$9,MATCH($D306,[3]BH!$D$2:$D$9,0))="","",INDEX([3]BH!$A$2:$A$9,MATCH($D306,[3]BH!$D$2:$D$9,0))),"")</f>
         <v>Denied</v>
@@ -52795,11 +51892,8 @@
       <c r="AO306" s="9">
         <v>46086</v>
       </c>
-      <c r="AP306" s="8" t="s">
-        <v>1280</v>
-      </c>
     </row>
-    <row r="307" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A307" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]GAE!$A$2:$A$12,MATCH($D307,[1]GAE!$D$2:$D$12,0))="","",INDEX([1]GAE!$A$2:$A$12,MATCH($D307,[1]GAE!$D$2:$D$12,0))),"")</f>
         <v/>
@@ -52924,11 +52018,8 @@
       <c r="AO307" s="9">
         <v>46062</v>
       </c>
-      <c r="AP307" s="8" t="s">
-        <v>1283</v>
-      </c>
     </row>
-    <row r="308" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A308" s="5" t="str">
         <f>IFERROR(IF(INDEX([3]ORTHO!$A$2:$A$11,MATCH($D308,[3]ORTHO!$D$2:$D$11,0))="","",INDEX([3]ORTHO!$A$2:$A$11,MATCH($D308,[3]ORTHO!$D$2:$D$11,0))),"")</f>
         <v>Denied</v>
@@ -53045,11 +52136,8 @@
       <c r="AO308" s="9">
         <v>46065</v>
       </c>
-      <c r="AP308" s="8" t="s">
-        <v>1285</v>
-      </c>
     </row>
-    <row r="309" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A309" s="5" t="str">
         <f>IFERROR(IF(INDEX([3]BH!$A$2:$A$9,MATCH($D309,[3]BH!$D$2:$D$9,0))="","",INDEX([3]BH!$A$2:$A$9,MATCH($D309,[3]BH!$D$2:$D$9,0))),"")</f>
         <v>Denied</v>
@@ -53166,11 +52254,8 @@
       <c r="AO309" s="9">
         <v>46090</v>
       </c>
-      <c r="AP309" s="8" t="s">
-        <v>1286</v>
-      </c>
     </row>
-    <row r="310" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A310" s="5" t="str">
         <f>IFERROR(IF(INDEX([3]BH!$A$2:$A$9,MATCH($D310,[3]BH!$D$2:$D$9,0))="","",INDEX([3]BH!$A$2:$A$9,MATCH($D310,[3]BH!$D$2:$D$9,0))),"")</f>
         <v>Finalized</v>
@@ -53289,11 +52374,8 @@
       <c r="AO310" s="9">
         <v>46086</v>
       </c>
-      <c r="AP310" s="8" t="s">
-        <v>1287</v>
-      </c>
     </row>
-    <row r="311" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A311" s="5" t="str">
         <f>IFERROR(IF(INDEX([3]US!$A$2:$A$6,MATCH($D311,[3]US!$D$2:$D$6,0))="","",INDEX([3]US!$A$2:$A$6,MATCH($D311,[3]US!$D$2:$D$6,0))),"")</f>
         <v>Pending</v>
@@ -53418,11 +52500,8 @@
       <c r="AO311" s="9">
         <v>46076</v>
       </c>
-      <c r="AP311" s="8" t="s">
-        <v>1290</v>
-      </c>
     </row>
-    <row r="312" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A312" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]BH!$A$2:$A$17,MATCH($D312,[1]BH!$D$2:$D$17,0))="","",INDEX([1]BH!$A$2:$A$17,MATCH($D312,[1]BH!$D$2:$D$17,0))),"")</f>
         <v>Rejected</v>
@@ -53539,11 +52618,8 @@
       <c r="AO312" s="9">
         <v>46056</v>
       </c>
-      <c r="AP312" s="8" t="s">
-        <v>1292</v>
-      </c>
     </row>
-    <row r="313" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A313" s="5" t="str">
         <f>IFERROR(IF(INDEX([3]BH!$A$2:$A$9,MATCH($D313,[3]BH!$D$2:$D$9,0))="","",INDEX([3]BH!$A$2:$A$9,MATCH($D313,[3]BH!$D$2:$D$9,0))),"")</f>
         <v>Denied</v>
@@ -53660,11 +52736,8 @@
       <c r="AO313" s="9">
         <v>46086</v>
       </c>
-      <c r="AP313" s="8" t="s">
-        <v>1293</v>
-      </c>
     </row>
-    <row r="314" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A314" s="5" t="str">
         <f>IFERROR(IF(INDEX([3]GAE!$A$2:$A$6,MATCH($D314,[3]GAE!$D$2:$D$6,0))="","",INDEX([3]GAE!$A$2:$A$6,MATCH($D314,[3]GAE!$D$2:$D$6,0))),"")</f>
         <v>Denied</v>
@@ -53789,11 +52862,8 @@
       <c r="AO314" s="9">
         <v>46090</v>
       </c>
-      <c r="AP314" s="8" t="s">
-        <v>1296</v>
-      </c>
     </row>
-    <row r="315" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A315" s="5" t="str">
         <f>IFERROR(IF(INDEX([3]DME!$A$2:$A$12,MATCH($D315,[3]DME!$D$2:$D$12,0))="","",INDEX([3]DME!$A$2:$A$12,MATCH($D315,[3]DME!$D$2:$D$12,0))),"")</f>
         <v>Under Review</v>
@@ -53912,11 +52982,8 @@
       <c r="AO315" s="9">
         <v>46080</v>
       </c>
-      <c r="AP315" s="8" t="s">
-        <v>1298</v>
-      </c>
     </row>
-    <row r="316" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A316" s="5" t="str">
         <f>IFERROR(IF(INDEX([3]BH!$A$2:$A$9,MATCH($D316,[3]BH!$D$2:$D$9,0))="","",INDEX([3]BH!$A$2:$A$9,MATCH($D316,[3]BH!$D$2:$D$9,0))),"")</f>
         <v>Denied</v>
@@ -54035,11 +53102,8 @@
       <c r="AO316" s="9">
         <v>46086</v>
       </c>
-      <c r="AP316" s="8" t="s">
-        <v>1299</v>
-      </c>
     </row>
-    <row r="317" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A317" s="5" t="str">
         <f>IFERROR(IF(INDEX([3]BH!$A$2:$A$9,MATCH($D317,[3]BH!$D$2:$D$9,0))="","",INDEX([3]BH!$A$2:$A$9,MATCH($D317,[3]BH!$D$2:$D$9,0))),"")</f>
         <v>Denied</v>
@@ -54156,11 +53220,8 @@
       <c r="AO317" s="9">
         <v>46086</v>
       </c>
-      <c r="AP317" s="8" t="s">
-        <v>1301</v>
-      </c>
     </row>
-    <row r="318" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A318" s="5" t="str">
         <f>IFERROR(IF(INDEX([3]DME!$A$2:$A$12,MATCH($D318,[3]DME!$D$2:$D$12,0))="","",INDEX([3]DME!$A$2:$A$12,MATCH($D318,[3]DME!$D$2:$D$12,0))),"")</f>
         <v>Denied</v>
@@ -54281,11 +53342,8 @@
       <c r="AO318" s="9">
         <v>46077</v>
       </c>
-      <c r="AP318" s="8" t="s">
-        <v>1304</v>
-      </c>
     </row>
-    <row r="319" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A319" s="5" t="str">
         <f>IFERROR(IF(INDEX([3]ORTHO!$A$2:$A$11,MATCH($D319,[3]ORTHO!$D$2:$D$11,0))="","",INDEX([3]ORTHO!$A$2:$A$11,MATCH($D319,[3]ORTHO!$D$2:$D$11,0))),"")</f>
         <v>Finalized</v>
@@ -54410,11 +53468,8 @@
       <c r="AO319" s="9">
         <v>46084</v>
       </c>
-      <c r="AP319" s="8" t="s">
-        <v>1308</v>
-      </c>
     </row>
-    <row r="320" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A320" s="5" t="str">
         <f>IFERROR(IF(INDEX([3]BH!$A$2:$A$9,MATCH($D320,[3]BH!$D$2:$D$9,0))="","",INDEX([3]BH!$A$2:$A$9,MATCH($D320,[3]BH!$D$2:$D$9,0))),"")</f>
         <v>Denied</v>
@@ -54531,11 +53586,8 @@
       <c r="AO320" s="9">
         <v>46086</v>
       </c>
-      <c r="AP320" s="8" t="s">
-        <v>1310</v>
-      </c>
     </row>
-    <row r="321" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A321" s="5" t="str">
         <f>IFERROR(IF(INDEX([3]BH!$A$2:$A$9,MATCH($D321,[3]BH!$D$2:$D$9,0))="","",INDEX([3]BH!$A$2:$A$9,MATCH($D321,[3]BH!$D$2:$D$9,0))),"")</f>
         <v>Denied</v>
@@ -54652,11 +53704,8 @@
       <c r="AO321" s="9">
         <v>46086</v>
       </c>
-      <c r="AP321" s="8" t="s">
-        <v>1311</v>
-      </c>
     </row>
-    <row r="322" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A322" s="5" t="str">
         <f>IFERROR(IF(INDEX([3]ORTHO!$A$2:$A$11,MATCH($D322,[3]ORTHO!$D$2:$D$11,0))="","",INDEX([3]ORTHO!$A$2:$A$11,MATCH($D322,[3]ORTHO!$D$2:$D$11,0))),"")</f>
         <v>Received</v>
@@ -54777,11 +53826,8 @@
       <c r="AO322" s="9">
         <v>46092</v>
       </c>
-      <c r="AP322" s="8" t="s">
-        <v>1313</v>
-      </c>
     </row>
-    <row r="323" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A323" s="5" t="str">
         <f>IFERROR(IF(INDEX([3]ORTHO!$A$2:$A$11,MATCH($D323,[3]ORTHO!$D$2:$D$11,0))="","",INDEX([3]ORTHO!$A$2:$A$11,MATCH($D323,[3]ORTHO!$D$2:$D$11,0))),"")</f>
         <v>Denied</v>
@@ -54900,11 +53946,8 @@
       <c r="AO323" s="9">
         <v>46083</v>
       </c>
-      <c r="AP323" s="8" t="s">
-        <v>1317</v>
-      </c>
     </row>
-    <row r="324" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A324" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]GAE!$A$2:$A$4,MATCH($D324,[2]GAE!$D$2:$D$4,0))="","",INDEX([2]GAE!$A$2:$A$4,MATCH($D324,[2]GAE!$D$2:$D$4,0))),"")</f>
         <v>Denied</v>
@@ -55031,11 +54074,8 @@
       <c r="AO324" s="9">
         <v>46119</v>
       </c>
-      <c r="AP324" s="8" t="s">
-        <v>1320</v>
-      </c>
     </row>
-    <row r="325" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A325" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]US!$A$2:$A$15,MATCH($D325,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$A$2:$A$15,MATCH($D325,[2]US!$D$2:$D$15,0))),"")</f>
         <v/>
@@ -55158,11 +54198,8 @@
       <c r="AO325" s="9">
         <v>46106</v>
       </c>
-      <c r="AP325" s="8" t="s">
-        <v>1324</v>
-      </c>
     </row>
-    <row r="326" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A326" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]ORTHO!$A$2:$A$16,MATCH($D326,[2]ORTHO!$D$2:$D$16,0))="","",INDEX([2]ORTHO!$A$2:$A$16,MATCH($D326,[2]ORTHO!$D$2:$D$16,0))),"")</f>
         <v>Denied</v>
@@ -55285,11 +54322,8 @@
       <c r="AO326" s="9">
         <v>46197</v>
       </c>
-      <c r="AP326" s="8" t="s">
-        <v>1327</v>
-      </c>
     </row>
-    <row r="327" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A327" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]BH!$A$2:$A$32,MATCH($D327,[2]BH!$D$2:$D$32,0))="","",INDEX([2]BH!$A$2:$A$32,MATCH($D327,[2]BH!$D$2:$D$32,0))),"")</f>
         <v>Denied</v>
@@ -55406,11 +54440,8 @@
       <c r="AO327" s="9">
         <v>46119</v>
       </c>
-      <c r="AP327" s="8" t="s">
-        <v>1328</v>
-      </c>
     </row>
-    <row r="328" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A328" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]BH!$A$2:$A$32,MATCH($D328,[2]BH!$D$2:$D$32,0))="","",INDEX([2]BH!$A$2:$A$32,MATCH($D328,[2]BH!$D$2:$D$32,0))),"")</f>
         <v>Denied</v>
@@ -55527,11 +54558,8 @@
       <c r="AO328" s="9">
         <v>46119</v>
       </c>
-      <c r="AP328" s="8" t="s">
-        <v>1329</v>
-      </c>
     </row>
-    <row r="329" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A329" s="5" t="str">
         <f>IFERROR(IF(INDEX([3]ORTHO!$A$2:$A$11,MATCH($D329,[3]ORTHO!$D$2:$D$11,0))="","",INDEX([3]ORTHO!$A$2:$A$11,MATCH($D329,[3]ORTHO!$D$2:$D$11,0))),"")</f>
         <v>Denied</v>
@@ -55650,11 +54678,8 @@
       <c r="AO329" s="9">
         <v>46077</v>
       </c>
-      <c r="AP329" s="8" t="s">
-        <v>1332</v>
-      </c>
     </row>
-    <row r="330" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A330" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]BH!$A$2:$A$32,MATCH($D330,[2]BH!$D$2:$D$32,0))="","",INDEX([2]BH!$A$2:$A$32,MATCH($D330,[2]BH!$D$2:$D$32,0))),"")</f>
         <v>Pending</v>
@@ -55773,11 +54798,8 @@
       <c r="AO330" s="9">
         <v>46119</v>
       </c>
-      <c r="AP330" s="8" t="s">
-        <v>1334</v>
-      </c>
     </row>
-    <row r="331" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A331" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]BH!$A$2:$A$32,MATCH($D331,[2]BH!$D$2:$D$32,0))="","",INDEX([2]BH!$A$2:$A$32,MATCH($D331,[2]BH!$D$2:$D$32,0))),"")</f>
         <v>Denied</v>
@@ -55894,11 +54916,8 @@
       <c r="AO331" s="9">
         <v>46119</v>
       </c>
-      <c r="AP331" s="8" t="s">
-        <v>1336</v>
-      </c>
     </row>
-    <row r="332" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A332" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]ORTHO!$A$2:$A$16,MATCH($D332,[2]ORTHO!$D$2:$D$16,0))="","",INDEX([2]ORTHO!$A$2:$A$16,MATCH($D332,[2]ORTHO!$D$2:$D$16,0))),"")</f>
         <v>Denied</v>
@@ -56015,11 +55034,8 @@
       <c r="AO332" s="9">
         <v>46091</v>
       </c>
-      <c r="AP332" s="8" t="s">
-        <v>1338</v>
-      </c>
     </row>
-    <row r="333" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A333" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]ORTHO!$A$2:$A$16,MATCH($D333,[2]ORTHO!$D$2:$D$16,0))="","",INDEX([2]ORTHO!$A$2:$A$16,MATCH($D333,[2]ORTHO!$D$2:$D$16,0))),"")</f>
         <v>PAID</v>
@@ -56138,11 +55154,8 @@
       <c r="AO333" s="9">
         <v>46197</v>
       </c>
-      <c r="AP333" s="8" t="s">
-        <v>1341</v>
-      </c>
     </row>
-    <row r="334" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A334" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]BH!$A$2:$A$32,MATCH($D334,[2]BH!$D$2:$D$32,0))="","",INDEX([2]BH!$A$2:$A$32,MATCH($D334,[2]BH!$D$2:$D$32,0))),"")</f>
         <v>Denied</v>
@@ -56259,11 +55272,8 @@
       <c r="AO334" s="9">
         <v>46119</v>
       </c>
-      <c r="AP334" s="8" t="s">
-        <v>1346</v>
-      </c>
     </row>
-    <row r="335" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A335" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]DME!$A$2:$A$11,MATCH($D335,[2]DME!$D$2:$D$11,0))="","",INDEX([2]DME!$A$2:$A$11,MATCH($D335,[2]DME!$D$2:$D$11,0))),"")</f>
         <v>Finalized</v>
@@ -56382,11 +55392,8 @@
       <c r="AO335" s="9">
         <v>46125</v>
       </c>
-      <c r="AP335" s="8" t="s">
-        <v>1349</v>
-      </c>
     </row>
-    <row r="336" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A336" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]ORTHO!$A$2:$A$16,MATCH($D336,[2]ORTHO!$D$2:$D$16,0))="","",INDEX([2]ORTHO!$A$2:$A$16,MATCH($D336,[2]ORTHO!$D$2:$D$16,0))),"")</f>
         <v>Denied</v>
@@ -56507,11 +55514,8 @@
       <c r="AO336" s="9">
         <v>46105</v>
       </c>
-      <c r="AP336" s="8" t="s">
-        <v>1353</v>
-      </c>
     </row>
-    <row r="337" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A337" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]ORTHO!$A$2:$A$16,MATCH($D337,[2]ORTHO!$D$2:$D$16,0))="","",INDEX([2]ORTHO!$A$2:$A$16,MATCH($D337,[2]ORTHO!$D$2:$D$16,0))),"")</f>
         <v>Denied</v>
@@ -56630,11 +55634,8 @@
       <c r="AO337" s="9">
         <v>46105</v>
       </c>
-      <c r="AP337" s="8" t="s">
-        <v>1356</v>
-      </c>
     </row>
-    <row r="338" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A338" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]ORTHO!$A$2:$A$16,MATCH($D338,[2]ORTHO!$D$2:$D$16,0))="","",INDEX([2]ORTHO!$A$2:$A$16,MATCH($D338,[2]ORTHO!$D$2:$D$16,0))),"")</f>
         <v>Denied</v>
@@ -56753,11 +55754,8 @@
       <c r="AO338" s="9">
         <v>46120</v>
       </c>
-      <c r="AP338" s="8" t="s">
-        <v>1357</v>
-      </c>
     </row>
-    <row r="339" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A339" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]BH!$A$2:$A$32,MATCH($D339,[2]BH!$D$2:$D$32,0))="","",INDEX([2]BH!$A$2:$A$32,MATCH($D339,[2]BH!$D$2:$D$32,0))),"")</f>
         <v>Rejected</v>
@@ -56876,11 +55874,8 @@
       <c r="AO339" s="9">
         <v>46119</v>
       </c>
-      <c r="AP339" s="8" t="s">
-        <v>1360</v>
-      </c>
     </row>
-    <row r="340" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A340" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]BH!$A$2:$A$32,MATCH($D340,[2]BH!$D$2:$D$32,0))="","",INDEX([2]BH!$A$2:$A$32,MATCH($D340,[2]BH!$D$2:$D$32,0))),"")</f>
         <v>Denied</v>
@@ -56999,11 +55994,8 @@
       <c r="AO340" s="9">
         <v>46119</v>
       </c>
-      <c r="AP340" s="8" t="s">
-        <v>1361</v>
-      </c>
     </row>
-    <row r="341" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A341" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]DME!$A$2:$A$11,MATCH($D341,[2]DME!$D$2:$D$11,0))="","",INDEX([2]DME!$A$2:$A$11,MATCH($D341,[2]DME!$D$2:$D$11,0))),"")</f>
         <v>Finalized</v>
@@ -57124,11 +56116,8 @@
       <c r="AO341" s="9">
         <v>46217</v>
       </c>
-      <c r="AP341" s="8" t="s">
-        <v>1365</v>
-      </c>
     </row>
-    <row r="342" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A342" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]US!$A$2:$A$15,MATCH($D342,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$A$2:$A$15,MATCH($D342,[2]US!$D$2:$D$15,0))),"")</f>
         <v/>
@@ -57247,11 +56236,8 @@
       <c r="AO342" s="9">
         <v>46119</v>
       </c>
-      <c r="AP342" s="8" t="s">
-        <v>1369</v>
-      </c>
     </row>
-    <row r="343" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A343" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]US!$A$2:$A$15,MATCH($D343,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$A$2:$A$15,MATCH($D343,[2]US!$D$2:$D$15,0))),"")</f>
         <v>Under Review</v>
@@ -57374,11 +56360,8 @@
       <c r="AO343" s="9">
         <v>46125</v>
       </c>
-      <c r="AP343" s="8" t="s">
-        <v>1371</v>
-      </c>
     </row>
-    <row r="344" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A344" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]BH!$A$2:$A$32,MATCH($D344,[2]BH!$D$2:$D$32,0))="","",INDEX([2]BH!$A$2:$A$32,MATCH($D344,[2]BH!$D$2:$D$32,0))),"")</f>
         <v>Denied</v>
@@ -57495,11 +56478,8 @@
       <c r="AO344" s="9">
         <v>46119</v>
       </c>
-      <c r="AP344" s="8" t="s">
-        <v>1373</v>
-      </c>
     </row>
-    <row r="345" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A345" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]BH!$A$2:$A$32,MATCH($D345,[2]BH!$D$2:$D$32,0))="","",INDEX([2]BH!$A$2:$A$32,MATCH($D345,[2]BH!$D$2:$D$32,0))),"")</f>
         <v>Denied</v>
@@ -57618,11 +56598,8 @@
       <c r="AO345" s="9">
         <v>46153</v>
       </c>
-      <c r="AP345" s="8" t="s">
-        <v>1375</v>
-      </c>
     </row>
-    <row r="346" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A346" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]US!$A$2:$A$15,MATCH($D346,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$A$2:$A$15,MATCH($D346,[2]US!$D$2:$D$15,0))),"")</f>
         <v>Not found</v>
@@ -57741,11 +56718,8 @@
       <c r="AO346" s="9">
         <v>46106</v>
       </c>
-      <c r="AP346" s="8" t="s">
-        <v>1377</v>
-      </c>
     </row>
-    <row r="347" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A347" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]BH!$A$2:$A$32,MATCH($D347,[2]BH!$D$2:$D$32,0))="","",INDEX([2]BH!$A$2:$A$32,MATCH($D347,[2]BH!$D$2:$D$32,0))),"")</f>
         <v>PAID</v>
@@ -57862,11 +56836,8 @@
       <c r="AO347" s="9">
         <v>46119</v>
       </c>
-      <c r="AP347" s="8" t="s">
-        <v>1379</v>
-      </c>
     </row>
-    <row r="348" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A348" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]BH!$A$2:$A$32,MATCH($D348,[2]BH!$D$2:$D$32,0))="","",INDEX([2]BH!$A$2:$A$32,MATCH($D348,[2]BH!$D$2:$D$32,0))),"")</f>
         <v>Under Review</v>
@@ -57983,11 +56954,8 @@
       <c r="AO348" s="9">
         <v>46119</v>
       </c>
-      <c r="AP348" s="8" t="s">
-        <v>1381</v>
-      </c>
     </row>
-    <row r="349" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A349" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]BH!$A$2:$A$32,MATCH($D349,[2]BH!$D$2:$D$32,0))="","",INDEX([2]BH!$A$2:$A$32,MATCH($D349,[2]BH!$D$2:$D$32,0))),"")</f>
         <v>Finalized</v>
@@ -58106,11 +57074,8 @@
       <c r="AO349" s="9">
         <v>46105</v>
       </c>
-      <c r="AP349" s="8" t="s">
-        <v>1382</v>
-      </c>
     </row>
-    <row r="350" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A350" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]US!$A$2:$A$15,MATCH($D350,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$A$2:$A$15,MATCH($D350,[2]US!$D$2:$D$15,0))),"")</f>
         <v/>
@@ -58229,11 +57194,8 @@
       <c r="AO350" s="9">
         <v>46121</v>
       </c>
-      <c r="AP350" s="8" t="s">
-        <v>1384</v>
-      </c>
     </row>
-    <row r="351" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A351" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]US!$A$2:$A$15,MATCH($D351,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$A$2:$A$15,MATCH($D351,[2]US!$D$2:$D$15,0))),"")</f>
         <v/>
@@ -58354,11 +57316,8 @@
       <c r="AO351" s="9">
         <v>46121</v>
       </c>
-      <c r="AP351" s="8" t="s">
-        <v>1386</v>
-      </c>
     </row>
-    <row r="352" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A352" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]BH!$A$2:$A$32,MATCH($D352,[2]BH!$D$2:$D$32,0))="","",INDEX([2]BH!$A$2:$A$32,MATCH($D352,[2]BH!$D$2:$D$32,0))),"")</f>
         <v>Finalized</v>
@@ -58477,11 +57436,8 @@
       <c r="AO352" s="9">
         <v>46119</v>
       </c>
-      <c r="AP352" s="8" t="s">
-        <v>1388</v>
-      </c>
     </row>
-    <row r="353" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A353" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]DME!$A$2:$A$11,MATCH($D353,[2]DME!$D$2:$D$11,0))="","",INDEX([2]DME!$A$2:$A$11,MATCH($D353,[2]DME!$D$2:$D$11,0))),"")</f>
         <v>Finalized</v>
@@ -58606,11 +57562,8 @@
       <c r="AO353" s="9">
         <v>46118</v>
       </c>
-      <c r="AP353" s="8" t="s">
-        <v>1391</v>
-      </c>
     </row>
-    <row r="354" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A354" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]BH!$A$2:$A$32,MATCH($D354,[2]BH!$D$2:$D$32,0))="","",INDEX([2]BH!$A$2:$A$32,MATCH($D354,[2]BH!$D$2:$D$32,0))),"")</f>
         <v>Denied</v>
@@ -58727,11 +57680,8 @@
       <c r="AO354" s="9">
         <v>46119</v>
       </c>
-      <c r="AP354" s="8" t="s">
-        <v>1392</v>
-      </c>
     </row>
-    <row r="355" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A355" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]BH!$A$2:$A$32,MATCH($D355,[2]BH!$D$2:$D$32,0))="","",INDEX([2]BH!$A$2:$A$32,MATCH($D355,[2]BH!$D$2:$D$32,0))),"")</f>
         <v>Denied</v>
@@ -58850,11 +57800,8 @@
       <c r="AO355" s="9">
         <v>46119</v>
       </c>
-      <c r="AP355" s="8" t="s">
-        <v>1395</v>
-      </c>
     </row>
-    <row r="356" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A356" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]ORTHO!$A$2:$A$21,MATCH($D356,[4]ORTHO!$D$2:$D$21,0))="","",INDEX([4]ORTHO!$A$2:$A$21,MATCH($D356,[4]ORTHO!$D$2:$D$21,0))),"")</f>
         <v>Denied</v>
@@ -58975,11 +57922,8 @@
       <c r="AO356" s="9">
         <v>46146</v>
       </c>
-      <c r="AP356" s="8" t="s">
-        <v>1399</v>
-      </c>
     </row>
-    <row r="357" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A357" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]ORTHO!$A$2:$A$21,MATCH($D357,[4]ORTHO!$D$2:$D$21,0))="","",INDEX([4]ORTHO!$A$2:$A$21,MATCH($D357,[4]ORTHO!$D$2:$D$21,0))),"")</f>
         <v>Finalized</v>
@@ -59098,11 +58042,8 @@
       <c r="AO357" s="9">
         <v>46197</v>
       </c>
-      <c r="AP357" s="8" t="s">
-        <v>1403</v>
-      </c>
     </row>
-    <row r="358" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A358" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]BH!$A$2:$A$12,MATCH($D358,[4]BH!$D$2:$D$12,0))="","",INDEX([4]BH!$A$2:$A$12,MATCH($D358,[4]BH!$D$2:$D$12,0))),"")</f>
         <v>Denied</v>
@@ -59219,11 +58160,8 @@
       <c r="AO358" s="9">
         <v>46153</v>
       </c>
-      <c r="AP358" s="8" t="s">
-        <v>1404</v>
-      </c>
     </row>
-    <row r="359" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A359" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]US!$A$2:$A$23,MATCH($D359,[4]US!$D$2:$D$23,0))="","",INDEX([4]US!$A$2:$A$23,MATCH($D359,[4]US!$D$2:$D$23,0))),"")</f>
         <v>Denied</v>
@@ -59344,11 +58282,8 @@
       <c r="AO359" s="9">
         <v>46148</v>
       </c>
-      <c r="AP359" s="8" t="s">
-        <v>1407</v>
-      </c>
     </row>
-    <row r="360" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A360" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]US!$A$2:$A$15,MATCH($D360,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$A$2:$A$15,MATCH($D360,[2]US!$D$2:$D$15,0))),"")</f>
         <v>Denied</v>
@@ -59467,11 +58402,8 @@
       <c r="AO360" s="9">
         <v>46106</v>
       </c>
-      <c r="AP360" s="8" t="s">
-        <v>1409</v>
-      </c>
     </row>
-    <row r="361" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A361" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$A$2:$A$34,MATCH($D361,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$A$2:$A$34,MATCH($D361,[4]DME!$D$2:$D$34,0))),"")</f>
         <v/>
@@ -59590,11 +58522,8 @@
       <c r="AO361" s="9">
         <v>46134</v>
       </c>
-      <c r="AP361" s="8" t="s">
-        <v>1411</v>
-      </c>
     </row>
-    <row r="362" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A362" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]GAE!$A$2:$A$8,MATCH($D362,[4]GAE!$D$2:$D$8,0))="","",INDEX([4]GAE!$A$2:$A$8,MATCH($D362,[4]GAE!$D$2:$D$8,0))),"")</f>
         <v>Under Review</v>
@@ -59721,11 +58650,8 @@
       <c r="AO362" s="9">
         <v>46149</v>
       </c>
-      <c r="AP362" s="8" t="s">
-        <v>1414</v>
-      </c>
     </row>
-    <row r="363" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A363" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$A$2:$A$34,MATCH($D363,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$A$2:$A$34,MATCH($D363,[4]DME!$D$2:$D$34,0))),"")</f>
         <v/>
@@ -59844,11 +58770,8 @@
       <c r="AO363" s="9">
         <v>46121</v>
       </c>
-      <c r="AP363" s="8" t="s">
-        <v>1416</v>
-      </c>
     </row>
-    <row r="364" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A364" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]ORTHO!$A$2:$A$24,MATCH($D364,[5]ORTHO!$D$2:$D$24,0))="","",INDEX([5]ORTHO!$A$2:$A$24,MATCH($D364,[5]ORTHO!$D$2:$D$24,0))),"")</f>
         <v>Under Review</v>
@@ -59967,11 +58890,8 @@
       <c r="AO364" s="9">
         <v>46155</v>
       </c>
-      <c r="AP364" s="8" t="s">
-        <v>1420</v>
-      </c>
     </row>
-    <row r="365" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A365" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]US!$A$2:$A$23,MATCH($D365,[4]US!$D$2:$D$23,0))="","",INDEX([4]US!$A$2:$A$23,MATCH($D365,[4]US!$D$2:$D$23,0))),"")</f>
         <v>Denied</v>
@@ -60088,11 +59008,8 @@
       <c r="AO365" s="9">
         <v>46140</v>
       </c>
-      <c r="AP365" s="8" t="s">
-        <v>1422</v>
-      </c>
     </row>
-    <row r="366" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A366" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]BH!$A$2:$A$33,MATCH($D366,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$A$2:$A$33,MATCH($D366,[5]BH!$D$2:$D$33,0))),"")</f>
         <v/>
@@ -60193,11 +59110,8 @@
       <c r="AO366" s="9">
         <v>46182</v>
       </c>
-      <c r="AP366" s="8" t="s">
-        <v>1424</v>
-      </c>
     </row>
-    <row r="367" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A367" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$A$2:$A$34,MATCH($D367,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$A$2:$A$34,MATCH($D367,[4]DME!$D$2:$D$34,0))),"")</f>
         <v/>
@@ -60318,11 +59232,8 @@
       <c r="AO367" s="9">
         <v>46133</v>
       </c>
-      <c r="AP367" s="8" t="s">
-        <v>1426</v>
-      </c>
     </row>
-    <row r="368" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A368" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]US!$A$2:$A$23,MATCH($D368,[4]US!$D$2:$D$23,0))="","",INDEX([4]US!$A$2:$A$23,MATCH($D368,[4]US!$D$2:$D$23,0))),"")</f>
         <v>Denied</v>
@@ -60441,11 +59352,8 @@
       <c r="AO368" s="9">
         <v>46148</v>
       </c>
-      <c r="AP368" s="8" t="s">
-        <v>1427</v>
-      </c>
     </row>
-    <row r="369" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A369" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]US!$A$2:$A$23,MATCH($D369,[4]US!$D$2:$D$23,0))="","",INDEX([4]US!$A$2:$A$23,MATCH($D369,[4]US!$D$2:$D$23,0))),"")</f>
         <v>Denied</v>
@@ -60562,11 +59470,8 @@
       <c r="AO369" s="9">
         <v>46150</v>
       </c>
-      <c r="AP369" s="8" t="s">
-        <v>1429</v>
-      </c>
     </row>
-    <row r="370" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A370" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]US!$A$2:$A$15,MATCH($D370,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$A$2:$A$15,MATCH($D370,[2]US!$D$2:$D$15,0))),"")</f>
         <v>Finalized</v>
@@ -60685,11 +59590,8 @@
       <c r="AO370" s="9">
         <v>46106</v>
       </c>
-      <c r="AP370" s="8" t="s">
-        <v>1431</v>
-      </c>
     </row>
-    <row r="371" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A371" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$A$2:$A$34,MATCH($D371,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$A$2:$A$34,MATCH($D371,[4]DME!$D$2:$D$34,0))),"")</f>
         <v/>
@@ -60808,11 +59710,8 @@
       <c r="AO371" s="9">
         <v>46133</v>
       </c>
-      <c r="AP371" s="8" t="s">
-        <v>1433</v>
-      </c>
     </row>
-    <row r="372" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A372" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]DME!$A$2:$A$35,MATCH($D372,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$A$2:$A$35,MATCH($D372,[5]DME!$D$2:$D$35,0))),"")</f>
         <v>Denied</v>
@@ -60931,11 +59830,8 @@
       <c r="AO372" s="9">
         <v>46155</v>
       </c>
-      <c r="AP372" s="8" t="s">
-        <v>1434</v>
-      </c>
     </row>
-    <row r="373" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A373" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]ORTHO!$A$2:$A$21,MATCH($D373,[4]ORTHO!$D$2:$D$21,0))="","",INDEX([4]ORTHO!$A$2:$A$21,MATCH($D373,[4]ORTHO!$D$2:$D$21,0))),"")</f>
         <v>Finalized</v>
@@ -61052,11 +59948,8 @@
       <c r="AO373" s="9">
         <v>46133</v>
       </c>
-      <c r="AP373" s="8" t="s">
-        <v>1437</v>
-      </c>
     </row>
-    <row r="374" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A374" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$A$2:$A$34,MATCH($D374,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$A$2:$A$34,MATCH($D374,[4]DME!$D$2:$D$34,0))),"")</f>
         <v/>
@@ -61177,11 +60070,8 @@
       <c r="AO374" s="9">
         <v>46134</v>
       </c>
-      <c r="AP374" s="8" t="s">
-        <v>1439</v>
-      </c>
     </row>
-    <row r="375" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A375" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$A$2:$A$34,MATCH($D375,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$A$2:$A$34,MATCH($D375,[4]DME!$D$2:$D$34,0))),"")</f>
         <v/>
@@ -61302,11 +60192,8 @@
       <c r="AO375" s="9">
         <v>46134</v>
       </c>
-      <c r="AP375" s="8" t="s">
-        <v>1441</v>
-      </c>
     </row>
-    <row r="376" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A376" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$A$2:$A$34,MATCH($D376,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$A$2:$A$34,MATCH($D376,[4]DME!$D$2:$D$34,0))),"")</f>
         <v/>
@@ -61427,11 +60314,8 @@
       <c r="AO376" s="9">
         <v>46134</v>
       </c>
-      <c r="AP376" s="8" t="s">
-        <v>1443</v>
-      </c>
     </row>
-    <row r="377" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A377" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]GAE!$A$2:$A$8,MATCH($D377,[4]GAE!$D$2:$D$8,0))="","",INDEX([4]GAE!$A$2:$A$8,MATCH($D377,[4]GAE!$D$2:$D$8,0))),"")</f>
         <v>Under Review</v>
@@ -61556,11 +60440,8 @@
       <c r="AO377" s="9">
         <v>46152</v>
       </c>
-      <c r="AP377" s="8" t="s">
-        <v>1446</v>
-      </c>
     </row>
-    <row r="378" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A378" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]BH!$A$2:$A$12,MATCH($D378,[4]BH!$D$2:$D$12,0))="","",INDEX([4]BH!$A$2:$A$12,MATCH($D378,[4]BH!$D$2:$D$12,0))),"")</f>
         <v>Denied</v>
@@ -61675,11 +60556,8 @@
       <c r="AO378" s="9">
         <v>46153</v>
       </c>
-      <c r="AP378" s="8" t="s">
-        <v>1457</v>
-      </c>
     </row>
-    <row r="379" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A379" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]ORTHO!$A$2:$A$21,MATCH($D379,[4]ORTHO!$D$2:$D$21,0))="","",INDEX([4]ORTHO!$A$2:$A$21,MATCH($D379,[4]ORTHO!$D$2:$D$21,0))),"")</f>
         <v>Denied</v>
@@ -61800,11 +60678,8 @@
       <c r="AO379" s="9">
         <v>46197</v>
       </c>
-      <c r="AP379" s="8" t="s">
-        <v>1460</v>
-      </c>
     </row>
-    <row r="380" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A380" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$A$2:$A$34,MATCH($D380,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$A$2:$A$34,MATCH($D380,[4]DME!$D$2:$D$34,0))),"")</f>
         <v/>
@@ -61925,11 +60800,8 @@
       <c r="AO380" s="9">
         <v>46134</v>
       </c>
-      <c r="AP380" s="8" t="s">
-        <v>1467</v>
-      </c>
     </row>
-    <row r="381" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A381" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$A$2:$A$34,MATCH($D381,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$A$2:$A$34,MATCH($D381,[4]DME!$D$2:$D$34,0))),"")</f>
         <v/>
@@ -62048,11 +60920,8 @@
       <c r="AO381" s="9">
         <v>46143</v>
       </c>
-      <c r="AP381" s="8" t="s">
-        <v>1469</v>
-      </c>
     </row>
-    <row r="382" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A382" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$A$2:$A$34,MATCH($D382,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$A$2:$A$34,MATCH($D382,[4]DME!$D$2:$D$34,0))),"")</f>
         <v/>
@@ -62173,11 +61042,8 @@
       <c r="AO382" s="9">
         <v>46134</v>
       </c>
-      <c r="AP382" s="8" t="s">
-        <v>1470</v>
-      </c>
     </row>
-    <row r="383" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A383" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]ORTHO!$A$2:$A$21,MATCH($D383,[4]ORTHO!$D$2:$D$21,0))="","",INDEX([4]ORTHO!$A$2:$A$21,MATCH($D383,[4]ORTHO!$D$2:$D$21,0))),"")</f>
         <v>Finalized</v>
@@ -62294,11 +61160,8 @@
       <c r="AO383" s="9">
         <v>46153</v>
       </c>
-      <c r="AP383" s="8" t="s">
-        <v>1472</v>
-      </c>
     </row>
-    <row r="384" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A384" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]BH!$A$2:$A$32,MATCH($D384,[2]BH!$D$2:$D$32,0))="","",INDEX([2]BH!$A$2:$A$32,MATCH($D384,[2]BH!$D$2:$D$32,0))),"")</f>
         <v>Rejected</v>
@@ -62415,11 +61278,8 @@
       <c r="AO384" s="9">
         <v>46119</v>
       </c>
-      <c r="AP384" s="8" t="s">
-        <v>1474</v>
-      </c>
     </row>
-    <row r="385" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A385" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]ORTHO!$A$2:$A$16,MATCH($D385,[2]ORTHO!$D$2:$D$16,0))="","",INDEX([2]ORTHO!$A$2:$A$16,MATCH($D385,[2]ORTHO!$D$2:$D$16,0))),"")</f>
         <v>Pending</v>
@@ -62536,11 +61396,8 @@
       <c r="AO385" s="9">
         <v>46105</v>
       </c>
-      <c r="AP385" s="8" t="s">
-        <v>1476</v>
-      </c>
     </row>
-    <row r="386" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A386" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]BH!$A$2:$A$33,MATCH($D386,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$A$2:$A$33,MATCH($D386,[5]BH!$D$2:$D$33,0))),"")</f>
         <v>Pending</v>
@@ -62657,11 +61514,8 @@
       <c r="AO386" s="9">
         <v>46181</v>
       </c>
-      <c r="AP386" s="8" t="s">
-        <v>1477</v>
-      </c>
     </row>
-    <row r="387" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A387" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]BH!$A$2:$A$12,MATCH($D387,[4]BH!$D$2:$D$12,0))="","",INDEX([4]BH!$A$2:$A$12,MATCH($D387,[4]BH!$D$2:$D$12,0))),"")</f>
         <v>Denied</v>
@@ -62778,11 +61632,8 @@
       <c r="AO387" s="9">
         <v>46153</v>
       </c>
-      <c r="AP387" s="8" t="s">
-        <v>1478</v>
-      </c>
     </row>
-    <row r="388" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A388" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$A$2:$A$34,MATCH($D388,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$A$2:$A$34,MATCH($D388,[4]DME!$D$2:$D$34,0))),"")</f>
         <v/>
@@ -62903,11 +61754,8 @@
       <c r="AO388" s="9">
         <v>46134</v>
       </c>
-      <c r="AP388" s="8" t="s">
-        <v>1479</v>
-      </c>
     </row>
-    <row r="389" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A389" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]GAE!$A$2:$A$8,MATCH($D389,[4]GAE!$D$2:$D$8,0))="","",INDEX([4]GAE!$A$2:$A$8,MATCH($D389,[4]GAE!$D$2:$D$8,0))),"")</f>
         <v>Denied</v>
@@ -63036,11 +61884,8 @@
       <c r="AO389" s="9">
         <v>46152</v>
       </c>
-      <c r="AP389" s="8" t="s">
-        <v>1482</v>
-      </c>
     </row>
-    <row r="390" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A390" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]BH!$A$2:$A$12,MATCH($D390,[4]BH!$D$2:$D$12,0))="","",INDEX([4]BH!$A$2:$A$12,MATCH($D390,[4]BH!$D$2:$D$12,0))),"")</f>
         <v>Denied</v>
@@ -63159,11 +62004,8 @@
       <c r="AO390" s="9">
         <v>46153</v>
       </c>
-      <c r="AP390" s="8" t="s">
-        <v>1483</v>
-      </c>
     </row>
-    <row r="391" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A391" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]BH!$A$2:$A$17,MATCH($D391,[1]BH!$D$2:$D$17,0))="","",INDEX([1]BH!$A$2:$A$17,MATCH($D391,[1]BH!$D$2:$D$17,0))),"")</f>
         <v>Received</v>
@@ -63280,11 +62122,8 @@
       <c r="AO391" s="9">
         <v>46057</v>
       </c>
-      <c r="AP391" s="8" t="s">
-        <v>1484</v>
-      </c>
     </row>
-    <row r="392" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A392" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]BH!$A$2:$A$12,MATCH($D392,[4]BH!$D$2:$D$12,0))="","",INDEX([4]BH!$A$2:$A$12,MATCH($D392,[4]BH!$D$2:$D$12,0))),"")</f>
         <v>Finalized</v>
@@ -63403,11 +62242,8 @@
       <c r="AO392" s="9">
         <v>46153</v>
       </c>
-      <c r="AP392" s="8" t="s">
-        <v>1485</v>
-      </c>
     </row>
-    <row r="393" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A393" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$A$2:$A$34,MATCH($D393,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$A$2:$A$34,MATCH($D393,[4]DME!$D$2:$D$34,0))),"")</f>
         <v>Under Review</v>
@@ -63524,11 +62360,8 @@
       <c r="AO393" s="9">
         <v>46150</v>
       </c>
-      <c r="AP393" s="8" t="s">
-        <v>1487</v>
-      </c>
     </row>
-    <row r="394" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A394" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]ORTHO!$A$2:$A$21,MATCH($D394,[4]ORTHO!$D$2:$D$21,0))="","",INDEX([4]ORTHO!$A$2:$A$21,MATCH($D394,[4]ORTHO!$D$2:$D$21,0))),"")</f>
         <v>Denied</v>
@@ -63649,11 +62482,8 @@
       <c r="AO394" s="9">
         <v>46147</v>
       </c>
-      <c r="AP394" s="8" t="s">
-        <v>1493</v>
-      </c>
     </row>
-    <row r="395" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A395" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]US!$A$2:$A$23,MATCH($D395,[4]US!$D$2:$D$23,0))="","",INDEX([4]US!$A$2:$A$23,MATCH($D395,[4]US!$D$2:$D$23,0))),"")</f>
         <v>Under Review</v>
@@ -63770,11 +62600,8 @@
       <c r="AO395" s="9">
         <v>46148</v>
       </c>
-      <c r="AP395" s="8" t="s">
-        <v>1495</v>
-      </c>
     </row>
-    <row r="396" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A396" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]BH!$A$2:$A$12,MATCH($D396,[4]BH!$D$2:$D$12,0))="","",INDEX([4]BH!$A$2:$A$12,MATCH($D396,[4]BH!$D$2:$D$12,0))),"")</f>
         <v>Denied</v>
@@ -63891,11 +62718,8 @@
       <c r="AO396" s="9">
         <v>46153</v>
       </c>
-      <c r="AP396" s="8" t="s">
-        <v>1496</v>
-      </c>
     </row>
-    <row r="397" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A397" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$A$2:$A$34,MATCH($D397,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$A$2:$A$34,MATCH($D397,[4]DME!$D$2:$D$34,0))),"")</f>
         <v/>
@@ -64016,11 +62840,8 @@
       <c r="AO397" s="9">
         <v>46140</v>
       </c>
-      <c r="AP397" s="8" t="s">
-        <v>1498</v>
-      </c>
     </row>
-    <row r="398" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A398" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]ORTHO!$A$2:$A$21,MATCH($D398,[4]ORTHO!$D$2:$D$21,0))="","",INDEX([4]ORTHO!$A$2:$A$21,MATCH($D398,[4]ORTHO!$D$2:$D$21,0))),"")</f>
         <v>Denied</v>
@@ -64141,11 +62962,8 @@
       <c r="AO398" s="9">
         <v>46148</v>
       </c>
-      <c r="AP398" s="8" t="s">
-        <v>1501</v>
-      </c>
     </row>
-    <row r="399" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A399" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$A$2:$A$34,MATCH($D399,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$A$2:$A$34,MATCH($D399,[4]DME!$D$2:$D$34,0))),"")</f>
         <v/>
@@ -64266,11 +63084,8 @@
       <c r="AO399" s="9">
         <v>46189</v>
       </c>
-      <c r="AP399" s="8" t="s">
-        <v>1503</v>
-      </c>
     </row>
-    <row r="400" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A400" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]BH!$A$2:$A$17,MATCH($D400,[1]BH!$D$2:$D$17,0))="","",INDEX([1]BH!$A$2:$A$17,MATCH($D400,[1]BH!$D$2:$D$17,0))),"")</f>
         <v>Rejected</v>
@@ -64387,11 +63202,8 @@
       <c r="AO400" s="9">
         <v>46188</v>
       </c>
-      <c r="AP400" s="8" t="s">
-        <v>1505</v>
-      </c>
     </row>
-    <row r="401" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A401" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$A$2:$A$34,MATCH($D401,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$A$2:$A$34,MATCH($D401,[4]DME!$D$2:$D$34,0))),"")</f>
         <v/>
@@ -64512,11 +63324,8 @@
       <c r="AO401" s="9">
         <v>46153</v>
       </c>
-      <c r="AP401" s="8" t="s">
-        <v>1508</v>
-      </c>
     </row>
-    <row r="402" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A402" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]ORTHO!$A$2:$A$21,MATCH($D402,[4]ORTHO!$D$2:$D$21,0))="","",INDEX([4]ORTHO!$A$2:$A$21,MATCH($D402,[4]ORTHO!$D$2:$D$21,0))),"")</f>
         <v>Denied</v>
@@ -64639,11 +63448,8 @@
       <c r="AO402" s="9">
         <v>46184</v>
       </c>
-      <c r="AP402" s="8" t="s">
-        <v>1512</v>
-      </c>
     </row>
-    <row r="403" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A403" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]BH!$A$2:$A$32,MATCH($D403,[2]BH!$D$2:$D$32,0))="","",INDEX([2]BH!$A$2:$A$32,MATCH($D403,[2]BH!$D$2:$D$32,0))),"")</f>
         <v>Denied</v>
@@ -64760,11 +63566,8 @@
       <c r="AO403" s="9">
         <v>46119</v>
       </c>
-      <c r="AP403" s="8" t="s">
-        <v>1514</v>
-      </c>
     </row>
-    <row r="404" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A404" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]US!$A$2:$A$15,MATCH($D404,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$A$2:$A$15,MATCH($D404,[2]US!$D$2:$D$15,0))),"")</f>
         <v>Finalized</v>
@@ -64883,11 +63686,8 @@
       <c r="AO404" s="9">
         <v>46121</v>
       </c>
-      <c r="AP404" s="8" t="s">
-        <v>1516</v>
-      </c>
     </row>
-    <row r="405" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A405" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]US!$A$2:$A$23,MATCH($D405,[4]US!$D$2:$D$23,0))="","",INDEX([4]US!$A$2:$A$23,MATCH($D405,[4]US!$D$2:$D$23,0))),"")</f>
         <v>Under Review</v>
@@ -65006,11 +63806,8 @@
       <c r="AO405" s="9">
         <v>46148</v>
       </c>
-      <c r="AP405" s="8" t="s">
-        <v>1518</v>
-      </c>
     </row>
-    <row r="406" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A406" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]US!$A$2:$A$23,MATCH($D406,[4]US!$D$2:$D$23,0))="","",INDEX([4]US!$A$2:$A$23,MATCH($D406,[4]US!$D$2:$D$23,0))),"")</f>
         <v>Denied</v>
@@ -65131,11 +63928,8 @@
       <c r="AO406" s="9">
         <v>46148</v>
       </c>
-      <c r="AP406" s="8" t="s">
-        <v>1520</v>
-      </c>
     </row>
-    <row r="407" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A407" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$A$2:$A$34,MATCH($D407,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$A$2:$A$34,MATCH($D407,[4]DME!$D$2:$D$34,0))),"")</f>
         <v/>
@@ -65256,11 +64050,8 @@
       <c r="AO407" s="9">
         <v>46153</v>
       </c>
-      <c r="AP407" s="8" t="s">
-        <v>1522</v>
-      </c>
     </row>
-    <row r="408" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A408" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$A$2:$A$34,MATCH($D408,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$A$2:$A$34,MATCH($D408,[4]DME!$D$2:$D$34,0))),"")</f>
         <v/>
@@ -65383,11 +64174,8 @@
       <c r="AO408" s="9">
         <v>46153</v>
       </c>
-      <c r="AP408" s="8" t="s">
-        <v>1523</v>
-      </c>
     </row>
-    <row r="409" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A409" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]ORTHO!$A$2:$A$21,MATCH($D409,[4]ORTHO!$D$2:$D$21,0))="","",INDEX([4]ORTHO!$A$2:$A$21,MATCH($D409,[4]ORTHO!$D$2:$D$21,0))),"")</f>
         <v>Denied</v>
@@ -65512,11 +64300,8 @@
       <c r="AO409" s="9">
         <v>46197</v>
       </c>
-      <c r="AP409" s="8" t="s">
-        <v>1527</v>
-      </c>
     </row>
-    <row r="410" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A410" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]US!$A$2:$A$23,MATCH($D410,[4]US!$D$2:$D$23,0))="","",INDEX([4]US!$A$2:$A$23,MATCH($D410,[4]US!$D$2:$D$23,0))),"")</f>
         <v>Under Review</v>
@@ -65632,11 +64417,8 @@
       <c r="AO410" s="9">
         <v>46140</v>
       </c>
-      <c r="AP410" s="8" t="s">
-        <v>1530</v>
-      </c>
     </row>
-    <row r="411" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A411" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]BH!$A$2:$A$33,MATCH($D411,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$A$2:$A$33,MATCH($D411,[5]BH!$D$2:$D$33,0))),"")</f>
         <v>Rejected</v>
@@ -65751,11 +64533,8 @@
       <c r="AO411" s="9">
         <v>46180</v>
       </c>
-      <c r="AP411" s="8" t="s">
-        <v>1532</v>
-      </c>
     </row>
-    <row r="412" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A412" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]DME!$A$2:$A$35,MATCH($D412,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$A$2:$A$35,MATCH($D412,[5]DME!$D$2:$D$35,0))),"")</f>
         <v>Under Review</v>
@@ -65874,11 +64653,8 @@
       <c r="AO412" s="9">
         <v>46217</v>
       </c>
-      <c r="AP412" s="8" t="s">
-        <v>1534</v>
-      </c>
     </row>
-    <row r="413" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A413" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]DME!$A$2:$A$35,MATCH($D413,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$A$2:$A$35,MATCH($D413,[5]DME!$D$2:$D$35,0))),"")</f>
         <v>Finalized</v>
@@ -65997,11 +64773,8 @@
       <c r="AO413" s="9">
         <v>46162</v>
       </c>
-      <c r="AP413" s="8" t="s">
-        <v>1536</v>
-      </c>
     </row>
-    <row r="414" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A414" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$A$2:$A$34,MATCH($D414,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$A$2:$A$34,MATCH($D414,[4]DME!$D$2:$D$34,0))),"")</f>
         <v/>
@@ -66122,11 +64895,8 @@
       <c r="AO414" s="9">
         <v>46133</v>
       </c>
-      <c r="AP414" s="8" t="s">
-        <v>1538</v>
-      </c>
     </row>
-    <row r="415" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A415" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]GAE!$A$2:$A$23,MATCH($D415,[6]GAE!$D$2:$D$23,0))="","",INDEX([6]GAE!$A$2:$A$23,MATCH($D415,[6]GAE!$D$2:$D$23,0))),"")</f>
         <v>Denied</v>
@@ -66253,11 +65023,8 @@
       <c r="AO415" s="9">
         <v>46216</v>
       </c>
-      <c r="AP415" s="8" t="s">
-        <v>1541</v>
-      </c>
     </row>
-    <row r="416" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A416" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]ORTHO!$A$2:$A$21,MATCH($D416,[4]ORTHO!$D$2:$D$21,0))="","",INDEX([4]ORTHO!$A$2:$A$21,MATCH($D416,[4]ORTHO!$D$2:$D$21,0))),"")</f>
         <v>Denied</v>
@@ -66374,11 +65141,8 @@
       <c r="AO416" s="9">
         <v>46119</v>
       </c>
-      <c r="AP416" s="8" t="s">
-        <v>1543</v>
-      </c>
     </row>
-    <row r="417" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A417" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]ORTHO!$A$2:$A$24,MATCH($D417,[5]ORTHO!$D$2:$D$24,0))="","",INDEX([5]ORTHO!$A$2:$A$24,MATCH($D417,[5]ORTHO!$D$2:$D$24,0))),"")</f>
         <v>Denied</v>
@@ -66495,11 +65259,8 @@
       <c r="AO417" s="9">
         <v>46153</v>
       </c>
-      <c r="AP417" s="8" t="s">
-        <v>1545</v>
-      </c>
     </row>
-    <row r="418" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A418" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]DME!$A$2:$A$35,MATCH($D418,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$A$2:$A$35,MATCH($D418,[5]DME!$D$2:$D$35,0))),"")</f>
         <v>Denied</v>
@@ -66620,11 +65381,8 @@
       <c r="AO418" s="9">
         <v>46157</v>
       </c>
-      <c r="AP418" s="8" t="s">
-        <v>1547</v>
-      </c>
     </row>
-    <row r="419" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A419" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]ORTHO!$A$2:$A$24,MATCH($D419,[5]ORTHO!$D$2:$D$24,0))="","",INDEX([5]ORTHO!$A$2:$A$24,MATCH($D419,[5]ORTHO!$D$2:$D$24,0))),"")</f>
         <v>Under Review</v>
@@ -66743,11 +65501,8 @@
       <c r="AO419" s="9">
         <v>46149</v>
       </c>
-      <c r="AP419" s="8" t="s">
-        <v>1555</v>
-      </c>
     </row>
-    <row r="420" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A420" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]BH!$A$2:$A$12,MATCH($D420,[4]BH!$D$2:$D$12,0))="","",INDEX([4]BH!$A$2:$A$12,MATCH($D420,[4]BH!$D$2:$D$12,0))),"")</f>
         <v>Denied</v>
@@ -66862,11 +65617,8 @@
       <c r="AO420" s="9">
         <v>46153</v>
       </c>
-      <c r="AP420" s="8" t="s">
-        <v>1558</v>
-      </c>
     </row>
-    <row r="421" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A421" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]DME!$A$2:$A$35,MATCH($D421,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$A$2:$A$35,MATCH($D421,[5]DME!$D$2:$D$35,0))),"")</f>
         <v>Denied</v>
@@ -66987,11 +65739,8 @@
       <c r="AO421" s="9">
         <v>46162</v>
       </c>
-      <c r="AP421" s="8" t="s">
-        <v>1561</v>
-      </c>
     </row>
-    <row r="422" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A422" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]BH!$A$2:$A$82,MATCH($D422,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$A$2:$A$82,MATCH($D422,[6]BH!$D$2:$D$82,0))),"")</f>
         <v/>
@@ -67106,9 +65855,8 @@
       <c r="AO422" s="9">
         <v>46274</v>
       </c>
-      <c r="AP422" s="8"/>
     </row>
-    <row r="423" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A423" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]DME!$A$2:$A$35,MATCH($D423,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$A$2:$A$35,MATCH($D423,[5]DME!$D$2:$D$35,0))),"")</f>
         <v>Finalized</v>
@@ -67233,11 +65981,8 @@
       <c r="AO423" s="9">
         <v>46183</v>
       </c>
-      <c r="AP423" s="8" t="s">
-        <v>1564</v>
-      </c>
     </row>
-    <row r="424" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A424" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]DME!$A$2:$A$35,MATCH($D424,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$A$2:$A$35,MATCH($D424,[5]DME!$D$2:$D$35,0))),"")</f>
         <v>Finalized</v>
@@ -67358,11 +66103,8 @@
       <c r="AO424" s="9">
         <v>46162</v>
       </c>
-      <c r="AP424" s="8" t="s">
-        <v>1566</v>
-      </c>
     </row>
-    <row r="425" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A425" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]GAE!$A$2:$A$7,MATCH($D425,[5]GAE!$D$2:$D$7,0))="","",INDEX([5]GAE!$A$2:$A$7,MATCH($D425,[5]GAE!$D$2:$D$7,0))),"")</f>
         <v>Finalized</v>
@@ -67487,11 +66229,8 @@
       <c r="AO425" s="9">
         <v>46182</v>
       </c>
-      <c r="AP425" s="8" t="s">
-        <v>1569</v>
-      </c>
     </row>
-    <row r="426" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A426" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]GAE!$A$2:$A$7,MATCH($D426,[5]GAE!$D$2:$D$7,0))="","",INDEX([5]GAE!$A$2:$A$7,MATCH($D426,[5]GAE!$D$2:$D$7,0))),"")</f>
         <v>Denied</v>
@@ -67618,11 +66357,8 @@
       <c r="AO426" s="9">
         <v>46182</v>
       </c>
-      <c r="AP426" s="8" t="s">
-        <v>1571</v>
-      </c>
     </row>
-    <row r="427" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A427" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]DME!$A$2:$A$35,MATCH($D427,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$A$2:$A$35,MATCH($D427,[5]DME!$D$2:$D$35,0))),"")</f>
         <v>Under Review</v>
@@ -67745,11 +66481,8 @@
       <c r="AO427" s="9">
         <v>46189</v>
       </c>
-      <c r="AP427" s="8" t="s">
-        <v>1572</v>
-      </c>
     </row>
-    <row r="428" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A428" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]BH!$A$2:$A$33,MATCH($D428,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$A$2:$A$33,MATCH($D428,[5]BH!$D$2:$D$33,0))),"")</f>
         <v>Finalized</v>
@@ -67866,11 +66599,8 @@
       <c r="AO428" s="9">
         <v>46180</v>
       </c>
-      <c r="AP428" s="8" t="s">
-        <v>1573</v>
-      </c>
     </row>
-    <row r="429" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A429" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]US!$A$2:$A$19,MATCH($D429,[5]US!$D$2:$D$19,0))="","",INDEX([5]US!$A$2:$A$19,MATCH($D429,[5]US!$D$2:$D$19,0))),"")</f>
         <v>PAID</v>
@@ -67989,11 +66719,8 @@
       <c r="AO429" s="9">
         <v>46164</v>
       </c>
-      <c r="AP429" s="8" t="s">
-        <v>1576</v>
-      </c>
     </row>
-    <row r="430" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A430" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]US!$A$2:$A$22,MATCH($D430,[6]US!$D$2:$D$22,0))="","",INDEX([6]US!$A$2:$A$22,MATCH($D430,[6]US!$D$2:$D$22,0))),"")</f>
         <v>Denied</v>
@@ -68116,11 +66843,8 @@
       <c r="AO430" s="9">
         <v>46195</v>
       </c>
-      <c r="AP430" s="8" t="s">
-        <v>1581</v>
-      </c>
     </row>
-    <row r="431" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A431" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]ORTHO!$A$2:$A$24,MATCH($D431,[5]ORTHO!$D$2:$D$24,0))="","",INDEX([5]ORTHO!$A$2:$A$24,MATCH($D431,[5]ORTHO!$D$2:$D$24,0))),"")</f>
         <v>Denied</v>
@@ -68243,11 +66967,8 @@
       <c r="AO431" s="9">
         <v>46161</v>
       </c>
-      <c r="AP431" s="8" t="s">
-        <v>1587</v>
-      </c>
     </row>
-    <row r="432" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A432" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D432,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D432,[6]DME!$D$2:$D$52,0))),"")</f>
         <v/>
@@ -68370,9 +67091,8 @@
       <c r="AO432" s="9">
         <v>46196</v>
       </c>
-      <c r="AP432" s="8"/>
     </row>
-    <row r="433" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A433" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]US!$A$2:$A$19,MATCH($D433,[5]US!$D$2:$D$19,0))="","",INDEX([5]US!$A$2:$A$19,MATCH($D433,[5]US!$D$2:$D$19,0))),"")</f>
         <v>Denied</v>
@@ -68493,11 +67213,8 @@
       <c r="AO433" s="9">
         <v>46164</v>
       </c>
-      <c r="AP433" s="8" t="s">
-        <v>1589</v>
-      </c>
     </row>
-    <row r="434" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A434" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]GAE!$A$2:$A$12,MATCH($D434,[1]GAE!$D$2:$D$12,0))="","",INDEX([1]GAE!$A$2:$A$12,MATCH($D434,[1]GAE!$D$2:$D$12,0))),"")</f>
         <v/>
@@ -68611,11 +67328,8 @@
       <c r="AO434" s="9">
         <v>46062</v>
       </c>
-      <c r="AP434" s="8" t="s">
-        <v>1594</v>
-      </c>
     </row>
-    <row r="435" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A435" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D435,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D435,[6]DME!$D$2:$D$52,0))),"")</f>
         <v/>
@@ -68740,9 +67454,8 @@
       <c r="AO435" s="9">
         <v>46196</v>
       </c>
-      <c r="AP435" s="8"/>
     </row>
-    <row r="436" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A436" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]ORTHO!$A$2:$A$10,MATCH($D436,[1]ORTHO!$D$2:$D$10,0))="","",INDEX([1]ORTHO!$A$2:$A$10,MATCH($D436,[1]ORTHO!$D$2:$D$10,0))),"")</f>
         <v/>
@@ -68847,11 +67560,8 @@
       <c r="AO436" s="9">
         <v>46058</v>
       </c>
-      <c r="AP436" s="8" t="s">
-        <v>1599</v>
-      </c>
     </row>
-    <row r="437" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A437" s="5" t="str">
         <f>IFERROR(IF(INDEX([1]ORTHO!$A$2:$A$10,MATCH($D437,[1]ORTHO!$D$2:$D$10,0))="","",INDEX([1]ORTHO!$A$2:$A$10,MATCH($D437,[1]ORTHO!$D$2:$D$10,0))),"")</f>
         <v/>
@@ -68952,11 +67662,8 @@
       <c r="AO437" s="9">
         <v>46079</v>
       </c>
-      <c r="AP437" s="8" t="s">
-        <v>1603</v>
-      </c>
     </row>
-    <row r="438" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A438" s="5" t="str">
         <f>IFERROR(IF(INDEX([3]ORTHO!$A$2:$A$11,MATCH($D438,[3]ORTHO!$D$2:$D$11,0))="","",INDEX([3]ORTHO!$A$2:$A$11,MATCH($D438,[3]ORTHO!$D$2:$D$11,0))),"")</f>
         <v>Finalized</v>
@@ -69079,11 +67786,8 @@
       <c r="AO438" s="9">
         <v>46083</v>
       </c>
-      <c r="AP438" s="8" t="s">
-        <v>1609</v>
-      </c>
     </row>
-    <row r="439" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A439" s="5" t="str">
         <f>IFERROR(IF(INDEX([3]DME!$A$2:$A$12,MATCH($D439,[3]DME!$D$2:$D$12,0))="","",INDEX([3]DME!$A$2:$A$12,MATCH($D439,[3]DME!$D$2:$D$12,0))),"")</f>
         <v>Denied</v>
@@ -69184,11 +67888,8 @@
       <c r="AO439" s="9">
         <v>46063</v>
       </c>
-      <c r="AP439" s="8" t="s">
-        <v>1612</v>
-      </c>
     </row>
-    <row r="440" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A440" s="5" t="str">
         <f>IFERROR(IF(INDEX([3]DME!$A$2:$A$12,MATCH($D440,[3]DME!$D$2:$D$12,0))="","",INDEX([3]DME!$A$2:$A$12,MATCH($D440,[3]DME!$D$2:$D$12,0))),"")</f>
         <v>Denied</v>
@@ -69291,11 +67992,8 @@
       <c r="AO440" s="9">
         <v>46099</v>
       </c>
-      <c r="AP440" s="8" t="s">
-        <v>1615</v>
-      </c>
     </row>
-    <row r="441" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A441" s="5" t="str">
         <f>IFERROR(IF(INDEX([3]ORTHO!$A$2:$A$11,MATCH($D441,[3]ORTHO!$D$2:$D$11,0))="","",INDEX([3]ORTHO!$A$2:$A$11,MATCH($D441,[3]ORTHO!$D$2:$D$11,0))),"")</f>
         <v>Denied</v>
@@ -69403,11 +68101,8 @@
       <c r="AO441" s="9">
         <v>46092</v>
       </c>
-      <c r="AP441" s="8" t="s">
-        <v>1618</v>
-      </c>
     </row>
-    <row r="442" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A442" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]GAE!$A$2:$A$4,MATCH($D442,[2]GAE!$D$2:$D$4,0))="","",INDEX([2]GAE!$A$2:$A$4,MATCH($D442,[2]GAE!$D$2:$D$4,0))),"")</f>
         <v>Under Review</v>
@@ -69521,11 +68216,8 @@
       <c r="AO442" s="9">
         <v>46119</v>
       </c>
-      <c r="AP442" s="8" t="s">
-        <v>1620</v>
-      </c>
     </row>
-    <row r="443" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A443" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]BH!$A$2:$A$82,MATCH($D443,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$A$2:$A$82,MATCH($D443,[6]BH!$D$2:$D$82,0))),"")</f>
         <v/>
@@ -69642,9 +68334,8 @@
       <c r="AO443" s="9">
         <v>46268</v>
       </c>
-      <c r="AP443" s="8"/>
     </row>
-    <row r="444" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A444" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]US!$A$2:$A$15,MATCH($D444,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$A$2:$A$15,MATCH($D444,[2]US!$D$2:$D$15,0))),"")</f>
         <v/>
@@ -69765,11 +68456,8 @@
       <c r="AO444" s="9">
         <v>46106</v>
       </c>
-      <c r="AP444" s="8" t="s">
-        <v>1622</v>
-      </c>
     </row>
-    <row r="445" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A445" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]BH!$A$2:$A$32,MATCH($D445,[2]BH!$D$2:$D$32,0))="","",INDEX([2]BH!$A$2:$A$32,MATCH($D445,[2]BH!$D$2:$D$32,0))),"")</f>
         <v>Denied</v>
@@ -69868,11 +68556,8 @@
       <c r="AO445" s="9">
         <v>46119</v>
       </c>
-      <c r="AP445" s="8" t="s">
-        <v>1623</v>
-      </c>
     </row>
-    <row r="446" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A446" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]BH!$A$2:$A$32,MATCH($D446,[2]BH!$D$2:$D$32,0))="","",INDEX([2]BH!$A$2:$A$32,MATCH($D446,[2]BH!$D$2:$D$32,0))),"")</f>
         <v>PAID</v>
@@ -69973,11 +68658,8 @@
       <c r="AO446" s="9">
         <v>46119</v>
       </c>
-      <c r="AP446" s="8" t="s">
-        <v>1626</v>
-      </c>
     </row>
-    <row r="447" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A447" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]ORTHO!$A$2:$A$21,MATCH($D447,[4]ORTHO!$D$2:$D$21,0))="","",INDEX([4]ORTHO!$A$2:$A$21,MATCH($D447,[4]ORTHO!$D$2:$D$21,0))),"")</f>
         <v>Under Review</v>
@@ -70082,11 +68764,8 @@
       <c r="AO447" s="9">
         <v>46133</v>
       </c>
-      <c r="AP447" s="8" t="s">
-        <v>1631</v>
-      </c>
     </row>
-    <row r="448" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A448" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]BH!$A$2:$A$12,MATCH($D448,[4]BH!$D$2:$D$12,0))="","",INDEX([4]BH!$A$2:$A$12,MATCH($D448,[4]BH!$D$2:$D$12,0))),"")</f>
         <v>Under Review</v>
@@ -70183,11 +68862,8 @@
       <c r="AO448" s="9">
         <v>46153</v>
       </c>
-      <c r="AP448" s="8" t="s">
-        <v>1633</v>
-      </c>
     </row>
-    <row r="449" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A449" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]ORTHO!$A$2:$A$21,MATCH($D449,[4]ORTHO!$D$2:$D$21,0))="","",INDEX([4]ORTHO!$A$2:$A$21,MATCH($D449,[4]ORTHO!$D$2:$D$21,0))),"")</f>
         <v>Under Review</v>
@@ -70290,11 +68966,8 @@
       <c r="AO449" s="9">
         <v>46164</v>
       </c>
-      <c r="AP449" s="8" t="s">
-        <v>1636</v>
-      </c>
     </row>
-    <row r="450" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A450" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]GAE!$A$2:$A$8,MATCH($D450,[4]GAE!$D$2:$D$8,0))="","",INDEX([4]GAE!$A$2:$A$8,MATCH($D450,[4]GAE!$D$2:$D$8,0))),"")</f>
         <v>PAID</v>
@@ -70403,11 +69076,8 @@
       <c r="AO450" s="9">
         <v>46152</v>
       </c>
-      <c r="AP450" s="8" t="s">
-        <v>1639</v>
-      </c>
     </row>
-    <row r="451" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A451" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$A$2:$A$34,MATCH($D451,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$A$2:$A$34,MATCH($D451,[4]DME!$D$2:$D$34,0))),"")</f>
         <v>Under Review</v>
@@ -70510,11 +69180,8 @@
       <c r="AO451" s="9">
         <v>46153</v>
       </c>
-      <c r="AP451" s="8" t="s">
-        <v>1641</v>
-      </c>
     </row>
-    <row r="452" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A452" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$A$2:$A$34,MATCH($D452,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$A$2:$A$34,MATCH($D452,[4]DME!$D$2:$D$34,0))),"")</f>
         <v>Under Review</v>
@@ -70613,11 +69280,8 @@
       <c r="AO452" s="9">
         <v>46140</v>
       </c>
-      <c r="AP452" s="8" t="s">
-        <v>1643</v>
-      </c>
     </row>
-    <row r="453" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A453" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]US!$A$2:$A$23,MATCH($D453,[4]US!$D$2:$D$23,0))="","",INDEX([4]US!$A$2:$A$23,MATCH($D453,[4]US!$D$2:$D$23,0))),"")</f>
         <v>Under Review</v>
@@ -70727,11 +69391,8 @@
       <c r="AO453" s="9">
         <v>46141</v>
       </c>
-      <c r="AP453" s="8" t="s">
-        <v>1645</v>
-      </c>
     </row>
-    <row r="454" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A454" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]BH!$A$2:$A$12,MATCH($D454,[4]BH!$D$2:$D$12,0))="","",INDEX([4]BH!$A$2:$A$12,MATCH($D454,[4]BH!$D$2:$D$12,0))),"")</f>
         <v>Under Review</v>
@@ -70828,11 +69489,8 @@
       <c r="AO454" s="9">
         <v>46153</v>
       </c>
-      <c r="AP454" s="8" t="s">
-        <v>1647</v>
-      </c>
     </row>
-    <row r="455" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A455" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]ORTHO!$A$2:$A$24,MATCH($D455,[5]ORTHO!$D$2:$D$24,0))="","",INDEX([5]ORTHO!$A$2:$A$24,MATCH($D455,[5]ORTHO!$D$2:$D$24,0))),"")</f>
         <v>PAID</v>
@@ -70931,11 +69589,8 @@
       <c r="AO455" s="9">
         <v>46155</v>
       </c>
-      <c r="AP455" s="8" t="s">
-        <v>1649</v>
-      </c>
     </row>
-    <row r="456" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A456" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]DME!$A$2:$A$35,MATCH($D456,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$A$2:$A$35,MATCH($D456,[5]DME!$D$2:$D$35,0))),"")</f>
         <v>Denied</v>
@@ -71034,11 +69689,8 @@
       <c r="AO456" s="9">
         <v>46162</v>
       </c>
-      <c r="AP456" s="8" t="s">
-        <v>1651</v>
-      </c>
     </row>
-    <row r="457" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A457" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]BH!$A$2:$A$33,MATCH($D457,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$A$2:$A$33,MATCH($D457,[5]BH!$D$2:$D$33,0))),"")</f>
         <v>Denied</v>
@@ -71137,11 +69789,8 @@
       <c r="AO457" s="9">
         <v>46182</v>
       </c>
-      <c r="AP457" s="8" t="s">
-        <v>1653</v>
-      </c>
     </row>
-    <row r="458" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A458" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]DME!$A$2:$A$35,MATCH($D458,[5]DME!$D$2:$D$35,0))="","",INDEX([5]DME!$A$2:$A$35,MATCH($D458,[5]DME!$D$2:$D$35,0))),"")</f>
         <v>Denied</v>
@@ -71244,11 +69893,8 @@
       <c r="AO458" s="9">
         <v>46162</v>
       </c>
-      <c r="AP458" s="8" t="s">
-        <v>1654</v>
-      </c>
     </row>
-    <row r="459" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A459" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]US!$A$2:$A$19,MATCH($D459,[5]US!$D$2:$D$19,0))="","",INDEX([5]US!$A$2:$A$19,MATCH($D459,[5]US!$D$2:$D$19,0))),"")</f>
         <v>Denied</v>
@@ -71369,11 +70015,8 @@
       <c r="AO459" s="9">
         <v>46164</v>
       </c>
-      <c r="AP459" s="8" t="s">
-        <v>1660</v>
-      </c>
     </row>
-    <row r="460" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A460" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]BH!$A$2:$A$33,MATCH($D460,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$A$2:$A$33,MATCH($D460,[5]BH!$D$2:$D$33,0))),"")</f>
         <v>Under Review</v>
@@ -71470,11 +70113,8 @@
       <c r="AO460" s="9">
         <v>46188</v>
       </c>
-      <c r="AP460" s="8" t="s">
-        <v>1662</v>
-      </c>
     </row>
-    <row r="461" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A461" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]GAE!$A$2:$A$7,MATCH($D461,[5]GAE!$D$2:$D$7,0))="","",INDEX([5]GAE!$A$2:$A$7,MATCH($D461,[5]GAE!$D$2:$D$7,0))),"")</f>
         <v>Under Review</v>
@@ -71581,11 +70221,8 @@
       <c r="AO461" s="9">
         <v>46182</v>
       </c>
-      <c r="AP461" s="8" t="s">
-        <v>1666</v>
-      </c>
     </row>
-    <row r="462" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A462" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]BH!$A$2:$A$33,MATCH($D462,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$A$2:$A$33,MATCH($D462,[5]BH!$D$2:$D$33,0))),"")</f>
         <v>Denied</v>
@@ -71684,11 +70321,8 @@
       <c r="AO462" s="9">
         <v>46181</v>
       </c>
-      <c r="AP462" s="8" t="s">
-        <v>1668</v>
-      </c>
     </row>
-    <row r="463" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A463" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]BH!$A$2:$A$33,MATCH($D463,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$A$2:$A$33,MATCH($D463,[5]BH!$D$2:$D$33,0))),"")</f>
         <v>Denied</v>
@@ -71789,11 +70423,8 @@
       <c r="AO463" s="9">
         <v>46182</v>
       </c>
-      <c r="AP463" s="8" t="s">
-        <v>1670</v>
-      </c>
     </row>
-    <row r="464" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A464" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]BH!$A$2:$A$33,MATCH($D464,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$A$2:$A$33,MATCH($D464,[5]BH!$D$2:$D$33,0))),"")</f>
         <v>Denied</v>
@@ -71892,11 +70523,8 @@
       <c r="AO464" s="9">
         <v>46182</v>
       </c>
-      <c r="AP464" s="8" t="s">
-        <v>1672</v>
-      </c>
     </row>
-    <row r="465" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A465" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]BH!$A$2:$A$33,MATCH($D465,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$A$2:$A$33,MATCH($D465,[5]BH!$D$2:$D$33,0))),"")</f>
         <v>Finalized</v>
@@ -71993,11 +70621,8 @@
       <c r="AO465" s="9">
         <v>46180</v>
       </c>
-      <c r="AP465" s="8" t="s">
-        <v>1675</v>
-      </c>
     </row>
-    <row r="466" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A466" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]BH!$A$2:$A$33,MATCH($D466,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$A$2:$A$33,MATCH($D466,[5]BH!$D$2:$D$33,0))),"")</f>
         <v>Under Review</v>
@@ -72094,11 +70719,8 @@
       <c r="AO466" s="9">
         <v>46182</v>
       </c>
-      <c r="AP466" s="8" t="s">
-        <v>1676</v>
-      </c>
     </row>
-    <row r="467" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A467" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]BH!$A$2:$A$82,MATCH($D467,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$A$2:$A$82,MATCH($D467,[6]BH!$D$2:$D$82,0))),"")</f>
         <v/>
@@ -72203,11 +70825,8 @@
       <c r="AO467" s="9">
         <v>46191</v>
       </c>
-      <c r="AP467" s="8" t="s">
-        <v>1683</v>
-      </c>
     </row>
-    <row r="468" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A468" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]BH!$A$2:$A$82,MATCH($D468,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$A$2:$A$82,MATCH($D468,[6]BH!$D$2:$D$82,0))),"")</f>
         <v/>
@@ -72306,11 +70925,8 @@
       <c r="AO468" s="9">
         <v>46217</v>
       </c>
-      <c r="AP468" s="8" t="s">
-        <v>1685</v>
-      </c>
     </row>
-    <row r="469" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A469" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]US!$A$2:$A$22,MATCH($D469,[6]US!$D$2:$D$22,0))="","",INDEX([6]US!$A$2:$A$22,MATCH($D469,[6]US!$D$2:$D$22,0))),"")</f>
         <v/>
@@ -72420,11 +71036,8 @@
       <c r="AO469" s="9">
         <v>46195</v>
       </c>
-      <c r="AP469" s="8" t="s">
-        <v>1686</v>
-      </c>
     </row>
-    <row r="470" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A470" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D470,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D470,[6]DME!$D$2:$D$52,0))),"")</f>
         <v>Under Review</v>
@@ -72527,11 +71140,8 @@
       <c r="AO470" s="9">
         <v>46185</v>
       </c>
-      <c r="AP470" s="8" t="s">
-        <v>1691</v>
-      </c>
     </row>
-    <row r="471" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A471" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]US!$A$2:$A$22,MATCH($D471,[6]US!$D$2:$D$22,0))="","",INDEX([6]US!$A$2:$A$22,MATCH($D471,[6]US!$D$2:$D$22,0))),"")</f>
         <v/>
@@ -72630,11 +71240,8 @@
       <c r="AO471" s="9">
         <v>46195</v>
       </c>
-      <c r="AP471" s="8" t="s">
-        <v>1697</v>
-      </c>
     </row>
-    <row r="472" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A472" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]BH!$A$2:$A$82,MATCH($D472,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$A$2:$A$82,MATCH($D472,[6]BH!$D$2:$D$82,0))),"")</f>
         <v/>
@@ -72731,11 +71338,8 @@
       <c r="AO472" s="9">
         <v>46217</v>
       </c>
-      <c r="AP472" s="8" t="s">
-        <v>1700</v>
-      </c>
     </row>
-    <row r="473" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A473" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]BH!$A$2:$A$82,MATCH($D473,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$A$2:$A$82,MATCH($D473,[6]BH!$D$2:$D$82,0))),"")</f>
         <v>Under Review</v>
@@ -72832,11 +71436,8 @@
       <c r="AO473" s="9">
         <v>46217</v>
       </c>
-      <c r="AP473" s="8" t="s">
-        <v>1702</v>
-      </c>
     </row>
-    <row r="474" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A474" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]BH!$A$2:$A$82,MATCH($D474,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$A$2:$A$82,MATCH($D474,[6]BH!$D$2:$D$82,0))),"")</f>
         <v/>
@@ -72933,11 +71534,8 @@
       <c r="AO474" s="9">
         <v>46217</v>
       </c>
-      <c r="AP474" s="8" t="s">
-        <v>1704</v>
-      </c>
     </row>
-    <row r="475" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A475" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]BH!$A$2:$A$82,MATCH($D475,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$A$2:$A$82,MATCH($D475,[6]BH!$D$2:$D$82,0))),"")</f>
         <v>Pending</v>
@@ -73036,11 +71634,8 @@
       <c r="AO475" s="9">
         <v>46217</v>
       </c>
-      <c r="AP475" s="8" t="s">
-        <v>1705</v>
-      </c>
     </row>
-    <row r="476" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A476" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]US!$A$2:$A$22,MATCH($D476,[6]US!$D$2:$D$22,0))="","",INDEX([6]US!$A$2:$A$22,MATCH($D476,[6]US!$D$2:$D$22,0))),"")</f>
         <v/>
@@ -73146,11 +71741,8 @@
       <c r="AO476" s="9">
         <v>46195</v>
       </c>
-      <c r="AP476" s="8" t="s">
-        <v>1706</v>
-      </c>
     </row>
-    <row r="477" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A477" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]BH!$A$2:$A$82,MATCH($D477,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$A$2:$A$82,MATCH($D477,[6]BH!$D$2:$D$82,0))),"")</f>
         <v/>
@@ -73256,11 +71848,8 @@
       <c r="AO477" s="9">
         <v>46234</v>
       </c>
-      <c r="AP477" s="8" t="s">
-        <v>1710</v>
-      </c>
     </row>
-    <row r="478" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A478" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]BH!$A$2:$A$82,MATCH($D478,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$A$2:$A$82,MATCH($D478,[6]BH!$D$2:$D$82,0))),"")</f>
         <v/>
@@ -73357,11 +71946,8 @@
       <c r="AO478" s="9">
         <v>46217</v>
       </c>
-      <c r="AP478" s="8" t="s">
-        <v>1712</v>
-      </c>
     </row>
-    <row r="479" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A479" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]ORTHO!$A$2:$A$39,MATCH($D479,[6]ORTHO!$D$2:$D$39,0))="","",INDEX([6]ORTHO!$A$2:$A$39,MATCH($D479,[6]ORTHO!$D$2:$D$39,0))),"")</f>
         <v>Under Review</v>
@@ -73464,11 +72050,8 @@
       <c r="AO479" s="9">
         <v>46203</v>
       </c>
-      <c r="AP479" s="8" t="s">
-        <v>1716</v>
-      </c>
     </row>
-    <row r="480" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A480" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D480,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D480,[6]DME!$D$2:$D$52,0))),"")</f>
         <v>Under Review</v>
@@ -73569,11 +72152,8 @@
       <c r="AO480" s="9">
         <v>46205</v>
       </c>
-      <c r="AP480" s="8" t="s">
-        <v>1728</v>
-      </c>
     </row>
-    <row r="481" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A481" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]BH!$A$2:$A$82,MATCH($D481,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$A$2:$A$82,MATCH($D481,[6]BH!$D$2:$D$82,0))),"")</f>
         <v/>
@@ -73670,11 +72250,8 @@
       <c r="AO481" s="9">
         <v>46217</v>
       </c>
-      <c r="AP481" s="8" t="s">
-        <v>1730</v>
-      </c>
     </row>
-    <row r="482" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A482" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]BH!$A$2:$A$82,MATCH($D482,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$A$2:$A$82,MATCH($D482,[6]BH!$D$2:$D$82,0))),"")</f>
         <v/>
@@ -73773,11 +72350,8 @@
       <c r="AO482" s="9">
         <v>46234</v>
       </c>
-      <c r="AP482" s="8" t="s">
-        <v>1734</v>
-      </c>
     </row>
-    <row r="483" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A483" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]ORTHO!$A$2:$A$39,MATCH($D483,[6]ORTHO!$D$2:$D$39,0))="","",INDEX([6]ORTHO!$A$2:$A$39,MATCH($D483,[6]ORTHO!$D$2:$D$39,0))),"")</f>
         <v/>
@@ -73878,12 +72452,9 @@
       <c r="AO483" s="9">
         <v>46210</v>
       </c>
-      <c r="AP483" s="8" t="s">
-        <v>1738</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AP483" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
+  <autoFilter ref="A1:AO483" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <conditionalFormatting sqref="L2:L483">
     <cfRule type="expression" dxfId="39" priority="1">
       <formula>AND($L2&lt;&gt;"", $L2&gt;=0, $L2&lt;=5)</formula>

--- a/Specialty Claims 2026-S1/ALL Claims 2026-S1 - Master.xlsx
+++ b/Specialty Claims 2026-S1/ALL Claims 2026-S1 - Master.xlsx
@@ -268,7 +268,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22671" uniqueCount="1762">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22721" uniqueCount="1771">
   <si>
     <t>ALL Claims 2026-S1 - Master</t>
   </si>
@@ -5554,6 +5554,33 @@
   </si>
   <si>
     <t xml:space="preserve">Statuses currently in use: Denied, Finalized, Not found, PAID, Pending, Received, Rejected, Under Review.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Every one of the 482 claims for 2026 S1, all specialties and all six months in one place, on the 'All Claims' tab.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    1 - Due in 5 days or less: 21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    2 - Due in 6-30 days: 25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    3 - Due in 31+ days: 155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    4 - Past deadline: 238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    5 - No limit on file: 43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Claim Status, Notes, Processed Date and Latest Date Worked (shaded pale green) are formulas. Each one looks up its claim by Primary Claim ID in the matching specialty sheet of the matching monthly workbook and returns whatever is entered there. Edit any of the four in a monthly file, save it, and this file shows the change.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    1 - Due in 5 days or less: 20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    4 - Past deadline: 239</t>
   </si>
 </sst>
 </file>
@@ -14662,7 +14689,7 @@
     </row>
     <row r="3" spans="1:1" ht="30" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>1</v>
+        <v>1762</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
@@ -14680,27 +14707,27 @@
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>4</v>
+        <v>1769</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>5</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>6</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>7</v>
+        <v>1770</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>8</v>
+        <v>1767</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
@@ -14721,7 +14748,7 @@
     </row>
     <row r="16" spans="1:1" ht="45" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>11</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="17" spans="1:1" ht="30" x14ac:dyDescent="0.25">
@@ -18345,7 +18372,7 @@
       </c>
       <c r="B30" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$B$2:$B$34,MATCH($D30,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$B$2:$B$34,MATCH($D30,[4]DME!$D$2:$D$34,0))),"")</f>
-        <v>Acodes not included in auth/referral</v>
+        <v>Adjusted balance - Acodes not included in auth/referral</v>
       </c>
       <c r="C30" s="6">
         <f>IFERROR(IF(INDEX([4]DME!$C$2:$C$34,MATCH($D30,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$C$2:$C$34,MATCH($D30,[4]DME!$D$2:$D$34,0))),"")</f>
@@ -18941,7 +18968,7 @@
     <row r="35" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D35,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D35,[6]DME!$D$2:$D$52,0))),"")</f>
-        <v>Denied</v>
+        <v>Finalized</v>
       </c>
       <c r="B35" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$B$2:$B$52,MATCH($D35,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$B$2:$B$52,MATCH($D35,[6]DME!$D$2:$D$52,0))),"")</f>
@@ -19927,7 +19954,7 @@
         <v>46203</v>
       </c>
       <c r="D43" s="7">
-        <v>563011043</v>
+        <v>570988442</v>
       </c>
       <c r="E43" s="8" t="s">
         <v>335</v>
@@ -20647,7 +20674,7 @@
         <v/>
       </c>
       <c r="D49" s="7">
-        <v>562567344</v>
+        <v>570979198</v>
       </c>
       <c r="E49" s="8" t="s">
         <v>361</v>
@@ -21147,7 +21174,7 @@
         <v>46225</v>
       </c>
       <c r="D53" s="7">
-        <v>565104372</v>
+        <v>570979060</v>
       </c>
       <c r="E53" s="8" t="s">
         <v>379</v>
@@ -21275,7 +21302,7 @@
         <v>46224</v>
       </c>
       <c r="D54" s="7">
-        <v>565107861</v>
+        <v>569910853</v>
       </c>
       <c r="E54" s="8" t="s">
         <v>383</v>
@@ -21401,7 +21428,7 @@
         <v>46231</v>
       </c>
       <c r="D55" s="7">
-        <v>562152108</v>
+        <v>570976486</v>
       </c>
       <c r="E55" s="8" t="s">
         <v>388</v>
@@ -21887,7 +21914,7 @@
         <v>46220</v>
       </c>
       <c r="D59" s="7">
-        <v>562169362</v>
+        <v>571031540</v>
       </c>
       <c r="E59" s="8" t="s">
         <v>411</v>
@@ -22232,7 +22259,7 @@
     <row r="62" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A62" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]ORTHO!$A$2:$A$39,MATCH($D62,[6]ORTHO!$D$2:$D$39,0))="","",INDEX([6]ORTHO!$A$2:$A$39,MATCH($D62,[6]ORTHO!$D$2:$D$39,0))),"")</f>
-        <v>Denied</v>
+        <v>Finalized</v>
       </c>
       <c r="B62" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]ORTHO!$B$2:$B$39,MATCH($D62,[6]ORTHO!$D$2:$D$39,0))="","",INDEX([6]ORTHO!$B$2:$B$39,MATCH($D62,[6]ORTHO!$D$2:$D$39,0))),"")</f>
@@ -22243,7 +22270,7 @@
         <v>46196</v>
       </c>
       <c r="D62" s="7">
-        <v>562553945</v>
+        <v>570992620</v>
       </c>
       <c r="E62" s="8" t="s">
         <v>428</v>
@@ -22365,7 +22392,7 @@
         <v>46197</v>
       </c>
       <c r="D63" s="7">
-        <v>562198452</v>
+        <v>570992408</v>
       </c>
       <c r="E63" s="8" t="s">
         <v>432</v>
@@ -22592,18 +22619,18 @@
     <row r="65" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]ORTHO!$A$2:$A$24,MATCH($D65,[5]ORTHO!$D$2:$D$24,0))="","",INDEX([5]ORTHO!$A$2:$A$24,MATCH($D65,[5]ORTHO!$D$2:$D$24,0))),"")</f>
-        <v/>
+        <v>Pending</v>
       </c>
       <c r="B65" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]ORTHO!$B$2:$B$24,MATCH($D65,[5]ORTHO!$D$2:$D$24,0))="","",INDEX([5]ORTHO!$B$2:$B$24,MATCH($D65,[5]ORTHO!$D$2:$D$24,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C65" s="6" t="str">
+        <v xml:space="preserve">Claim not found - Resubmitted - Asked April to print </v>
+      </c>
+      <c r="C65" s="6">
         <f>IFERROR(IF(INDEX([5]ORTHO!$C$2:$C$24,MATCH($D65,[5]ORTHO!$D$2:$D$24,0))="","",INDEX([5]ORTHO!$C$2:$C$24,MATCH($D65,[5]ORTHO!$D$2:$D$24,0))),"")</f>
-        <v/>
+        <v>46184</v>
       </c>
       <c r="D65" s="7">
-        <v>559611258</v>
+        <v>568765283</v>
       </c>
       <c r="E65" s="8" t="s">
         <v>438</v>
@@ -22623,21 +22650,21 @@
       <c r="J65" s="8" t="s">
         <v>439</v>
       </c>
-      <c r="K65" s="6" t="str">
+      <c r="K65" s="6">
         <f>IFERROR(IF(INDEX([5]ORTHO!$K$2:$K$24,MATCH($D65,[5]ORTHO!$D$2:$D$24,0))="","",INDEX([5]ORTHO!$K$2:$K$24,MATCH($D65,[5]ORTHO!$D$2:$D$24,0))),"")</f>
-        <v/>
+        <v>46250</v>
       </c>
       <c r="L65" s="11">
         <f ca="1">IF($O65="","",$O65-TODAY())</f>
         <v>-7</v>
       </c>
-      <c r="M65" s="11" t="str">
+      <c r="M65" s="11">
         <f ca="1">IF($C65="","",$C65+365-TODAY())</f>
-        <v/>
-      </c>
-      <c r="N65" s="11" t="str">
+        <v>266</v>
+      </c>
+      <c r="N65" s="11">
         <f ca="1">IF($C65="","",$C65+90-TODAY())</f>
-        <v/>
+        <v>-9</v>
       </c>
       <c r="O65" s="9">
         <v>46276</v>
@@ -23308,18 +23335,18 @@
     <row r="71" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]US!$A$2:$A$22,MATCH($D71,[6]US!$D$2:$D$22,0))="","",INDEX([6]US!$A$2:$A$22,MATCH($D71,[6]US!$D$2:$D$22,0))),"")</f>
-        <v>Denied</v>
+        <v>Finalized</v>
       </c>
       <c r="B71" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]US!$B$2:$B$22,MATCH($D71,[6]US!$D$2:$D$22,0))="","",INDEX([6]US!$B$2:$B$22,MATCH($D71,[6]US!$D$2:$D$22,0))),"")</f>
-        <v>Removed Dx I872, and resubmitted</v>
+        <v>PAID - Removed Dx I872, and resubmitted</v>
       </c>
       <c r="C71" s="6">
         <f>IFERROR(IF(INDEX([6]US!$C$2:$C$22,MATCH($D71,[6]US!$D$2:$D$22,0))="","",INDEX([6]US!$C$2:$C$22,MATCH($D71,[6]US!$D$2:$D$22,0))),"")</f>
         <v>46202</v>
       </c>
       <c r="D71" s="7">
-        <v>563070750</v>
+        <v>570990107</v>
       </c>
       <c r="E71" s="8" t="s">
         <v>473</v>
@@ -23341,7 +23368,7 @@
       </c>
       <c r="K71" s="6">
         <f>IFERROR(IF(INDEX([6]US!$K$2:$K$22,MATCH($D71,[6]US!$D$2:$D$22,0))="","",INDEX([6]US!$K$2:$K$22,MATCH($D71,[6]US!$D$2:$D$22,0))),"")</f>
-        <v>46271</v>
+        <v>46282</v>
       </c>
       <c r="L71" s="11">
         <f ca="1">IF($O71="","",$O71-TODAY())</f>
@@ -23784,18 +23811,18 @@
     <row r="75" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D75,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D75,[6]DME!$D$2:$D$52,0))),"")</f>
-        <v>Denied</v>
+        <v>Finalized</v>
       </c>
       <c r="B75" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$B$2:$B$52,MATCH($D75,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$B$2:$B$52,MATCH($D75,[6]DME!$D$2:$D$52,0))),"")</f>
-        <v>Edited insured's info, and resubmitted - DND Remark: Patient/Insured health identification number and name do not match</v>
+        <v>Insurance paid - Edited insured's info, and resubmitted - DND Remark: Patient/Insured health identification number and name do not match</v>
       </c>
       <c r="C75" s="6">
         <f>IFERROR(IF(INDEX([6]DME!$C$2:$C$52,MATCH($D75,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$C$2:$C$52,MATCH($D75,[6]DME!$D$2:$D$52,0))),"")</f>
         <v>46203</v>
       </c>
       <c r="D75" s="7">
-        <v>563171807</v>
+        <v>571030818</v>
       </c>
       <c r="E75" s="8" t="s">
         <v>428</v>
@@ -23817,7 +23844,7 @@
       </c>
       <c r="K75" s="6">
         <f>IFERROR(IF(INDEX([6]DME!$K$2:$K$52,MATCH($D75,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$K$2:$K$52,MATCH($D75,[6]DME!$D$2:$D$52,0))),"")</f>
-        <v>46272</v>
+        <v>46282</v>
       </c>
       <c r="L75" s="11">
         <f ca="1">IF($O75="","",$O75-TODAY())</f>
@@ -24031,7 +24058,7 @@
         <v/>
       </c>
       <c r="D77" s="7">
-        <v>564509654</v>
+        <v>571013418</v>
       </c>
       <c r="E77" s="8" t="s">
         <v>489</v>
@@ -24142,11 +24169,11 @@
     <row r="78" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]BH!$A$2:$A$82,MATCH($D78,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$A$2:$A$82,MATCH($D78,[6]BH!$D$2:$D$82,0))),"")</f>
-        <v>Denied</v>
+        <v>Finalized</v>
       </c>
       <c r="B78" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]BH!$B$2:$B$82,MATCH($D78,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$B$2:$B$82,MATCH($D78,[6]BH!$D$2:$D$82,0))),"")</f>
-        <v>I sent an email to provider about this matter - The 3-year clock follows the provider relationship - Dr Wilson doesnt want to change the cpt code - BCBS AZ denied 99204 because she's an established patient. The encounter notes calls it a "re-establishment visit," and she had ESIs with us in 2024-2025- DND 99204+25 Remark CO_B16 Contractual Obligation - 'New Patient' qualifications were not met</v>
+        <v>Adjusted balance - I sent an email to provider about this matter - The 3-year clock follows the provider relationship - Dr Wilson doesnt want to change the cpt code - BCBS AZ denied 99204 because she's an established patient. The encounter notes calls it a "re-establishment visit," and she had ESIs with us in 2024-2025- DND 99204+25 Remark CO_B16 Contractual Obligation - 'New Patient' qualifications were not met</v>
       </c>
       <c r="C78" s="6">
         <f>IFERROR(IF(INDEX([6]BH!$C$2:$C$82,MATCH($D78,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$C$2:$C$82,MATCH($D78,[6]BH!$D$2:$D$82,0))),"")</f>
@@ -24260,7 +24287,7 @@
     <row r="79" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D79,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D79,[6]DME!$D$2:$D$52,0))),"")</f>
-        <v>Denied</v>
+        <v>Finalized</v>
       </c>
       <c r="B79" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$B$2:$B$52,MATCH($D79,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$B$2:$B$52,MATCH($D79,[6]DME!$D$2:$D$52,0))),"")</f>
@@ -24382,7 +24409,7 @@
     <row r="80" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D80,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D80,[6]DME!$D$2:$D$52,0))),"")</f>
-        <v>Denied</v>
+        <v>Finalized</v>
       </c>
       <c r="B80" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$B$2:$B$52,MATCH($D80,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$B$2:$B$52,MATCH($D80,[6]DME!$D$2:$D$52,0))),"")</f>
@@ -24624,7 +24651,7 @@
     <row r="82" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D82,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D82,[6]DME!$D$2:$D$52,0))),"")</f>
-        <v>Denied</v>
+        <v>Finalized</v>
       </c>
       <c r="B82" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$B$2:$B$52,MATCH($D82,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$B$2:$B$52,MATCH($D82,[6]DME!$D$2:$D$52,0))),"")</f>
@@ -25609,7 +25636,7 @@
         <v/>
       </c>
       <c r="D90" s="7">
-        <v>563844305</v>
+        <v>572208778</v>
       </c>
       <c r="E90" s="8" t="s">
         <v>549</v>
@@ -25960,7 +25987,7 @@
     <row r="93" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D93,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D93,[6]DME!$D$2:$D$52,0))),"")</f>
-        <v>Denied</v>
+        <v>Finalized</v>
       </c>
       <c r="B93" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$B$2:$B$52,MATCH($D93,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$B$2:$B$52,MATCH($D93,[6]DME!$D$2:$D$52,0))),"")</f>
@@ -26444,7 +26471,7 @@
     <row r="97" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$A$2:$A$52,MATCH($D97,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$A$2:$A$52,MATCH($D97,[6]DME!$D$2:$D$52,0))),"")</f>
-        <v>Denied</v>
+        <v>Finalized</v>
       </c>
       <c r="B97" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]DME!$B$2:$B$52,MATCH($D97,[6]DME!$D$2:$D$52,0))="","",INDEX([6]DME!$B$2:$B$52,MATCH($D97,[6]DME!$D$2:$D$52,0))),"")</f>
@@ -26573,7 +26600,7 @@
         <v>46210</v>
       </c>
       <c r="D98" s="7">
-        <v>564120985</v>
+        <v>572251031</v>
       </c>
       <c r="E98" s="8" t="s">
         <v>588</v>
@@ -26817,7 +26844,7 @@
         <v/>
       </c>
       <c r="D100" s="7">
-        <v>565290727</v>
+        <v>572251311</v>
       </c>
       <c r="E100" s="8" t="s">
         <v>549</v>
@@ -34524,18 +34551,18 @@
     <row r="163" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A163" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]US!$A$2:$A$15,MATCH($D163,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$A$2:$A$15,MATCH($D163,[2]US!$D$2:$D$15,0))),"")</f>
-        <v/>
+        <v>Denied</v>
       </c>
       <c r="B163" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]US!$B$2:$B$15,MATCH($D163,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$B$2:$B$15,MATCH($D163,[2]US!$D$2:$D$15,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C163" s="6" t="str">
+        <v>Corrected ordering/referring provider, and resubmitted</v>
+      </c>
+      <c r="C163" s="6">
         <f>IFERROR(IF(INDEX([2]US!$C$2:$C$15,MATCH($D163,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$C$2:$C$15,MATCH($D163,[2]US!$D$2:$D$15,0))),"")</f>
-        <v/>
+        <v>46113</v>
       </c>
       <c r="D163" s="7">
-        <v>566164852</v>
+        <v>571606148</v>
       </c>
       <c r="E163" s="8" t="s">
         <v>834</v>
@@ -34555,21 +34582,21 @@
       <c r="J163" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="K163" s="6" t="str">
+      <c r="K163" s="6">
         <f>IFERROR(IF(INDEX([2]US!$K$2:$K$15,MATCH($D163,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$K$2:$K$15,MATCH($D163,[2]US!$D$2:$D$15,0))),"")</f>
-        <v/>
+        <v>46278</v>
       </c>
       <c r="L163" s="11">
         <f ca="1">IF($O163="","",$O163-TODAY())</f>
         <v>173</v>
       </c>
-      <c r="M163" s="11" t="str">
+      <c r="M163" s="11">
         <f ca="1">IF($C163="","",$C163+365-TODAY())</f>
-        <v/>
-      </c>
-      <c r="N163" s="11" t="str">
+        <v>195</v>
+      </c>
+      <c r="N163" s="11">
         <f ca="1">IF($C163="","",$C163+120-TODAY())</f>
-        <v/>
+        <v>-50</v>
       </c>
       <c r="O163" s="9">
         <v>46456</v>
@@ -36700,18 +36727,18 @@
     <row r="181" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A181" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]US!$A$2:$A$15,MATCH($D181,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$A$2:$A$15,MATCH($D181,[2]US!$D$2:$D$15,0))),"")</f>
-        <v/>
+        <v>Denied</v>
       </c>
       <c r="B181" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]US!$B$2:$B$15,MATCH($D181,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$B$2:$B$15,MATCH($D181,[2]US!$D$2:$D$15,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C181" s="6" t="str">
+        <v>Corrected ordering/referring provider, and resubmitted</v>
+      </c>
+      <c r="C181" s="6">
         <f>IFERROR(IF(INDEX([2]US!$C$2:$C$15,MATCH($D181,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$C$2:$C$15,MATCH($D181,[2]US!$D$2:$D$15,0))),"")</f>
-        <v/>
+        <v>46126</v>
       </c>
       <c r="D181" s="7">
-        <v>555443022</v>
+        <v>571606263</v>
       </c>
       <c r="E181" s="8" t="s">
         <v>915</v>
@@ -36731,21 +36758,21 @@
       <c r="J181" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="K181" s="6" t="str">
+      <c r="K181" s="6">
         <f>IFERROR(IF(INDEX([2]US!$K$2:$K$15,MATCH($D181,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$K$2:$K$15,MATCH($D181,[2]US!$D$2:$D$15,0))),"")</f>
-        <v/>
+        <v>46278</v>
       </c>
       <c r="L181" s="11">
         <f ca="1">IF($O181="","",$O181-TODAY())</f>
         <v>194</v>
       </c>
-      <c r="M181" s="11" t="str">
+      <c r="M181" s="11">
         <f ca="1">IF($C181="","",$C181+365-TODAY())</f>
-        <v/>
-      </c>
-      <c r="N181" s="11" t="str">
+        <v>208</v>
+      </c>
+      <c r="N181" s="11">
         <f ca="1">IF($C181="","",$C181+120-TODAY())</f>
-        <v/>
+        <v>-37</v>
       </c>
       <c r="O181" s="9">
         <v>46477</v>
@@ -36940,11 +36967,11 @@
     <row r="183" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A183" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$A$2:$A$34,MATCH($D183,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$A$2:$A$34,MATCH($D183,[4]DME!$D$2:$D$34,0))),"")</f>
-        <v/>
+        <v>Denied</v>
       </c>
       <c r="B183" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$B$2:$B$34,MATCH($D183,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$B$2:$B$34,MATCH($D183,[4]DME!$D$2:$D$34,0))),"")</f>
-        <v/>
+        <v>Filed appeal with MR on portal - Confirmation Number: 148586224 - L1851 requires auth, and we didn't get one</v>
       </c>
       <c r="C183" s="6">
         <f>IFERROR(IF(INDEX([4]DME!$C$2:$C$34,MATCH($D183,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$C$2:$C$34,MATCH($D183,[4]DME!$D$2:$D$34,0))),"")</f>
@@ -36971,9 +36998,9 @@
       <c r="J183" s="8" t="s">
         <v>922</v>
       </c>
-      <c r="K183" s="6" t="str">
+      <c r="K183" s="6">
         <f>IFERROR(IF(INDEX([4]DME!$K$2:$K$34,MATCH($D183,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$K$2:$K$34,MATCH($D183,[4]DME!$D$2:$D$34,0))),"")</f>
-        <v/>
+        <v>46283</v>
       </c>
       <c r="L183" s="11">
         <f ca="1">IF($O183="","",$O183-TODAY())</f>
@@ -37424,15 +37451,15 @@
     <row r="187" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A187" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$A$2:$A$34,MATCH($D187,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$A$2:$A$34,MATCH($D187,[4]DME!$D$2:$D$34,0))),"")</f>
-        <v/>
+        <v>Denied</v>
       </c>
       <c r="B187" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$B$2:$B$34,MATCH($D187,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$B$2:$B$34,MATCH($D187,[4]DME!$D$2:$D$34,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C187" s="6" t="str">
+        <v>Adjusted balance - Only 1 Incision was performed - 20 units each were order - We dispensed 40 unit each as per POD - DND Coverage/program guidelines were exceeded.</v>
+      </c>
+      <c r="C187" s="6">
         <f>IFERROR(IF(INDEX([4]DME!$C$2:$C$34,MATCH($D187,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$C$2:$C$34,MATCH($D187,[4]DME!$D$2:$D$34,0))),"")</f>
-        <v/>
+        <v>46249</v>
       </c>
       <c r="D187" s="7">
         <v>556771003</v>
@@ -37455,21 +37482,21 @@
       <c r="J187" s="8" t="s">
         <v>937</v>
       </c>
-      <c r="K187" s="6" t="str">
+      <c r="K187" s="6">
         <f>IFERROR(IF(INDEX([4]DME!$K$2:$K$34,MATCH($D187,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$K$2:$K$34,MATCH($D187,[4]DME!$D$2:$D$34,0))),"")</f>
-        <v/>
+        <v>46283</v>
       </c>
       <c r="L187" s="11">
         <f ca="1">IF($O187="","",$O187-TODAY())</f>
         <v>203</v>
       </c>
-      <c r="M187" s="11" t="str">
+      <c r="M187" s="11">
         <f ca="1">IF($C187="","",$C187+365-TODAY())</f>
-        <v/>
-      </c>
-      <c r="N187" s="11" t="str">
+        <v>331</v>
+      </c>
+      <c r="N187" s="11">
         <f ca="1">IF($C187="","",$C187+120-TODAY())</f>
-        <v/>
+        <v>86</v>
       </c>
       <c r="O187" s="9">
         <v>46486</v>
@@ -37542,11 +37569,11 @@
     <row r="188" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A188" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$A$2:$A$34,MATCH($D188,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$A$2:$A$34,MATCH($D188,[4]DME!$D$2:$D$34,0))),"")</f>
-        <v/>
+        <v>Denied</v>
       </c>
       <c r="B188" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$B$2:$B$34,MATCH($D188,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$B$2:$B$34,MATCH($D188,[4]DME!$D$2:$D$34,0))),"")</f>
-        <v/>
+        <v>Shift to PT - ABN signed - Another L0650 was dispensed back on 04/25/2022 - Supplier SONOSPINE ARIZONA LLC - DND L0650 M3 Equipment is the same or similar to equipment already being used</v>
       </c>
       <c r="C188" s="6">
         <f>IFERROR(IF(INDEX([4]DME!$C$2:$C$34,MATCH($D188,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$C$2:$C$34,MATCH($D188,[4]DME!$D$2:$D$34,0))),"")</f>
@@ -37573,9 +37600,9 @@
       <c r="J188" s="8" t="s">
         <v>514</v>
       </c>
-      <c r="K188" s="6" t="str">
+      <c r="K188" s="6">
         <f>IFERROR(IF(INDEX([4]DME!$K$2:$K$34,MATCH($D188,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$K$2:$K$34,MATCH($D188,[4]DME!$D$2:$D$34,0))),"")</f>
-        <v/>
+        <v>46283</v>
       </c>
       <c r="L188" s="11">
         <f ca="1">IF($O188="","",$O188-TODAY())</f>
@@ -37662,15 +37689,15 @@
     <row r="189" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A189" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$A$2:$A$34,MATCH($D189,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$A$2:$A$34,MATCH($D189,[4]DME!$D$2:$D$34,0))),"")</f>
-        <v/>
+        <v>Denied</v>
       </c>
       <c r="B189" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$B$2:$B$34,MATCH($D189,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$B$2:$B$34,MATCH($D189,[4]DME!$D$2:$D$34,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C189" s="6" t="str">
+        <v>Resubmitted to Region B - PT state on portal: WI - DND N104 This claim/service is not payable under our claims jurisdiction area</v>
+      </c>
+      <c r="C189" s="6">
         <f>IFERROR(IF(INDEX([4]DME!$C$2:$C$34,MATCH($D189,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$C$2:$C$34,MATCH($D189,[4]DME!$D$2:$D$34,0))),"")</f>
-        <v/>
+        <v>46247</v>
       </c>
       <c r="D189" s="7">
         <v>556799664</v>
@@ -37693,21 +37720,21 @@
       <c r="J189" s="8" t="s">
         <v>216</v>
       </c>
-      <c r="K189" s="6" t="str">
+      <c r="K189" s="6">
         <f>IFERROR(IF(INDEX([4]DME!$K$2:$K$34,MATCH($D189,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$K$2:$K$34,MATCH($D189,[4]DME!$D$2:$D$34,0))),"")</f>
-        <v/>
+        <v>46283</v>
       </c>
       <c r="L189" s="11">
         <f ca="1">IF($O189="","",$O189-TODAY())</f>
         <v>207</v>
       </c>
-      <c r="M189" s="11" t="str">
+      <c r="M189" s="11">
         <f ca="1">IF($C189="","",$C189+365-TODAY())</f>
-        <v/>
-      </c>
-      <c r="N189" s="11" t="str">
+        <v>329</v>
+      </c>
+      <c r="N189" s="11">
         <f ca="1">IF($C189="","",$C189+120-TODAY())</f>
-        <v/>
+        <v>84</v>
       </c>
       <c r="O189" s="9">
         <v>46490</v>
@@ -37782,11 +37809,11 @@
     <row r="190" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A190" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$A$2:$A$34,MATCH($D190,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$A$2:$A$34,MATCH($D190,[4]DME!$D$2:$D$34,0))),"")</f>
-        <v/>
+        <v>Pending</v>
       </c>
       <c r="B190" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$B$2:$B$34,MATCH($D190,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$B$2:$B$34,MATCH($D190,[4]DME!$D$2:$D$34,0))),"")</f>
-        <v/>
+        <v>secondary - Primary paid</v>
       </c>
       <c r="C190" s="6">
         <f>IFERROR(IF(INDEX([4]DME!$C$2:$C$34,MATCH($D190,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$C$2:$C$34,MATCH($D190,[4]DME!$D$2:$D$34,0))),"")</f>
@@ -37813,9 +37840,9 @@
       <c r="J190" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="K190" s="6" t="str">
+      <c r="K190" s="6">
         <f>IFERROR(IF(INDEX([4]DME!$K$2:$K$34,MATCH($D190,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$K$2:$K$34,MATCH($D190,[4]DME!$D$2:$D$34,0))),"")</f>
-        <v/>
+        <v>46261</v>
       </c>
       <c r="L190" s="11">
         <f ca="1">IF($O190="","",$O190-TODAY())</f>
@@ -38390,15 +38417,15 @@
     <row r="195" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A195" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$A$2:$A$34,MATCH($D195,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$A$2:$A$34,MATCH($D195,[4]DME!$D$2:$D$34,0))),"")</f>
-        <v/>
+        <v>Denied</v>
       </c>
       <c r="B195" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$B$2:$B$34,MATCH($D195,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$B$2:$B$34,MATCH($D195,[4]DME!$D$2:$D$34,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C195" s="6" t="str">
+        <v>secondary - Edited COB info, and resubmitted - Primary paid</v>
+      </c>
+      <c r="C195" s="6">
         <f>IFERROR(IF(INDEX([4]DME!$C$2:$C$34,MATCH($D195,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$C$2:$C$34,MATCH($D195,[4]DME!$D$2:$D$34,0))),"")</f>
-        <v/>
+        <v>46281</v>
       </c>
       <c r="D195" s="7">
         <v>556808178</v>
@@ -38421,21 +38448,21 @@
       <c r="J195" s="8" t="s">
         <v>479</v>
       </c>
-      <c r="K195" s="6" t="str">
+      <c r="K195" s="6">
         <f>IFERROR(IF(INDEX([4]DME!$K$2:$K$34,MATCH($D195,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$K$2:$K$34,MATCH($D195,[4]DME!$D$2:$D$34,0))),"")</f>
-        <v/>
+        <v>46283</v>
       </c>
       <c r="L195" s="11">
         <f ca="1">IF($O195="","",$O195-TODAY())</f>
         <v>214</v>
       </c>
-      <c r="M195" s="11" t="str">
+      <c r="M195" s="11">
         <f ca="1">IF($C195="","",$C195+365-TODAY())</f>
-        <v/>
-      </c>
-      <c r="N195" s="11" t="str">
+        <v>363</v>
+      </c>
+      <c r="N195" s="11">
         <f ca="1">IF($C195="","",$C195+120-TODAY())</f>
-        <v/>
+        <v>118</v>
       </c>
       <c r="O195" s="9">
         <v>46497</v>
@@ -38510,11 +38537,11 @@
     <row r="196" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A196" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$A$2:$A$34,MATCH($D196,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$A$2:$A$34,MATCH($D196,[4]DME!$D$2:$D$34,0))),"")</f>
-        <v/>
+        <v>Denied</v>
       </c>
       <c r="B196" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$B$2:$B$34,MATCH($D196,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$B$2:$B$34,MATCH($D196,[4]DME!$D$2:$D$34,0))),"")</f>
-        <v/>
+        <v>MBI updated - Resubmitted - DND Missing/incomplete/invalid patient identifier</v>
       </c>
       <c r="C196" s="6">
         <f>IFERROR(IF(INDEX([4]DME!$C$2:$C$34,MATCH($D196,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$C$2:$C$34,MATCH($D196,[4]DME!$D$2:$D$34,0))),"")</f>
@@ -38541,9 +38568,9 @@
       <c r="J196" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="K196" s="6" t="str">
+      <c r="K196" s="6">
         <f>IFERROR(IF(INDEX([4]DME!$K$2:$K$34,MATCH($D196,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$K$2:$K$34,MATCH($D196,[4]DME!$D$2:$D$34,0))),"")</f>
-        <v/>
+        <v>46283</v>
       </c>
       <c r="L196" s="11">
         <f ca="1">IF($O196="","",$O196-TODAY())</f>
@@ -39364,11 +39391,11 @@
     <row r="203" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A203" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$A$2:$A$34,MATCH($D203,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$A$2:$A$34,MATCH($D203,[4]DME!$D$2:$D$34,0))),"")</f>
-        <v/>
+        <v>Denied</v>
       </c>
       <c r="B203" s="5" t="str">
         <f>IFERROR(IF(INDEX([4]DME!$B$2:$B$34,MATCH($D203,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$B$2:$B$34,MATCH($D203,[4]DME!$D$2:$D$34,0))),"")</f>
-        <v/>
+        <v>MBI updated on chart, and resubmitted - DND Missing/incomplete/invalid patient identifier</v>
       </c>
       <c r="C203" s="6">
         <f>IFERROR(IF(INDEX([4]DME!$C$2:$C$34,MATCH($D203,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$C$2:$C$34,MATCH($D203,[4]DME!$D$2:$D$34,0))),"")</f>
@@ -39395,9 +39422,9 @@
       <c r="J203" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="K203" s="6" t="str">
+      <c r="K203" s="6">
         <f>IFERROR(IF(INDEX([4]DME!$K$2:$K$34,MATCH($D203,[4]DME!$D$2:$D$34,0))="","",INDEX([4]DME!$K$2:$K$34,MATCH($D203,[4]DME!$D$2:$D$34,0))),"")</f>
-        <v/>
+        <v>46278</v>
       </c>
       <c r="L203" s="11">
         <f ca="1">IF($O203="","",$O203-TODAY())</f>
@@ -40554,18 +40581,18 @@
     <row r="213" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A213" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]ORTHO!$A$2:$A$24,MATCH($D213,[5]ORTHO!$D$2:$D$24,0))="","",INDEX([5]ORTHO!$A$2:$A$24,MATCH($D213,[5]ORTHO!$D$2:$D$24,0))),"")</f>
-        <v/>
+        <v>Denied</v>
       </c>
       <c r="B213" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]ORTHO!$B$2:$B$24,MATCH($D213,[5]ORTHO!$D$2:$D$24,0))="","",INDEX([5]ORTHO!$B$2:$B$24,MATCH($D213,[5]ORTHO!$D$2:$D$24,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C213" s="6" t="str">
+        <v>MBI updated on chart, and resubmitted</v>
+      </c>
+      <c r="C213" s="6">
         <f>IFERROR(IF(INDEX([5]ORTHO!$C$2:$C$24,MATCH($D213,[5]ORTHO!$D$2:$D$24,0))="","",INDEX([5]ORTHO!$C$2:$C$24,MATCH($D213,[5]ORTHO!$D$2:$D$24,0))),"")</f>
-        <v/>
+        <v>46161</v>
       </c>
       <c r="D213" s="7">
-        <v>558830669</v>
+        <v>569308141</v>
       </c>
       <c r="E213" s="8" t="s">
         <v>842</v>
@@ -40585,21 +40612,21 @@
       <c r="J213" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="K213" s="6" t="str">
+      <c r="K213" s="6">
         <f>IFERROR(IF(INDEX([5]ORTHO!$K$2:$K$24,MATCH($D213,[5]ORTHO!$D$2:$D$24,0))="","",INDEX([5]ORTHO!$K$2:$K$24,MATCH($D213,[5]ORTHO!$D$2:$D$24,0))),"")</f>
-        <v/>
+        <v>46254</v>
       </c>
       <c r="L213" s="11">
         <f ca="1">IF($O213="","",$O213-TODAY())</f>
         <v>228</v>
       </c>
-      <c r="M213" s="11" t="str">
+      <c r="M213" s="11">
         <f ca="1">IF($C213="","",$C213+365-TODAY())</f>
-        <v/>
-      </c>
-      <c r="N213" s="11" t="str">
+        <v>243</v>
+      </c>
+      <c r="N213" s="11">
         <f ca="1">IF($C213="","",$C213+120-TODAY())</f>
-        <v/>
+        <v>-2</v>
       </c>
       <c r="O213" s="9">
         <v>46511</v>
@@ -52401,7 +52428,7 @@
         <v>221</v>
       </c>
       <c r="H311" s="8" t="s">
-        <v>221</v>
+        <v>640</v>
       </c>
       <c r="I311" s="8" t="s">
         <v>221</v>
@@ -52415,33 +52442,33 @@
       </c>
       <c r="L311" s="11">
         <f ca="1">IF($O311="","",$O311-TODAY())</f>
-        <v>-128</v>
+        <v>147</v>
       </c>
       <c r="M311" s="11">
-        <f ca="1">IF($F311="","",$F311+90-TODAY())</f>
-        <v>-128</v>
+        <f ca="1">IF($C311="","",$C311+365-TODAY())</f>
+        <v>293</v>
       </c>
       <c r="N311" s="11">
-        <f ca="1">IF($C311="","",$C311+60-TODAY())</f>
-        <v>-12</v>
+        <f ca="1">IF($C311="","",$C311+120-TODAY())</f>
+        <v>48</v>
       </c>
       <c r="O311" s="9">
-        <v>46155</v>
+        <v>46430</v>
       </c>
       <c r="P311" s="8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="Q311" s="8" t="s">
-        <v>223</v>
+        <v>737</v>
       </c>
       <c r="R311" s="8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="S311" s="8" t="s">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="T311" s="8" t="s">
-        <v>151</v>
+        <v>72</v>
       </c>
       <c r="U311" s="8" t="s">
         <v>75</v>
@@ -54078,18 +54105,18 @@
     <row r="325" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A325" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]US!$A$2:$A$15,MATCH($D325,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$A$2:$A$15,MATCH($D325,[2]US!$D$2:$D$15,0))),"")</f>
-        <v/>
+        <v>Denied</v>
       </c>
       <c r="B325" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]US!$B$2:$B$15,MATCH($D325,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$B$2:$B$15,MATCH($D325,[2]US!$D$2:$D$15,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C325" s="6" t="str">
+        <v>Edited dx order, and resubmitted - DND Diagnosis was invalid for the date(s) of service reported</v>
+      </c>
+      <c r="C325" s="6">
         <f>IFERROR(IF(INDEX([2]US!$C$2:$C$15,MATCH($D325,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$C$2:$C$15,MATCH($D325,[2]US!$D$2:$D$15,0))),"")</f>
-        <v/>
+        <v>46113</v>
       </c>
       <c r="D325" s="7">
-        <v>553766486</v>
+        <v>571606836</v>
       </c>
       <c r="E325" s="8" t="s">
         <v>1321</v>
@@ -54109,9 +54136,9 @@
       <c r="J325" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="K325" s="6" t="str">
+      <c r="K325" s="6">
         <f>IFERROR(IF(INDEX([2]US!$K$2:$K$15,MATCH($D325,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$K$2:$K$15,MATCH($D325,[2]US!$D$2:$D$15,0))),"")</f>
-        <v/>
+        <v>46278</v>
       </c>
       <c r="L325" s="11">
         <f ca="1">IF($O325="","",$O325-TODAY())</f>
@@ -54121,9 +54148,9 @@
         <f ca="1">IF($F325="","",$F325+90-TODAY())</f>
         <v>-109</v>
       </c>
-      <c r="N325" s="11" t="str">
+      <c r="N325" s="11">
         <f ca="1">IF($C325="","",$C325+180-TODAY())</f>
-        <v/>
+        <v>10</v>
       </c>
       <c r="O325" s="9">
         <v>46174</v>
@@ -56120,18 +56147,18 @@
     <row r="342" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A342" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]US!$A$2:$A$15,MATCH($D342,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$A$2:$A$15,MATCH($D342,[2]US!$D$2:$D$15,0))),"")</f>
-        <v/>
+        <v>Denied</v>
       </c>
       <c r="B342" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]US!$B$2:$B$15,MATCH($D342,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$B$2:$B$15,MATCH($D342,[2]US!$D$2:$D$15,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C342" s="6" t="str">
+        <v>Resubmitted to UHC as primary - DND This care may be covered by another payer per coordination of benefits</v>
+      </c>
+      <c r="C342" s="6">
         <f>IFERROR(IF(INDEX([2]US!$C$2:$C$15,MATCH($D342,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$C$2:$C$15,MATCH($D342,[2]US!$D$2:$D$15,0))),"")</f>
-        <v/>
+        <v>46135</v>
       </c>
       <c r="D342" s="7">
-        <v>555085468</v>
+        <v>571607238</v>
       </c>
       <c r="E342" s="8" t="s">
         <v>1260</v>
@@ -56140,32 +56167,32 @@
         <v>46098</v>
       </c>
       <c r="G342" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="H342" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="I342" s="8" t="s">
         <v>296</v>
-      </c>
-      <c r="H342" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="I342" s="8" t="s">
-        <v>86</v>
       </c>
       <c r="J342" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="K342" s="6" t="str">
+      <c r="K342" s="6">
         <f>IFERROR(IF(INDEX([2]US!$K$2:$K$15,MATCH($D342,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$K$2:$K$15,MATCH($D342,[2]US!$D$2:$D$15,0))),"")</f>
-        <v/>
+        <v>46278</v>
       </c>
       <c r="L342" s="11">
         <f ca="1">IF($O342="","",$O342-TODAY())</f>
         <v>-95</v>
       </c>
       <c r="M342" s="11">
-        <f ca="1">IF($F342="","",$F342+90-TODAY())</f>
-        <v>-95</v>
-      </c>
-      <c r="N342" s="11" t="str">
+        <f ca="1">IF($C342="","",$C342+180-TODAY())</f>
+        <v>32</v>
+      </c>
+      <c r="N342" s="11">
         <f ca="1">IF($C342="","",$C342+365-TODAY())</f>
-        <v/>
+        <v>217</v>
       </c>
       <c r="O342" s="9">
         <v>46188</v>
@@ -56174,13 +56201,13 @@
         <v>88</v>
       </c>
       <c r="Q342" s="8" t="s">
-        <v>298</v>
+        <v>89</v>
       </c>
       <c r="R342" s="8" t="s">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="S342" s="8" t="s">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="T342" s="8" t="s">
         <v>90</v>
@@ -56707,7 +56734,7 @@
       <c r="AJ346" s="8"/>
       <c r="AK346" s="8"/>
       <c r="AL346" s="7">
-        <v>555928717</v>
+        <v>571607938</v>
       </c>
       <c r="AM346" s="8" t="s">
         <v>246</v>
@@ -57078,18 +57105,18 @@
     <row r="350" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A350" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]US!$A$2:$A$15,MATCH($D350,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$A$2:$A$15,MATCH($D350,[2]US!$D$2:$D$15,0))),"")</f>
-        <v/>
+        <v>Finalized</v>
       </c>
       <c r="B350" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]US!$B$2:$B$15,MATCH($D350,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$B$2:$B$15,MATCH($D350,[2]US!$D$2:$D$15,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C350" s="6" t="str">
+        <v>PAID - Insurance approved correction - Edited dx order, used I83811 as a primary code, and resubmitted - Denied payment for 93970 with remark: invalid dx</v>
+      </c>
+      <c r="C350" s="6">
         <f>IFERROR(IF(INDEX([2]US!$C$2:$C$15,MATCH($D350,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$C$2:$C$15,MATCH($D350,[2]US!$D$2:$D$15,0))),"")</f>
-        <v/>
+        <v>46127</v>
       </c>
       <c r="D350" s="7">
-        <v>555431454</v>
+        <v>569508762</v>
       </c>
       <c r="E350" s="8" t="s">
         <v>1383</v>
@@ -57109,9 +57136,9 @@
       <c r="J350" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="K350" s="6" t="str">
+      <c r="K350" s="6">
         <f>IFERROR(IF(INDEX([2]US!$K$2:$K$15,MATCH($D350,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$K$2:$K$15,MATCH($D350,[2]US!$D$2:$D$15,0))),"")</f>
-        <v/>
+        <v>46269</v>
       </c>
       <c r="L350" s="11">
         <f ca="1">IF($O350="","",$O350-TODAY())</f>
@@ -57121,9 +57148,9 @@
         <f ca="1">IF($F350="","",$F350+90-TODAY())</f>
         <v>-88</v>
       </c>
-      <c r="N350" s="11" t="str">
+      <c r="N350" s="11">
         <f ca="1">IF($C350="","",$C350+180-TODAY())</f>
-        <v/>
+        <v>24</v>
       </c>
       <c r="O350" s="9">
         <v>46195</v>
@@ -57198,18 +57225,18 @@
     <row r="351" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A351" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]US!$A$2:$A$15,MATCH($D351,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$A$2:$A$15,MATCH($D351,[2]US!$D$2:$D$15,0))),"")</f>
-        <v/>
+        <v>Denied</v>
       </c>
       <c r="B351" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]US!$B$2:$B$15,MATCH($D351,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$B$2:$B$15,MATCH($D351,[2]US!$D$2:$D$15,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C351" s="6" t="str">
+        <v>Resubmitted to the same payer - Active coverage on DOS - DND Expenses incurred after coverage terminated</v>
+      </c>
+      <c r="C351" s="6">
         <f>IFERROR(IF(INDEX([2]US!$C$2:$C$15,MATCH($D351,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$C$2:$C$15,MATCH($D351,[2]US!$D$2:$D$15,0))),"")</f>
-        <v/>
+        <v>46126</v>
       </c>
       <c r="D351" s="7">
-        <v>555432879</v>
+        <v>571608266</v>
       </c>
       <c r="E351" s="8" t="s">
         <v>1385</v>
@@ -57229,21 +57256,21 @@
       <c r="J351" s="8" t="s">
         <v>222</v>
       </c>
-      <c r="K351" s="6" t="str">
+      <c r="K351" s="6">
         <f>IFERROR(IF(INDEX([2]US!$K$2:$K$15,MATCH($D351,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$K$2:$K$15,MATCH($D351,[2]US!$D$2:$D$15,0))),"")</f>
-        <v/>
+        <v>46278</v>
       </c>
       <c r="L351" s="11">
         <f ca="1">IF($O351="","",$O351-TODAY())</f>
         <v>-88</v>
       </c>
-      <c r="M351" s="11" t="str">
+      <c r="M351" s="11">
         <f ca="1">IF($C351="","",$C351+365-TODAY())</f>
-        <v/>
-      </c>
-      <c r="N351" s="11" t="str">
+        <v>208</v>
+      </c>
+      <c r="N351" s="11">
         <f ca="1">IF($C351="","",$C351+365-TODAY())</f>
-        <v/>
+        <v>208</v>
       </c>
       <c r="O351" s="9">
         <v>46195</v>
@@ -59012,18 +59039,18 @@
     <row r="366" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A366" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]BH!$A$2:$A$33,MATCH($D366,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$A$2:$A$33,MATCH($D366,[5]BH!$D$2:$D$33,0))),"")</f>
-        <v/>
+        <v>Pending</v>
       </c>
       <c r="B366" s="5" t="str">
         <f>IFERROR(IF(INDEX([5]BH!$B$2:$B$33,MATCH($D366,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$B$2:$B$33,MATCH($D366,[5]BH!$D$2:$D$33,0))),"")</f>
-        <v/>
+        <v>Resubmitted to AARP MedicareComplete (SecureHorizons &amp; Oxford Network)</v>
       </c>
       <c r="C366" s="6" t="str">
         <f>IFERROR(IF(INDEX([5]BH!$C$2:$C$33,MATCH($D366,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$C$2:$C$33,MATCH($D366,[5]BH!$D$2:$D$33,0))),"")</f>
         <v/>
       </c>
       <c r="D366" s="7">
-        <v>558768409</v>
+        <v>568553454</v>
       </c>
       <c r="E366" s="8" t="s">
         <v>1423</v>
@@ -59032,10 +59059,10 @@
         <v>46149</v>
       </c>
       <c r="G366" s="8" t="s">
-        <v>1276</v>
+        <v>1605</v>
       </c>
       <c r="H366" s="8" t="s">
-        <v>1276</v>
+        <v>70</v>
       </c>
       <c r="I366" s="8" t="s">
         <v>70</v>
@@ -59043,29 +59070,43 @@
       <c r="J366" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="K366" s="6" t="str">
+      <c r="K366" s="6">
         <f>IFERROR(IF(INDEX([5]BH!$K$2:$K$33,MATCH($D366,[5]BH!$D$2:$D$33,0))="","",INDEX([5]BH!$K$2:$K$33,MATCH($D366,[5]BH!$D$2:$D$33,0))),"")</f>
-        <v/>
+        <v>46247</v>
       </c>
       <c r="L366" s="11">
         <f ca="1">IF($O366="","",$O366-TODAY())</f>
-        <v>-74</v>
-      </c>
-      <c r="M366" s="11"/>
-      <c r="N366" s="11"/>
+        <v>-44</v>
+      </c>
+      <c r="M366" s="11" t="str">
+        <f ca="1">IF($C366="","",$C366+365-TODAY())</f>
+        <v/>
+      </c>
+      <c r="N366" s="11" t="str">
+        <f ca="1">IF($C366="","",$C366+365-TODAY())</f>
+        <v/>
+      </c>
       <c r="O366" s="9">
-        <v>46209</v>
+        <v>46239</v>
       </c>
       <c r="P366" s="8" t="s">
-        <v>151</v>
+        <v>88</v>
       </c>
       <c r="Q366" s="8" t="s">
-        <v>1277</v>
-      </c>
-      <c r="R366" s="8"/>
-      <c r="S366" s="8"/>
-      <c r="T366" s="8"/>
-      <c r="U366" s="8"/>
+        <v>1607</v>
+      </c>
+      <c r="R366" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="S366" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="T366" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="U366" s="8" t="s">
+        <v>75</v>
+      </c>
       <c r="V366" s="8" t="s">
         <v>91</v>
       </c>
@@ -66723,18 +66764,18 @@
     <row r="430" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A430" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]US!$A$2:$A$22,MATCH($D430,[6]US!$D$2:$D$22,0))="","",INDEX([6]US!$A$2:$A$22,MATCH($D430,[6]US!$D$2:$D$22,0))),"")</f>
-        <v>Denied</v>
+        <v>Finalized</v>
       </c>
       <c r="B430" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]US!$B$2:$B$22,MATCH($D430,[6]US!$D$2:$D$22,0))="","",INDEX([6]US!$B$2:$B$22,MATCH($D430,[6]US!$D$2:$D$22,0))),"")</f>
-        <v>Delete 93923 that's bundling, and resubmitted -  93923 billed on claim 568263929</v>
+        <v>PAID - Delete 93923 that's bundling, and resubmitted -  93923 billed on claim 568263929</v>
       </c>
       <c r="C430" s="6">
         <f>IFERROR(IF(INDEX([6]US!$C$2:$C$22,MATCH($D430,[6]US!$D$2:$D$22,0))="","",INDEX([6]US!$C$2:$C$22,MATCH($D430,[6]US!$D$2:$D$22,0))),"")</f>
         <v>46198</v>
       </c>
       <c r="D430" s="7">
-        <v>563065806</v>
+        <v>568262814</v>
       </c>
       <c r="E430" s="8" t="s">
         <v>1577</v>
@@ -66756,7 +66797,7 @@
       </c>
       <c r="K430" s="6">
         <f>IFERROR(IF(INDEX([6]US!$K$2:$K$22,MATCH($D430,[6]US!$D$2:$D$22,0))="","",INDEX([6]US!$K$2:$K$22,MATCH($D430,[6]US!$D$2:$D$22,0))),"")</f>
-        <v>46245</v>
+        <v>46261</v>
       </c>
       <c r="L430" s="11">
         <f ca="1">IF($O430="","",$O430-TODAY())</f>
@@ -68338,18 +68379,18 @@
     <row r="444" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A444" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]US!$A$2:$A$15,MATCH($D444,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$A$2:$A$15,MATCH($D444,[2]US!$D$2:$D$15,0))),"")</f>
-        <v/>
+        <v>Denied</v>
       </c>
       <c r="B444" s="5" t="str">
         <f>IFERROR(IF(INDEX([2]US!$B$2:$B$15,MATCH($D444,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$B$2:$B$15,MATCH($D444,[2]US!$D$2:$D$15,0))),"")</f>
-        <v/>
-      </c>
-      <c r="C444" s="6" t="str">
+        <v>Corrected cpt codes, added code 7, and resubmitted</v>
+      </c>
+      <c r="C444" s="6">
         <f>IFERROR(IF(INDEX([2]US!$C$2:$C$15,MATCH($D444,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$C$2:$C$15,MATCH($D444,[2]US!$D$2:$D$15,0))),"")</f>
-        <v/>
+        <v>46146</v>
       </c>
       <c r="D444" s="7">
-        <v>566781514</v>
+        <v>571612561</v>
       </c>
       <c r="E444" s="8" t="s">
         <v>1621</v>
@@ -68369,21 +68410,21 @@
       <c r="J444" s="8" t="s">
         <v>184</v>
       </c>
-      <c r="K444" s="6" t="str">
+      <c r="K444" s="6">
         <f>IFERROR(IF(INDEX([2]US!$K$2:$K$15,MATCH($D444,[2]US!$D$2:$D$15,0))="","",INDEX([2]US!$K$2:$K$15,MATCH($D444,[2]US!$D$2:$D$15,0))),"")</f>
-        <v/>
+        <v>46278</v>
       </c>
       <c r="L444" s="11">
         <f ca="1">IF($O444="","",$O444-TODAY())</f>
         <v>-95</v>
       </c>
-      <c r="M444" s="11" t="str">
+      <c r="M444" s="11">
         <f ca="1">IF($C444="","",$C444+365-TODAY())</f>
-        <v/>
-      </c>
-      <c r="N444" s="11" t="str">
+        <v>228</v>
+      </c>
+      <c r="N444" s="11">
         <f ca="1">IF($C444="","",$C444+365-TODAY())</f>
-        <v/>
+        <v>228</v>
       </c>
       <c r="O444" s="9">
         <v>46188</v>
@@ -71144,18 +71185,18 @@
     <row r="471" spans="1:41" x14ac:dyDescent="0.25">
       <c r="A471" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]US!$A$2:$A$22,MATCH($D471,[6]US!$D$2:$D$22,0))="","",INDEX([6]US!$A$2:$A$22,MATCH($D471,[6]US!$D$2:$D$22,0))),"")</f>
-        <v/>
+        <v>Pending</v>
       </c>
       <c r="B471" s="5" t="str">
         <f>IFERROR(IF(INDEX([6]US!$B$2:$B$22,MATCH($D471,[6]US!$D$2:$D$22,0))="","",INDEX([6]US!$B$2:$B$22,MATCH($D471,[6]US!$D$2:$D$22,0))),"")</f>
-        <v/>
+        <v xml:space="preserve">Resubmitted to Optum - The claim was denied due to missrouted claim - Claim was initially submitted to SCAN Health Plan </v>
       </c>
       <c r="C471" s="6" t="str">
         <f>IFERROR(IF(INDEX([6]US!$C$2:$C$22,MATCH($D471,[6]US!$D$2:$D$22,0))="","",INDEX([6]US!$C$2:$C$22,MATCH($D471,[6]US!$D$2:$D$22,0))),"")</f>
         <v/>
       </c>
       <c r="D471" s="7">
-        <v>566827110</v>
+        <v>571160597</v>
       </c>
       <c r="E471" s="8" t="s">
         <v>1695</v>
@@ -71164,10 +71205,10 @@
         <v>46182</v>
       </c>
       <c r="G471" s="8" t="s">
-        <v>1696</v>
+        <v>112</v>
       </c>
       <c r="H471" s="8" t="s">
-        <v>1696</v>
+        <v>112</v>
       </c>
       <c r="I471" s="8" t="s">
         <v>70</v>
@@ -71175,25 +71216,43 @@
       <c r="J471" s="8" t="s">
         <v>242</v>
       </c>
-      <c r="K471" s="6" t="str">
+      <c r="K471" s="6">
         <f>IFERROR(IF(INDEX([6]US!$K$2:$K$22,MATCH($D471,[6]US!$D$2:$D$22,0))="","",INDEX([6]US!$K$2:$K$22,MATCH($D471,[6]US!$D$2:$D$22,0))),"")</f>
+        <v>46273</v>
+      </c>
+      <c r="L471" s="11">
+        <f ca="1">IF($O471="","",$O471-TODAY())</f>
+        <v>-11</v>
+      </c>
+      <c r="M471" s="11" t="str">
+        <f ca="1">IF($C471="","",$C471+365-TODAY())</f>
         <v/>
       </c>
-      <c r="L471" s="11" t="str">
-        <f ca="1">IF($O471="","",$O471-TODAY())</f>
+      <c r="N471" s="11" t="str">
+        <f ca="1">IF($C471="","",$C471+365-TODAY())</f>
         <v/>
       </c>
-      <c r="M471" s="11"/>
-      <c r="N471" s="11"/>
-      <c r="O471" s="9"/>
-      <c r="P471" s="8"/>
+      <c r="O471" s="9">
+        <v>46272</v>
+      </c>
+      <c r="P471" s="8" t="s">
+        <v>88</v>
+      </c>
       <c r="Q471" s="8" t="s">
-        <v>1598</v>
-      </c>
-      <c r="R471" s="8"/>
-      <c r="S471" s="8"/>
-      <c r="T471" s="8"/>
-      <c r="U471" s="8"/>
+        <v>115</v>
+      </c>
+      <c r="R471" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="S471" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="T471" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="U471" s="8" t="s">
+        <v>75</v>
+      </c>
       <c r="V471" s="8" t="s">
         <v>159</v>
       </c>
@@ -71558,10 +71617,10 @@
         <v>46190</v>
       </c>
       <c r="G475" s="8" t="s">
-        <v>1696</v>
+        <v>112</v>
       </c>
       <c r="H475" s="8" t="s">
-        <v>1696</v>
+        <v>112</v>
       </c>
       <c r="I475" s="8" t="s">
         <v>211</v>
@@ -71573,21 +71632,39 @@
         <f>IFERROR(IF(INDEX([6]BH!$K$2:$K$82,MATCH($D475,[6]BH!$D$2:$D$82,0))="","",INDEX([6]BH!$K$2:$K$82,MATCH($D475,[6]BH!$D$2:$D$82,0))),"")</f>
         <v>46277</v>
       </c>
-      <c r="L475" s="11" t="str">
+      <c r="L475" s="11">
         <f ca="1">IF($O475="","",$O475-TODAY())</f>
+        <v>-3</v>
+      </c>
+      <c r="M475" s="11" t="str">
+        <f ca="1">IF($C475="","",$C475+365-TODAY())</f>
         <v/>
       </c>
-      <c r="M475" s="11"/>
-      <c r="N475" s="11"/>
-      <c r="O475" s="9"/>
-      <c r="P475" s="8"/>
+      <c r="N475" s="11" t="str">
+        <f ca="1">IF($C475="","",$C475+365-TODAY())</f>
+        <v/>
+      </c>
+      <c r="O475" s="9">
+        <v>46280</v>
+      </c>
+      <c r="P475" s="8" t="s">
+        <v>88</v>
+      </c>
       <c r="Q475" s="8" t="s">
-        <v>1598</v>
-      </c>
-      <c r="R475" s="8"/>
-      <c r="S475" s="8"/>
-      <c r="T475" s="8"/>
-      <c r="U475" s="8"/>
+        <v>115</v>
+      </c>
+      <c r="R475" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="S475" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="T475" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="U475" s="8" t="s">
+        <v>75</v>
+      </c>
       <c r="V475" s="8" t="s">
         <v>159</v>
       </c>

--- a/Specialty Claims 2026-S1/ALL Claims 2026-S1 - Master.xlsx
+++ b/Specialty Claims 2026-S1/ALL Claims 2026-S1 - Master.xlsx
@@ -6991,10 +6991,10 @@
         </row>
         <row r="11">
           <cell r="A11" t="str">
-            <v>Pending</v>
+            <v>Under Review</v>
           </cell>
           <cell r="B11" t="str">
-            <v>***Waiting for payment to be posted, so I can cross over to secondary - Primary paid - Edited rendering and referral provider, and resubmitted - Invalid rendering provider NPIInvalid rendering provider NPI - Rejected</v>
+            <v>Waiting for payment to be posted, so I can cross over to secondary - Primary paid - Edited rendering and referral provider, and resubmitted - Invalid rendering provider NPIInvalid rendering provider NPI - Rejected</v>
           </cell>
           <cell r="C11">
             <v>46268</v>
@@ -7195,10 +7195,10 @@
         </row>
         <row r="23">
           <cell r="A23" t="str">
-            <v>Denied</v>
+            <v>Under Review</v>
           </cell>
           <cell r="B23" t="str">
-            <v>***Sent email to AZ Blue for insights - active coverage on DOS - DND Expenses incurred after coverage terminated</v>
+            <v>Sent email to AZ Blue for insights - active coverage on DOS - DND Expenses incurred after coverage terminated</v>
           </cell>
           <cell r="C23">
             <v>46124</v>
@@ -7529,10 +7529,10 @@
         </row>
         <row r="4">
           <cell r="A4" t="str">
-            <v>Denied</v>
+            <v>Under Review</v>
           </cell>
           <cell r="B4" t="str">
-            <v>***Checking tax code on UMR records - I'm expecting a response by email</v>
+            <v>Checking tax code on UMR records - I'm expecting a response by email</v>
           </cell>
           <cell r="C4">
             <v>46132</v>
@@ -7903,10 +7903,10 @@
         </row>
         <row r="8">
           <cell r="A8" t="str">
-            <v>Denied</v>
+            <v>Under Review</v>
           </cell>
           <cell r="B8" t="str">
-            <v xml:space="preserve">***I need to ask Juan for MR </v>
+            <v xml:space="preserve">I need to ask Juan for MR </v>
           </cell>
           <cell r="C8">
             <v>46220</v>
@@ -7918,7 +7918,7 @@
         </row>
         <row r="9">
           <cell r="A9" t="str">
-            <v>No found</v>
+            <v>Not found</v>
           </cell>
           <cell r="B9" t="str">
             <v xml:space="preserve">secondary - Resubmitted to Tricare for life - claim sent to tricare west and cant be locate it on Availity </v>
@@ -8301,10 +8301,10 @@
         </row>
         <row r="9">
           <cell r="A9" t="str">
-            <v>Denied</v>
+            <v>Under Review</v>
           </cell>
           <cell r="B9" t="str">
-            <v xml:space="preserve">***Auth issue - Denied payment again - Bri resubmitted - Provider TAX ID/NPI Combination is not on file with BCBS AZ. </v>
+            <v xml:space="preserve">Auth issue - Denied payment again - Bri resubmitted - Provider TAX ID/NPI Combination is not on file with BCBS AZ. </v>
           </cell>
           <cell r="C9">
             <v>46227</v>
@@ -8873,9 +8873,11 @@
           </cell>
         </row>
         <row r="11">
-          <cell r="A11"/>
+          <cell r="A11" t="str">
+            <v>Under Review</v>
+          </cell>
           <cell r="B11" t="str">
-            <v>***Waiting for account to get activated again</v>
+            <v>Waiting for account to get activated again</v>
           </cell>
           <cell r="C11"/>
           <cell r="D11">
@@ -8884,9 +8886,11 @@
           <cell r="K11"/>
         </row>
         <row r="12">
-          <cell r="A12"/>
+          <cell r="A12" t="str">
+            <v>Under Review</v>
+          </cell>
           <cell r="B12" t="str">
-            <v>***Waiting for account to get activated again</v>
+            <v>Waiting for account to get activated again</v>
           </cell>
           <cell r="C12"/>
           <cell r="D12">
@@ -8901,7 +8905,7 @@
             <v>Finalized</v>
           </cell>
           <cell r="B2" t="str">
-            <v>Acodes not included in auth/referral</v>
+            <v>Adjusted balance - Acodes not included in auth/referral</v>
           </cell>
           <cell r="C2">
             <v>46170</v>
@@ -8914,59 +8918,97 @@
           </cell>
         </row>
         <row r="3">
-          <cell r="A3"/>
-          <cell r="B3"/>
+          <cell r="A3" t="str">
+            <v>Denied</v>
+          </cell>
+          <cell r="B3" t="str">
+            <v>Filed appeal with MR on portal - Confirmation Number: 148586224 - L1851 requires auth, and we didn't get one</v>
+          </cell>
           <cell r="C3">
             <v>46127</v>
           </cell>
           <cell r="D3">
             <v>555436823</v>
           </cell>
-          <cell r="K3"/>
+          <cell r="K3">
+            <v>46283</v>
+          </cell>
         </row>
         <row r="4">
-          <cell r="A4"/>
-          <cell r="B4"/>
-          <cell r="C4"/>
+          <cell r="A4" t="str">
+            <v>Denied</v>
+          </cell>
+          <cell r="B4" t="str">
+            <v>Adjusted balance - Only 1 Incision was performed - 20 units each were order - We dispensed 40 unit each as per POD - DND Coverage/program guidelines were exceeded.</v>
+          </cell>
+          <cell r="C4">
+            <v>46249</v>
+          </cell>
           <cell r="D4">
             <v>556771003</v>
           </cell>
-          <cell r="K4"/>
+          <cell r="K4">
+            <v>46283</v>
+          </cell>
         </row>
         <row r="5">
-          <cell r="A5"/>
-          <cell r="B5"/>
+          <cell r="A5" t="str">
+            <v>Denied</v>
+          </cell>
+          <cell r="B5" t="str">
+            <v>Shift to PT - ABN signed - Another L0650 was dispensed back on 04/25/2022 - Supplier SONOSPINE ARIZONA LLC - DND L0650 M3 Equipment is the same or similar to equipment already being used</v>
+          </cell>
           <cell r="C5">
             <v>46139</v>
           </cell>
           <cell r="D5">
             <v>556764690</v>
           </cell>
-          <cell r="K5"/>
+          <cell r="K5">
+            <v>46283</v>
+          </cell>
         </row>
         <row r="6">
-          <cell r="A6"/>
-          <cell r="B6"/>
-          <cell r="C6"/>
+          <cell r="A6" t="str">
+            <v>Denied</v>
+          </cell>
+          <cell r="B6" t="str">
+            <v>Resubmitted to Region B - PT state on portal: WI - DND N104 This claim/service is not payable under our claims jurisdiction area</v>
+          </cell>
+          <cell r="C6">
+            <v>46247</v>
+          </cell>
           <cell r="D6">
             <v>556799664</v>
           </cell>
-          <cell r="K6"/>
+          <cell r="K6">
+            <v>46283</v>
+          </cell>
         </row>
         <row r="7">
-          <cell r="A7"/>
-          <cell r="B7"/>
+          <cell r="A7" t="str">
+            <v>Pending</v>
+          </cell>
+          <cell r="B7" t="str">
+            <v>secondary - Primary paid</v>
+          </cell>
           <cell r="C7">
             <v>46151</v>
           </cell>
           <cell r="D7">
             <v>556803684</v>
           </cell>
-          <cell r="K7"/>
+          <cell r="K7">
+            <v>46261</v>
+          </cell>
         </row>
         <row r="8">
-          <cell r="A8"/>
-          <cell r="B8"/>
+          <cell r="A8" t="str">
+            <v>Under Review</v>
+          </cell>
+          <cell r="B8" t="str">
+            <v>Shift to PT if I find same and similar on portal  - ABN signed - Another L0650 was dispensed back on 04/25/2022 - Supplier SONOSPINE ARIZONA LLC - DND L0650 M3 Equipment is the same or similar to equipment already being used</v>
+          </cell>
           <cell r="C8">
             <v>46148</v>
           </cell>
@@ -8976,35 +9018,55 @@
           <cell r="K8"/>
         </row>
         <row r="9">
-          <cell r="A9"/>
-          <cell r="B9"/>
-          <cell r="C9"/>
+          <cell r="A9" t="str">
+            <v>Denied</v>
+          </cell>
+          <cell r="B9" t="str">
+            <v>secondary - Edited COB info, and resubmitted - Primary paid</v>
+          </cell>
+          <cell r="C9">
+            <v>46281</v>
+          </cell>
           <cell r="D9">
             <v>556808178</v>
           </cell>
-          <cell r="K9"/>
+          <cell r="K9">
+            <v>46283</v>
+          </cell>
         </row>
         <row r="10">
-          <cell r="A10"/>
-          <cell r="B10"/>
+          <cell r="A10" t="str">
+            <v>Denied</v>
+          </cell>
+          <cell r="B10" t="str">
+            <v>MBI updated - Resubmitted - DND Missing/incomplete/invalid patient identifier</v>
+          </cell>
           <cell r="C10">
             <v>46199</v>
           </cell>
           <cell r="D10">
             <v>556834981</v>
           </cell>
-          <cell r="K10"/>
+          <cell r="K10">
+            <v>46283</v>
+          </cell>
         </row>
         <row r="11">
-          <cell r="A11"/>
-          <cell r="B11"/>
+          <cell r="A11" t="str">
+            <v>Denied</v>
+          </cell>
+          <cell r="B11" t="str">
+            <v>MBI updated on chart, and resubmitted - DND Missing/incomplete/invalid patient identifier</v>
+          </cell>
           <cell r="C11">
             <v>46142</v>
           </cell>
           <cell r="D11">
             <v>557499174</v>
           </cell>
-          <cell r="K11"/>
+          <cell r="K11">
+            <v>46278</v>
+          </cell>
         </row>
         <row r="12">
           <cell r="A12"/>
@@ -9166,10 +9228,10 @@
         </row>
         <row r="26">
           <cell r="A26" t="str">
-            <v>Denied</v>
+            <v>Under Review</v>
           </cell>
           <cell r="B26" t="str">
-            <v>***chat with ins to confirm covarage - ABN signed - charges per ins contract - PR non covered</v>
+            <v>chat with ins to confirm covarage - ABN signed - charges per ins contract - PR non covered</v>
           </cell>
           <cell r="C26">
             <v>46154</v>
@@ -9246,9 +9308,11 @@
           <cell r="K32"/>
         </row>
         <row r="33">
-          <cell r="A33"/>
+          <cell r="A33" t="str">
+            <v>Under Review</v>
+          </cell>
           <cell r="B33" t="str">
-            <v>***Waiting for account to get activated again</v>
+            <v>Waiting for account to get activated again</v>
           </cell>
           <cell r="C33"/>
           <cell r="D33">
@@ -9257,9 +9321,11 @@
           <cell r="K33"/>
         </row>
         <row r="34">
-          <cell r="A34"/>
+          <cell r="A34" t="str">
+            <v>Under Review</v>
+          </cell>
           <cell r="B34" t="str">
-            <v>***Waiting for account to get activated again</v>
+            <v>Waiting for account to get activated again</v>
           </cell>
           <cell r="C34"/>
           <cell r="D34">
@@ -9305,10 +9371,10 @@
         </row>
         <row r="4">
           <cell r="A4" t="str">
-            <v>Denied</v>
+            <v>Under Review</v>
           </cell>
           <cell r="B4" t="str">
-            <v xml:space="preserve">***DND 75710 This procedure or procedure/modifier combination is not compatible with another procedure or procedure/modifier combination provided on the same day according to the National Correct Coding Initiative or workers compensation state regulations/ fee schedule requirements - Adjusted balance for 36246 not included in the auth requested - 36248 add on requires payment for other cpt code - 99153 cant be billed on pos 24 </v>
+            <v xml:space="preserve">DND 75710 This procedure or procedure/modifier combination is not compatible with another procedure or procedure/modifier combination provided on the same day according to the National Correct Coding Initiative or workers compensation state regulations/ fee schedule requirements - Adjusted balance for 36246 not included in the auth requested - 36248 add on requires payment for other cpt code - 99153 cant be billed on pos 24 </v>
           </cell>
           <cell r="C4">
             <v>46165</v>
@@ -9320,10 +9386,10 @@
         </row>
         <row r="5">
           <cell r="A5" t="str">
-            <v>Denied</v>
+            <v>Under Review</v>
           </cell>
           <cell r="B5" t="str">
-            <v xml:space="preserve">***DND 36248 due to exceeded MUE - DND 36245, 36246, and 75710 due to invalid dx </v>
+            <v xml:space="preserve">DND 36248 due to exceeded MUE - DND 36245, 36246, and 75710 due to invalid dx </v>
           </cell>
           <cell r="C5">
             <v>46162</v>
@@ -9693,9 +9759,11 @@
           </cell>
         </row>
         <row r="20">
-          <cell r="A20"/>
+          <cell r="A20" t="str">
+            <v>Under Review</v>
+          </cell>
           <cell r="B20" t="str">
-            <v xml:space="preserve">***trying to get access to EOB with imperial </v>
+            <v xml:space="preserve">trying to get access to EOB with imperial </v>
           </cell>
           <cell r="C20"/>
           <cell r="D20">
@@ -9704,9 +9772,11 @@
           <cell r="K20"/>
         </row>
         <row r="21">
-          <cell r="A21"/>
+          <cell r="A21" t="str">
+            <v>Under Review</v>
+          </cell>
           <cell r="B21" t="str">
-            <v>***no access</v>
+            <v>no access</v>
           </cell>
           <cell r="C21"/>
           <cell r="D21">
@@ -10005,10 +10075,10 @@
         </row>
         <row r="19">
           <cell r="A19" t="str">
-            <v>Denied</v>
+            <v>Under Review</v>
           </cell>
           <cell r="B19" t="str">
-            <v>***START A CHAT AND ASK FOR A PIQ REVIEW OR STATUS</v>
+            <v>START A CHAT AND ASK FOR A PIQ REVIEW OR STATUS</v>
           </cell>
           <cell r="C19">
             <v>46177</v>
@@ -10020,10 +10090,10 @@
         </row>
         <row r="20">
           <cell r="A20" t="str">
-            <v>Pending</v>
+            <v>Under Review</v>
           </cell>
           <cell r="B20" t="str">
-            <v>***secondary - check cob on noridian, if nothing there, check with April - 1A95CU0TY97</v>
+            <v>secondary - check cob on noridian, if nothing there, check with April - 1A95CU0TY97</v>
           </cell>
           <cell r="C20">
             <v>46152</v>
@@ -10052,10 +10122,10 @@
         </row>
         <row r="22">
           <cell r="A22" t="str">
-            <v>Denied</v>
+            <v>Under Review</v>
           </cell>
           <cell r="B22" t="str">
-            <v>***Send pending msm to Bri</v>
+            <v>Send pending msm to Bri</v>
           </cell>
           <cell r="C22">
             <v>46153</v>
@@ -10067,10 +10137,10 @@
         </row>
         <row r="23">
           <cell r="A23" t="str">
-            <v>Denied</v>
+            <v>Under Review</v>
           </cell>
           <cell r="B23" t="str">
-            <v xml:space="preserve">***I need to ask Juan for MR </v>
+            <v xml:space="preserve">Waiting for Bri's reply - Juan sent MR to me </v>
           </cell>
           <cell r="C23">
             <v>46157</v>
@@ -10247,10 +10317,10 @@
         </row>
         <row r="11">
           <cell r="A11" t="str">
-            <v>Denied</v>
+            <v>Under Review</v>
           </cell>
           <cell r="B11" t="str">
-            <v>***I need to call PT - Aetna termed date March 31, 2026</v>
+            <v>I need to call PT - Aetna termed date March 31, 2026</v>
           </cell>
           <cell r="C11">
             <v>46195</v>
@@ -10532,10 +10602,10 @@
         </row>
         <row r="28">
           <cell r="A28" t="str">
-            <v>Received</v>
+            <v>Under Review</v>
           </cell>
           <cell r="B28" t="str">
-            <v>***Waiting for account to get activated again</v>
+            <v>Waiting for account to get activated again</v>
           </cell>
           <cell r="C28"/>
           <cell r="D28">
@@ -10613,10 +10683,10 @@
         </row>
         <row r="33">
           <cell r="A33" t="str">
-            <v>Received</v>
+            <v>Under Review</v>
           </cell>
           <cell r="B33" t="str">
-            <v>***Waiting for account to get activated again</v>
+            <v>Waiting for account to get activated again</v>
           </cell>
           <cell r="C33"/>
           <cell r="D33">
@@ -10796,10 +10866,10 @@
         </row>
         <row r="12">
           <cell r="A12" t="str">
-            <v>Denied</v>
+            <v>Under Review</v>
           </cell>
           <cell r="B12" t="str">
-            <v>***MUE issue - CALL INS</v>
+            <v>MUE issue - CALL INS</v>
           </cell>
           <cell r="C12">
             <v>46190</v>
@@ -11041,10 +11111,10 @@
         </row>
         <row r="27">
           <cell r="A27" t="str">
-            <v>Pending</v>
+            <v>Under Review</v>
           </cell>
           <cell r="B27" t="str">
-            <v>***Still processing - ins received claim on 07/20/2026</v>
+            <v>Still processing - ins received claim on 07/20/2026</v>
           </cell>
           <cell r="C27"/>
           <cell r="D27">
@@ -11139,10 +11209,10 @@
         </row>
         <row r="33">
           <cell r="A33" t="str">
-            <v>Denied</v>
+            <v>Under Review</v>
           </cell>
           <cell r="B33" t="str">
-            <v>***Call PT for COB update needed by ins - Rep said the patient will need to update their Coordination of Benefits (COB) information with their insurance carrier. Once the COB has been updated, the claim can be reprocessed for review and adjudication. On yearly basis patient needs to update the COB.</v>
+            <v>Call PT for COB update needed by ins - Rep said the patient will need to update their Coordination of Benefits (COB) information with their insurance carrier. Once the COB has been updated, the claim can be reprocessed for review and adjudication. On yearly basis patient needs to update the COB.</v>
           </cell>
           <cell r="C33">
             <v>46203</v>
@@ -11277,10 +11347,10 @@
         </row>
         <row r="7">
           <cell r="A7" t="str">
-            <v>Received</v>
+            <v>Under Review</v>
           </cell>
           <cell r="B7" t="str">
-            <v>***Waiting for account to get activated again</v>
+            <v>Waiting for account to get activated again</v>
           </cell>
           <cell r="C7"/>
           <cell r="D7">
@@ -11564,7 +11634,7 @@
         </row>
         <row r="18">
           <cell r="A18" t="str">
-            <v>Pendiing</v>
+            <v>Pending</v>
           </cell>
           <cell r="B18" t="str">
             <v>secondary - Added Medicare ICN, and crossover electronically</v>
@@ -11581,10 +11651,10 @@
         </row>
         <row r="19">
           <cell r="A19" t="str">
-            <v>Denied</v>
+            <v>Under Review</v>
           </cell>
           <cell r="B19" t="str">
-            <v xml:space="preserve">***Call ins - Bundled - but we have an auth for this one </v>
+            <v xml:space="preserve">Call ins - Bundled - but we have an auth for this one </v>
           </cell>
           <cell r="C19">
             <v>46162</v>
@@ -11630,10 +11700,10 @@
         </row>
         <row r="22">
           <cell r="A22" t="str">
-            <v>Denied</v>
+            <v>Under Review</v>
           </cell>
           <cell r="B22" t="str">
-            <v xml:space="preserve">***Expecting ins reply - DND as medical necessity - Jess sent MR </v>
+            <v xml:space="preserve">Expecting ins reply - DND as medical necessity - Jess sent MR </v>
           </cell>
           <cell r="C22">
             <v>46197</v>
@@ -12248,10 +12318,10 @@
         </row>
         <row r="16">
           <cell r="A16" t="str">
-            <v>Denied</v>
+            <v>Under Review</v>
           </cell>
           <cell r="B16" t="str">
-            <v xml:space="preserve">***Start chat on UHC portal to check the rendering provider status </v>
+            <v xml:space="preserve">Start chat on UHC portal to check the rendering provider status </v>
           </cell>
           <cell r="C16">
             <v>46240</v>
@@ -12293,10 +12363,10 @@
         </row>
         <row r="19">
           <cell r="A19" t="str">
-            <v>Denied</v>
+            <v>Finalized</v>
           </cell>
           <cell r="B19" t="str">
-            <v>I sent an email to provider about this matter - The 3-year clock follows the provider relationship - Dr Wilson doesnt want to change the cpt code - BCBS AZ denied 99204 because she's an established patient. The encounter notes calls it a "re-establishment visit," and she had ESIs with us in 2024-2025- DND 99204+25 Remark CO_B16 Contractual Obligation - 'New Patient' qualifications were not met</v>
+            <v>Adjusted balance - I sent an email to provider about this matter - The 3-year clock follows the provider relationship - Dr Wilson doesnt want to change the cpt code - BCBS AZ denied 99204 because she's an established patient. The encounter notes calls it a "re-establishment visit," and she had ESIs with us in 2024-2025- DND 99204+25 Remark CO_B16 Contractual Obligation - 'New Patient' qualifications were not met</v>
           </cell>
           <cell r="C19">
             <v>46238</v>
@@ -12693,8 +12763,11 @@
           </cell>
         </row>
         <row r="74">
+          <cell r="A74" t="str">
+            <v>Under Review</v>
+          </cell>
           <cell r="B74" t="str">
-            <v>***Waiting for account to get activated again</v>
+            <v>Waiting for account to get activated again</v>
           </cell>
           <cell r="D74">
             <v>562518339</v>
@@ -12770,7 +12843,7 @@
         </row>
         <row r="3">
           <cell r="A3" t="str">
-            <v>Denied</v>
+            <v>Finalized</v>
           </cell>
           <cell r="B3" t="str">
             <v>ABN signed - $0.00 charges listed for A6010 in case insurance didn't pay</v>
@@ -12821,10 +12894,10 @@
         </row>
         <row r="6">
           <cell r="A6" t="str">
-            <v>Pending</v>
+            <v>Under Review</v>
           </cell>
           <cell r="B6" t="str">
-            <v>***Still processing - check again on 09/16/2026</v>
+            <v>Still processing - check again on 09/16/2026</v>
           </cell>
           <cell r="D6">
             <v>564662813</v>
@@ -12849,10 +12922,10 @@
         </row>
         <row r="8">
           <cell r="A8" t="str">
-            <v>Denied</v>
+            <v>Under Review</v>
           </cell>
           <cell r="B8" t="str">
-            <v xml:space="preserve">***Waiting for bcbs alabama portal access - Jess sent MR throught fax </v>
+            <v xml:space="preserve">Waiting for bcbs alabama portal access - Jess sent MR throught fax </v>
           </cell>
           <cell r="C8">
             <v>46204</v>
@@ -12880,10 +12953,10 @@
         </row>
         <row r="10">
           <cell r="A10" t="str">
-            <v>Denied</v>
+            <v>Under Review</v>
           </cell>
           <cell r="B10" t="str">
-            <v>***call ins and check provider status on dos - DND rendering provider OON</v>
+            <v>call ins and check provider status on dos - DND rendering provider OON</v>
           </cell>
           <cell r="C10">
             <v>46225</v>
@@ -12945,7 +13018,7 @@
         </row>
         <row r="14">
           <cell r="A14" t="str">
-            <v>Denied</v>
+            <v>Finalized</v>
           </cell>
           <cell r="B14" t="str">
             <v>Shifted to PT - ABN signed - No coverage - Policy Number: MP.009.35 - DND Acodes - PR_204 Patient Responsibility - This service/equipment/drug is not covered under the patient's current benefit plan</v>
@@ -12979,7 +13052,7 @@
         </row>
         <row r="16">
           <cell r="A16" t="str">
-            <v>Denied</v>
+            <v>Finalized</v>
           </cell>
           <cell r="B16" t="str">
             <v xml:space="preserve">Adjusted balance - no auth found - DND Acodes missing auth  </v>
@@ -12996,10 +13069,10 @@
         </row>
         <row r="17">
           <cell r="A17" t="str">
-            <v>Denied</v>
+            <v>Under Review</v>
           </cell>
           <cell r="B17" t="str">
-            <v>***DND Acodes Preferred Homecare is responsible for these services. Please submit the claim to Preferred Homecare for consideration.</v>
+            <v>DND Acodes Preferred Homecare is responsible for these services. Please submit the claim to Preferred Homecare for consideration.</v>
           </cell>
           <cell r="C17">
             <v>46204</v>
@@ -13010,7 +13083,7 @@
         </row>
         <row r="18">
           <cell r="A18" t="str">
-            <v>Denied</v>
+            <v>Finalized</v>
           </cell>
           <cell r="B18" t="str">
             <v xml:space="preserve">Adjusted balance - Acodes no covered with BCBS M2K - DND missing auth </v>
@@ -13044,10 +13117,10 @@
         </row>
         <row r="20">
           <cell r="A20" t="str">
-            <v>Denied</v>
+            <v>Under Review</v>
           </cell>
           <cell r="B20" t="str">
-            <v>*** DND Acodes Preferred Homecare is responsible for these services. Please submit the claim to Preferred Homecare for consideration. -Remark N216 We do not offer coverage for this type of service or the patient is not enrolled in this portion of our benefit package</v>
+            <v>DND Acodes Preferred Homecare is responsible for these services. Please submit the claim to Preferred Homecare for consideration. -Remark N216 We do not offer coverage for this type of service or the patient is not enrolled in this portion of our benefit package</v>
           </cell>
           <cell r="C20">
             <v>46211</v>
@@ -13058,7 +13131,7 @@
         </row>
         <row r="21">
           <cell r="A21" t="str">
-            <v>Denied</v>
+            <v>Finalized</v>
           </cell>
           <cell r="B21" t="str">
             <v xml:space="preserve">Adjusted balance - Acodes no covered with BCBS M2K - DND missing auth </v>
@@ -13109,7 +13182,7 @@
         </row>
         <row r="24">
           <cell r="A24" t="str">
-            <v>Denied</v>
+            <v>Finalized</v>
           </cell>
           <cell r="B24" t="str">
             <v>Shifted to PT - ABN signed - No coverage - Policy Number: MP.009.35 - DND Acodes - PR_204 Patient Responsibility - This service/equipment/drug is not covered under the patient's current benefit plan</v>
@@ -13364,8 +13437,11 @@
           </cell>
         </row>
         <row r="50">
+          <cell r="A50" t="str">
+            <v>Under Review</v>
+          </cell>
           <cell r="B50" t="str">
-            <v>***Waiting for account to get activated again</v>
+            <v>Waiting for account to get activated again</v>
           </cell>
           <cell r="D50">
             <v>562142694</v>
@@ -13389,8 +13465,11 @@
           </cell>
         </row>
         <row r="52">
+          <cell r="A52" t="str">
+            <v>Under Review</v>
+          </cell>
           <cell r="B52" t="str">
-            <v>***Waiting for account to get activated again</v>
+            <v>Waiting for account to get activated again</v>
           </cell>
           <cell r="D52">
             <v>564106191</v>
@@ -13744,10 +13823,10 @@
         </row>
         <row r="7">
           <cell r="A7" t="str">
-            <v>Denied</v>
+            <v>Under Review</v>
           </cell>
           <cell r="B7" t="str">
-            <v>***Call ins to get bar code letter if needed and insights on denials</v>
+            <v>Call ins to get bar code letter if needed and insights on denials</v>
           </cell>
           <cell r="C7">
             <v>46197</v>
@@ -13775,10 +13854,10 @@
         </row>
         <row r="9">
           <cell r="A9" t="str">
-            <v>Denied</v>
+            <v>Under Review</v>
           </cell>
           <cell r="B9" t="str">
-            <v>***Call ins to get bar code letter if needed and insights on denials</v>
+            <v>Call ins to get bar code letter if needed and insights on denials</v>
           </cell>
           <cell r="C9">
             <v>46197</v>
@@ -14118,8 +14197,11 @@
           </cell>
         </row>
         <row r="37">
+          <cell r="A37" t="str">
+            <v>Under Review</v>
+          </cell>
           <cell r="B37" t="str">
-            <v>***Waiting for account to get activated again</v>
+            <v>Waiting for account to get activated again</v>
           </cell>
           <cell r="D37">
             <v>563830748</v>

--- a/Specialty Claims 2026-S1/ALL Claims 2026-S1 - Master.xlsx
+++ b/Specialty Claims 2026-S1/ALL Claims 2026-S1 - Master.xlsx
@@ -279,7 +279,7 @@
     <t>Row order - timely filing deadline</t>
   </si>
   <si>
-    <t>Sorted the same way as the monthly workbooks: by Days Until Deadline, most urgent first, so the two views line up. A negative number means the filing window has already closed; a blank means no limit is on file.</t>
+    <t>Sorted the same way as the monthly workbooks: by Days Until Deadline, most urgent first, so the two views line up. A negative number means the filing window has already closed; a blank means no limit is on file. The counts below are as at 19 September 2026, and the row order is a snapshot - sort ascending on Days Until Deadline to bring it up to date.</t>
   </si>
   <si>
     <t xml:space="preserve">    1 - Due in 5 days or less: 10</t>
@@ -327,10 +327,10 @@
     <t xml:space="preserve">    [1]  2026-01 January - Specialty Claims.xlsx</t>
   </si>
   <si>
-    <t xml:space="preserve">    [2]  2026-02 February - Specialty Claims.xlsx</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    [3]  2026-03 March - Specialty Claims.xlsx</t>
+    <t xml:space="preserve">    [2]  2026-03 March - Specialty Claims.xlsx</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    [3]  2026-02 February - Specialty Claims.xlsx</t>
   </si>
   <si>
     <t xml:space="preserve">    [4]  2026-04 April - Specialty Claims.xlsx</t>
@@ -5562,7 +5562,7 @@
     <t xml:space="preserve">    1 - Due in 5 days or less: 21</t>
   </si>
   <si>
-    <t xml:space="preserve">    2 - Due in 6-30 days: 25</t>
+    <t xml:space="preserve">    2 - Due in 6-30 days: 23</t>
   </si>
   <si>
     <t xml:space="preserve">    3 - Due in 31+ days: 155</t>
@@ -5577,7 +5577,7 @@
     <t xml:space="preserve">Claim Status, Notes, Processed Date and Latest Date Worked (shaded pale green) are formulas. Each one looks up its claim by Primary Claim ID in the matching specialty sheet of the matching monthly workbook and returns whatever is entered there. Edit any of the four in a monthly file, save it, and this file shows the change.</t>
   </si>
   <si>
-    <t xml:space="preserve">    1 - Due in 5 days or less: 20</t>
+    <t xml:space="preserve">    1 - Due in 5 days or less: 22</t>
   </si>
   <si>
     <t xml:space="preserve">    4 - Past deadline: 239</t>
